--- a/For Python_final.xlsx
+++ b/For Python_final.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Администратор\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Администратор\Desktop\automation\new0.1\bond_platform_3\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C6F38CF0-0DA4-40B5-B65C-19D80B4D0E1B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{97AB25E5-55D0-42E2-B3F4-38B190545516}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-30015" yWindow="6390" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="B+S+B+S" sheetId="2" r:id="rId1"/>
@@ -4476,7 +4476,7 @@
         <v>670</v>
       </c>
       <c r="E66" s="78">
-        <f t="shared" si="22"/>
+        <f>+$F$20+F66</f>
         <v>-67757.416909206862</v>
       </c>
       <c r="F66" s="79">

--- a/For Python_final.xlsx
+++ b/For Python_final.xlsx
@@ -8,13 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Администратор\Desktop\automation\new0.1\bond_platform_3\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{97AB25E5-55D0-42E2-B3F4-38B190545516}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5EB61B68-25B3-4421-A388-669A0A61C67E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-30015" yWindow="6390" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="B+S+B+S" sheetId="2" r:id="rId1"/>
-    <sheet name="Sheet1" sheetId="1" r:id="rId2"/>
+    <sheet name="exel caalculator" sheetId="1" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,8 +39,30 @@
 </workbook>
 </file>
 
+<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+  <metadataTypes count="1">
+    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
+  </metadataTypes>
+  <futureMetadata name="XLDAPR" count="1">
+    <bk>
+      <extLst>
+        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
+          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
+        </ext>
+      </extLst>
+    </bk>
+  </futureMetadata>
+  <cellMetadata count="1">
+    <bk>
+      <rc t="1" v="0"/>
+    </bk>
+  </cellMetadata>
+</metadata>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="56">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="180" uniqueCount="84">
   <si>
     <t>ISIN</t>
   </si>
@@ -212,12 +234,96 @@
   <si>
     <t>US91</t>
   </si>
+  <si>
+    <t>aaa1</t>
+  </si>
+  <si>
+    <t>Coupon Date</t>
+  </si>
+  <si>
+    <t>Transaction Table</t>
+  </si>
+  <si>
+    <t>bbb1</t>
+  </si>
+  <si>
+    <t>Date</t>
+  </si>
+  <si>
+    <t>Nominal Buy/Sell</t>
+  </si>
+  <si>
+    <t xml:space="preserve">New Coupon </t>
+  </si>
+  <si>
+    <t>Buy/Sell Type</t>
+  </si>
+  <si>
+    <t>Remaining Discount</t>
+  </si>
+  <si>
+    <t>Remaining Premium</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Buy Premium </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Buy Discount </t>
+  </si>
+  <si>
+    <t>Cash flow</t>
+  </si>
+  <si>
+    <t>Acrrued Coupon</t>
+  </si>
+  <si>
+    <t>Nominals</t>
+  </si>
+  <si>
+    <t>Par Value</t>
+  </si>
+  <si>
+    <t>Clean Trade Price</t>
+  </si>
+  <si>
+    <t>Coupon Rate</t>
+  </si>
+  <si>
+    <t>Interest Frequency</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Full Sell </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Maturity </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Partial Sell </t>
+  </si>
+  <si>
+    <t>Buy Date</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Premium </t>
+  </si>
+  <si>
+    <t>Sell Date</t>
+  </si>
+  <si>
+    <t>ECV Transaction</t>
+  </si>
+  <si>
+    <t>Realized Interest Income</t>
+  </si>
+  <si>
+    <t xml:space="preserve">                       </t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="11">
+  <numFmts count="27">
     <numFmt numFmtId="43" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="164" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="165" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
@@ -229,8 +335,24 @@
     <numFmt numFmtId="171" formatCode="_(* #,##0.000000000000000000000000_);_(* \(#,##0.000000000000000000000000\);_(* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="172" formatCode="_(* #,##0.0000000_);_(* \(#,##0.0000000\);_(* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="173" formatCode="0.0000%"/>
+    <numFmt numFmtId="174" formatCode="dd/mm/yy;@"/>
+    <numFmt numFmtId="175" formatCode="0.0000000"/>
+    <numFmt numFmtId="176" formatCode="_-* #,##0.000\ _₽_-;\-* #,##0.000\ _₽_-;_-* &quot;-&quot;???\ _₽_-;_-@_-"/>
+    <numFmt numFmtId="177" formatCode="#,##0.000"/>
+    <numFmt numFmtId="178" formatCode="#,##0.0"/>
+    <numFmt numFmtId="179" formatCode="#,##0.0000"/>
+    <numFmt numFmtId="180" formatCode="_-* #,##0.00000\ _₽_-;\-* #,##0.00000\ _₽_-;_-* &quot;-&quot;?????\ _₽_-;_-@_-"/>
+    <numFmt numFmtId="181" formatCode="yyyy\-mm\-dd;@"/>
+    <numFmt numFmtId="182" formatCode="_(* #,##0.000_);_(* \(#,##0.000\);_(* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="183" formatCode="#,##0.00000"/>
+    <numFmt numFmtId="184" formatCode="dd/mm/yyyy;@"/>
+    <numFmt numFmtId="185" formatCode="_-* #,##0.000000_-;\-* #,##0.000000_-;_-* &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="186" formatCode="0.0000000000"/>
+    <numFmt numFmtId="187" formatCode="_(* #,##0.00000_);_(* \(#,##0.00000\);_(* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="188" formatCode="_(* #,##0.0_);_(* \(#,##0.0\);_(* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="189" formatCode="#,##0.000000"/>
   </numFmts>
-  <fonts count="14" x14ac:knownFonts="1">
+  <fonts count="22" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -340,8 +462,69 @@
       <name val="Arial"/>
       <family val="2"/>
     </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="204"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="14"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="1"/>
+      <name val="Arial Black"/>
+      <family val="2"/>
+      <charset val="204"/>
+    </font>
+    <font>
+      <sz val="16"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="16"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="204"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
   </fonts>
-  <fills count="11">
+  <fills count="16">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -402,8 +585,38 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.39997558519241921"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.39997558519241921"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.39997558519241921"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="16">
+  <borders count="30">
     <border>
       <left/>
       <right/>
@@ -604,6 +817,164 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="dotted">
+        <color indexed="64"/>
+      </right>
+      <top style="dotted">
+        <color indexed="64"/>
+      </top>
+      <bottom style="dotted">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="dotted">
+        <color indexed="64"/>
+      </left>
+      <right style="dotted">
+        <color indexed="64"/>
+      </right>
+      <top style="dotted">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="dotted">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="dotted">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="dotted">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="dotted">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="dotted">
+        <color indexed="64"/>
+      </left>
+      <right style="dotted">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="dotted">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="dotted">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="dotted">
+        <color indexed="64"/>
+      </left>
+      <right style="dotted">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
@@ -611,7 +982,7 @@
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="112">
+  <cellXfs count="247">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
@@ -915,6 +1286,325 @@
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="11" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="15" fillId="7" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="4" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="174" fontId="4" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="4" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="7" borderId="7" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="7" borderId="7" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="0" fillId="7" borderId="7" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="175" fontId="0" fillId="7" borderId="7" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="7" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="7" borderId="7" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="18" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="7" borderId="7" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="7" borderId="7" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="19" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="3" fontId="5" fillId="8" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="3" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="179" fontId="5" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="14" fontId="0" fillId="7" borderId="20" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="0" fillId="7" borderId="20" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="7" borderId="20" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="20" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="7" borderId="20" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="7" borderId="20" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="21" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="5" fillId="7" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="180" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="174" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="14" fontId="5" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="181" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="14" fillId="12" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="12" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="182" fontId="5" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="10" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="4" fontId="5" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="174" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="13" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="183" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="38" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="13" fillId="5" borderId="7" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="184" fontId="0" fillId="7" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="37" fontId="0" fillId="7" borderId="7" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="182" fontId="0" fillId="7" borderId="7" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="182" fontId="0" fillId="7" borderId="7" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="185" fontId="0" fillId="7" borderId="7" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="4" fontId="0" fillId="7" borderId="7" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="186" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="184" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="37" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="182" fontId="0" fillId="7" borderId="7" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="43" fontId="0" fillId="7" borderId="7" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="182" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="182" fontId="0" fillId="0" borderId="7" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="4" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="4" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="187" fontId="0" fillId="7" borderId="7" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="187" fontId="0" fillId="8" borderId="7" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="188" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="188" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="188" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="188" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="188" fontId="0" fillId="0" borderId="7" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="185" fontId="0" fillId="14" borderId="7" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="15" borderId="7" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="189" fontId="0" fillId="15" borderId="7" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="187" fontId="0" fillId="8" borderId="7" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="172" fontId="0" fillId="15" borderId="7" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="187" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="184" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="4">
@@ -923,7 +1613,411 @@
     <cellStyle name="Процентный" xfId="2" builtinId="5"/>
     <cellStyle name="Финансовый" xfId="1" builtinId="3"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="26">
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="5"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="166" formatCode="_-* #,##0.00000_-;\-* #,##0.00000_-;_-* &quot;-&quot;??_-;_-@_-"/>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color auto="1"/>
+        </left>
+        <right style="thin">
+          <color auto="1"/>
+        </right>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <bottom style="thin">
+          <color auto="1"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="3" formatCode="#,##0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color auto="1"/>
+        </left>
+        <right style="thin">
+          <color auto="1"/>
+        </right>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <bottom style="thin">
+          <color auto="1"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="177" formatCode="#,##0.000"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color auto="1"/>
+        </left>
+        <right style="thin">
+          <color auto="1"/>
+        </right>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <bottom style="thin">
+          <color auto="1"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="178" formatCode="#,##0.0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color auto="1"/>
+        </left>
+        <right style="thin">
+          <color auto="1"/>
+        </right>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <bottom style="thin">
+          <color auto="1"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="3" formatCode="#,##0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color auto="1"/>
+        </left>
+        <right style="thin">
+          <color auto="1"/>
+        </right>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <bottom style="thin">
+          <color auto="1"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="3" formatCode="#,##0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color auto="1"/>
+        </left>
+        <right style="thin">
+          <color auto="1"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="177" formatCode="#,##0.000"/>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="9" tint="0.59999389629810485"/>
+        </patternFill>
+      </fill>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="176" formatCode="_-* #,##0.000\ _₽_-;\-* #,##0.000\ _₽_-;_-* &quot;-&quot;???\ _₽_-;_-@_-"/>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="9" tint="0.59999389629810485"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color auto="1"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="4" formatCode="#,##0.00"/>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color auto="1"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="2" formatCode="0.00"/>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="9" tint="0.59999389629810485"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color auto="1"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="3" formatCode="#,##0"/>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="9" tint="0.59999389629810485"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color auto="1"/>
+        </left>
+        <right style="thin">
+          <color auto="1"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="9" tint="0.59999389629810485"/>
+        </patternFill>
+      </fill>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left/>
+        <right style="thin">
+          <color auto="1"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <bottom style="thin">
+          <color auto="1"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <left style="thin">
+          <color auto="1"/>
+        </left>
+        <right style="thin">
+          <color auto="1"/>
+        </right>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <bottom style="thin">
+          <color auto="1"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top/>
+        <bottom/>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="190" formatCode="dd/mm/yyyy"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <bottom style="thin">
+          <color auto="1"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <bottom style="thin">
+          <color auto="1"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <left style="thin">
+          <color auto="1"/>
+        </left>
+        <right style="thin">
+          <color auto="1"/>
+        </right>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <bottom style="thin">
+          <color auto="1"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -934,6 +2028,87 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{18640111-A66C-4FE9-9DD6-4AE223971B26}" name="CouponDates53678910311541015592055814114" displayName="CouponDates53678910311541015592055814114" ref="F1:F13" totalsRowShown="0" headerRowDxfId="25" dataDxfId="24" headerRowBorderDxfId="22" tableBorderDxfId="23" totalsRowBorderDxfId="21">
+  <autoFilter ref="F1:F13" xr:uid="{18640111-A66C-4FE9-9DD6-4AE223971B26}"/>
+  <tableColumns count="1">
+    <tableColumn id="1" xr3:uid="{0907E50E-6285-421C-80D0-D9EECA6C05D8}" name="Coupon Date" dataDxfId="20"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{FF9EC445-CA7D-47BC-8825-18993C84BB80}" name="SellTable1213614168132166915125" displayName="SellTable1213614168132166915125" ref="J2:V7" totalsRowShown="0" headerRowDxfId="19" headerRowBorderDxfId="17" tableBorderDxfId="18" totalsRowBorderDxfId="16">
+  <autoFilter ref="J2:V7" xr:uid="{FF9EC445-CA7D-47BC-8825-18993C84BB80}"/>
+  <tableColumns count="13">
+    <tableColumn id="1" xr3:uid="{B8BFF16C-D7D3-4566-A7B2-5591DE9B445A}" name="Date" dataDxfId="15"/>
+    <tableColumn id="2" xr3:uid="{B4FB979A-EF32-4E01-94B4-562DD18D35BB}" name="Nominal Buy/Sell" dataDxfId="14"/>
+    <tableColumn id="3" xr3:uid="{DAD197F1-DB3E-4393-8548-942480708311}" name="Price" dataDxfId="13"/>
+    <tableColumn id="4" xr3:uid="{7F7973B5-27F7-41E6-8BA2-752A37E8C355}" name="New Coupon " dataDxfId="12">
+      <calculatedColumnFormula>IF(COUNTIF($J$3:$J$8,J3)=0,0,
+  _xlfn.LET(
+    _xlpm.t,J3,
+    _xlpm.nomRemaining,
+    MAX(0,
+      $B$3
+      + SUMIFS($K$3:$K$8,$J$3:$J$8,"&lt;="&amp;_xlpm.t)
+    ),
+    _xlpm.nomRemaining * ($B$5/100) / $B$8
+  )
+)</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="5" xr3:uid="{564456A6-BC7B-48EE-BBF1-E4EDBF794B7B}" name="Buy/Sell Type" dataDxfId="11"/>
+    <tableColumn id="6" xr3:uid="{F6D97D62-4BA2-4BC4-823B-E651EAF02ADC}" name="Remaining Discount" dataDxfId="10">
+      <calculatedColumnFormula>B13+SellTable1213614168132166915125[[#This Row],[Buy Discount ]]</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="7" xr3:uid="{4F6D090F-C1B0-435B-9E33-1EC9B6171BDA}" name="Remaining Premium" dataDxfId="9">
+      <calculatedColumnFormula>B13+SellTable1213614168132166915125[[#This Row],[Buy Discount ]]</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="8" xr3:uid="{D6FAD4B5-9D6D-4653-8F5F-CD823C5AA3A7}" name="Buy Premium " dataDxfId="8">
+      <calculatedColumnFormula>IF(L3&gt;=100,((L3/100)-1)*K3,0)</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="9" xr3:uid="{BBF9B549-94B6-46DC-A527-D11C11ED5014}" name="Buy Discount " dataDxfId="7">
+      <calculatedColumnFormula>IF(OR(L3=0,L3&gt;=100,K3&lt;0),0,((L3/100)-1)*K3)</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="10" xr3:uid="{F2EFBE4A-13EC-4E65-A8B8-3FCAA912BFC2}" name="Cash flow" dataDxfId="6">
+      <calculatedColumnFormula>-SellTable1213614168132166915125[[#This Row],[Nominal Buy/Sell]]*SellTable1213614168132166915125[[#This Row],[Price]]/100</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="11" xr3:uid="{4E2BF662-8ACC-4507-AB2A-53349338F337}" name="Acrrued Coupon" dataDxfId="5">
+      <calculatedColumnFormula>IF($J3="","",
+  IF($K3&lt;=0,"",
+    _xlfn.LET(
+      _xlpm.t,       $J3,
+      _xlpm.nom,     $K3,
+      _xlpm.lastCpn, IFERROR(_xlfn.MAXIFS($F$2:$F$14,$F$2:$F$14,"&lt;="&amp;_xlpm.t),$B$10),
+      _xlpm.lastCpn2,IF(_xlpm.lastCpn=0,$B$10,_xlpm.lastCpn),
+      _xlpm.nextCpn, _xlfn.MINIFS($F$2:$F$14,$F$2:$F$14,"&gt;"&amp;_xlpm.t),
+      _xlpm.frac,    (_xlpm.t-_xlpm.lastCpn2)/(_xlpm.nextCpn-_xlpm.lastCpn2),
+      _xlpm.frac * (_xlpm.nom*$B$5/2/100)
+    )
+  )
+)</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="12" xr3:uid="{200261F9-B6E7-42E4-8C7A-A8126F24A308}" name="Nominals" dataDxfId="4">
+      <calculatedColumnFormula>$B$3+SUM($K$3:K3)</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="13" xr3:uid="{E00C3FDC-BC9B-449E-ADD5-0999A62AD192}" name="WAC" dataDxfId="3">
+      <calculatedColumnFormula array="1">_xlfn.LET(
+  _xlpm.i,        ROW()-ROW($V$3)+1,
+  _xlpm.prev_wac, IF(_xlpm.i=1, $B$4, INDEX($V$3:$V$8, _xlpm.i-1)),
+  _xlpm.prev_nom, IF(_xlpm.i=1, $B$3, INDEX($U$3:$U$8, _xlpm.i-1)),
+  _xlpm.k,        INDEX($K$3:$K$8, _xlpm.i),
+  _xlpm.pr,       INDEX($L$3:$L$8, _xlpm.i),
+  _xlpm.d,        INDEX($J$3:$J$8, _xlpm.i),
+  IF(_xlpm.d="", "",
+    IF(_xlpm.k&gt;0, (_xlpm.prev_nom*_xlpm.prev_wac + _xlpm.k*_xlpm.pr)/(_xlpm.prev_nom+_xlpm.k), _xlpm.prev_wac))
+)</calculatedColumnFormula>
+    </tableColumn>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -2367,25 +3542,25 @@
         <f>I34-G34-E34</f>
         <v>137000000</v>
       </c>
-      <c r="L34" s="80">
-        <f>+L33</f>
-        <v>99.86328125</v>
+      <c r="L34" s="80" t="b">
+        <f>F4=+L33</f>
+        <v>0</v>
       </c>
       <c r="M34" s="50">
-        <f t="shared" ref="M34:M39" si="5">($K$32*(L34-$L$32)/100)</f>
-        <v>0</v>
+        <f>($K$32*(L34-$L$32)/100)</f>
+        <v>-136812695.3125</v>
       </c>
       <c r="N34" s="50">
         <f>M34-H34-F34</f>
-        <v>-2712.2484923339011</v>
+        <v>-136815407.56099233</v>
       </c>
       <c r="O34" s="50">
         <f t="shared" si="0"/>
-        <v>136812695.31</v>
+        <v>0</v>
       </c>
       <c r="P34" s="51">
-        <f t="shared" ref="P34:P41" si="6">+$I$32+H34+N34-O34+F34</f>
-        <v>3.5884113458450884E-9</v>
+        <f t="shared" ref="P34:P41" si="5">+$I$32+H34+N34-O34+F34</f>
+        <v>-2.4999940274028631E-3</v>
       </c>
       <c r="R34" s="51"/>
       <c r="V34" s="81">
@@ -2431,14 +3606,14 @@
         <v>2270718.232044199</v>
       </c>
       <c r="K35" s="79">
-        <f t="shared" ref="K35:K75" si="7">I35-G35-E35</f>
+        <f t="shared" ref="K35:K75" si="6">I35-G35-E35</f>
         <v>137000000</v>
       </c>
       <c r="L35" s="87">
         <v>97.132788000000005</v>
       </c>
       <c r="M35" s="50">
-        <f t="shared" si="5"/>
+        <f>($K$32*(L35-$L$32)/100)</f>
         <v>-3740775.752499993</v>
       </c>
       <c r="N35" s="50">
@@ -2446,11 +3621,11 @@
         <v>-3748274.3218611516</v>
       </c>
       <c r="O35" s="50">
-        <f t="shared" si="0"/>
+        <f>ROUND(K35*L35/100,2)</f>
         <v>133071919.56</v>
       </c>
       <c r="P35" s="51">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>-2.4999894476422924E-3</v>
       </c>
       <c r="Q35" s="88"/>
@@ -2499,14 +3674,14 @@
         <v>2740000</v>
       </c>
       <c r="K36" s="79">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>137000000</v>
       </c>
       <c r="L36" s="87">
         <v>97.132788000000005</v>
       </c>
       <c r="M36" s="50">
-        <f t="shared" si="5"/>
+        <f>($K$32*(L36-$L$32)/100)</f>
         <v>-3740775.752499993</v>
       </c>
       <c r="N36" s="50">
@@ -2518,7 +3693,7 @@
         <v>133071919.56</v>
       </c>
       <c r="P36" s="51">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>-2.4999916695378488E-3</v>
       </c>
       <c r="Q36" s="88"/>
@@ -2534,7 +3709,7 @@
         <v>56060.4</v>
       </c>
       <c r="Y36" s="82">
-        <f t="shared" ref="Y36:Y75" si="8">+X36-X35</f>
+        <f t="shared" ref="Y36:Y75" si="7">+X36-X35</f>
         <v>0</v>
       </c>
     </row>
@@ -2566,14 +3741,14 @@
         <v>461630.4347826087</v>
       </c>
       <c r="K37" s="79">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>137000000</v>
       </c>
       <c r="L37" s="87">
         <v>97.132788000000005</v>
       </c>
       <c r="M37" s="50">
-        <f t="shared" si="5"/>
+        <f>($K$32*(L37-$L$32)/100)</f>
         <v>-3740775.752499993</v>
       </c>
       <c r="N37" s="50">
@@ -2585,7 +3760,7 @@
         <v>133071919.56</v>
       </c>
       <c r="P37" s="51">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>-2.4999938905239105E-3</v>
       </c>
       <c r="Q37" s="88"/>
@@ -2597,11 +3772,11 @@
         <v>0.6</v>
       </c>
       <c r="X37" s="82">
-        <f t="shared" ref="X37:X48" si="9">ROUND((K37+Q37)*V37*W37,2)</f>
+        <f t="shared" ref="X37:X48" si="8">ROUND((K37+Q37)*V37*W37,2)</f>
         <v>56060.4</v>
       </c>
       <c r="Y37" s="82">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
     </row>
@@ -2633,14 +3808,14 @@
         <v>908369.56521739124</v>
       </c>
       <c r="K38" s="79">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>137000000</v>
       </c>
       <c r="L38" s="87">
         <v>97.132788000000005</v>
       </c>
       <c r="M38" s="50">
-        <f t="shared" si="5"/>
+        <f>($K$32*(L38-$L$32)/100)</f>
         <v>-3740775.752499993</v>
       </c>
       <c r="N38" s="50">
@@ -2664,11 +3839,11 @@
         <v>0.6</v>
       </c>
       <c r="X38" s="82">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>56060.4</v>
       </c>
       <c r="Y38" s="82">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
     </row>
@@ -2700,14 +3875,14 @@
         <v>1370000</v>
       </c>
       <c r="K39" s="79">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>137000000</v>
       </c>
       <c r="L39" s="87">
         <v>97.132788000000005</v>
       </c>
       <c r="M39" s="50">
-        <f t="shared" si="5"/>
+        <f t="shared" ref="M34:M39" si="9">($K$32*(L39-$L$32)/100)</f>
         <v>-3740775.752499993</v>
       </c>
       <c r="N39" s="50">
@@ -2719,7 +3894,7 @@
         <v>133071919.56</v>
       </c>
       <c r="P39" s="51">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>-2.4999915331136435E-3</v>
       </c>
       <c r="Q39" s="88"/>
@@ -2731,11 +3906,11 @@
         <v>0.6</v>
       </c>
       <c r="X39" s="82">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>56060.4</v>
       </c>
       <c r="Y39" s="82">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
     </row>
@@ -2762,7 +3937,7 @@
       </c>
       <c r="J40" s="96"/>
       <c r="K40" s="96">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>5899999.9950000001</v>
       </c>
       <c r="L40" s="98">
@@ -2809,7 +3984,7 @@
         <v>1894978.260869565</v>
       </c>
       <c r="K41" s="79">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>137000000</v>
       </c>
       <c r="L41" s="87">
@@ -2828,7 +4003,7 @@
         <v>136507656.25</v>
       </c>
       <c r="P41" s="51">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>-2.4999869565363042E-3</v>
       </c>
       <c r="Q41" s="88"/>
@@ -2840,7 +4015,7 @@
         <v>0.6</v>
       </c>
       <c r="X41" s="82">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>56060.4</v>
       </c>
       <c r="Y41" s="82">
@@ -2879,7 +4054,7 @@
         <v>2376489.1304347827</v>
       </c>
       <c r="K42" s="79">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>142899999.995</v>
       </c>
       <c r="L42" s="87">
@@ -2910,11 +4085,11 @@
         <v>0.6</v>
       </c>
       <c r="X42" s="82">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>58474.68</v>
       </c>
       <c r="Y42" s="82">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>2414.2799999999988</v>
       </c>
     </row>
@@ -2949,7 +4124,7 @@
         <v>2858000</v>
       </c>
       <c r="K43" s="79">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>142899999.995</v>
       </c>
       <c r="L43" s="87">
@@ -2964,7 +4139,7 @@
         <v>-3931888.3562190086</v>
       </c>
       <c r="O43" s="50">
-        <f t="shared" si="0"/>
+        <f>ROUND(K43*L43/100,2)</f>
         <v>138802754.05000001</v>
       </c>
       <c r="P43" s="51">
@@ -2980,11 +4155,11 @@
         <v>0.6</v>
       </c>
       <c r="X43" s="82">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>58474.68</v>
       </c>
       <c r="Y43" s="82">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
     </row>
@@ -3019,7 +4194,7 @@
         <v>442121.54696132598</v>
       </c>
       <c r="K44" s="79">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>142899999.995</v>
       </c>
       <c r="L44" s="87">
@@ -3050,11 +4225,11 @@
         <v>0.6</v>
       </c>
       <c r="X44" s="82">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>58474.68</v>
       </c>
       <c r="Y44" s="82">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
     </row>
@@ -3089,7 +4264,7 @@
         <v>931613.25966850831</v>
       </c>
       <c r="K45" s="79">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>142899999.995</v>
       </c>
       <c r="L45" s="87">
@@ -3121,11 +4296,11 @@
         <v>0.6</v>
       </c>
       <c r="X45" s="82">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>58474.68</v>
       </c>
       <c r="Y45" s="82">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
     </row>
@@ -3160,7 +4335,7 @@
         <v>1405314.9171270719</v>
       </c>
       <c r="K46" s="79">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>142899999.995</v>
       </c>
       <c r="L46" s="87">
@@ -3192,11 +4367,11 @@
         <v>0.6</v>
       </c>
       <c r="X46" s="82">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>58474.68</v>
       </c>
       <c r="Y46" s="82">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
     </row>
@@ -3231,7 +4406,7 @@
         <v>1894806.629834254</v>
       </c>
       <c r="K47" s="79">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>142899999.995</v>
       </c>
       <c r="L47" s="87">
@@ -3262,11 +4437,11 @@
         <v>0.6</v>
       </c>
       <c r="X47" s="82">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>58474.68</v>
       </c>
       <c r="Y47" s="82">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
     </row>
@@ -3302,7 +4477,7 @@
         <v>2368508.2872928176</v>
       </c>
       <c r="K48" s="79">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>142899999.995</v>
       </c>
       <c r="L48" s="87">
@@ -3333,11 +4508,11 @@
         <v>0.6</v>
       </c>
       <c r="X48" s="82">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>58474.68</v>
       </c>
       <c r="Y48" s="82">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
     </row>
@@ -3373,14 +4548,14 @@
         <v>2858000</v>
       </c>
       <c r="K49" s="79">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>142899999.995</v>
       </c>
       <c r="L49" s="87">
         <v>97.132788000000005</v>
       </c>
       <c r="M49" s="50">
-        <f t="shared" si="15"/>
+        <f>($K$32*(L49-$L$32)/100)+($K$40*(L49-$L$40)/100)</f>
         <v>-3888738.135374601</v>
       </c>
       <c r="N49" s="50">
@@ -3444,14 +4619,14 @@
         <v>481510.86956521741</v>
       </c>
       <c r="K50" s="79">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>142899999.995</v>
       </c>
       <c r="L50" s="87">
         <v>97.132788000000005</v>
       </c>
       <c r="M50" s="50">
-        <f t="shared" si="15"/>
+        <f>($K$32*(L50-$L$32)/100)+($K$40*(L50-$L$40)/100)</f>
         <v>-3888738.135374601</v>
       </c>
       <c r="N50" s="50">
@@ -3479,7 +4654,7 @@
         <v>58474.68</v>
       </c>
       <c r="Y50" s="82">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
     </row>
@@ -3515,14 +4690,14 @@
         <v>947489.13043478248</v>
       </c>
       <c r="K51" s="79">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>142899999.995</v>
       </c>
       <c r="L51" s="87">
         <v>97.132788000000005</v>
       </c>
       <c r="M51" s="50">
-        <f t="shared" si="15"/>
+        <f>($K$32*(L51-$L$32)/100)+($K$40*(L51-$L$40)/100)</f>
         <v>-3888738.135374601</v>
       </c>
       <c r="N51" s="50">
@@ -3550,7 +4725,7 @@
         <v>58474.68</v>
       </c>
       <c r="Y51" s="82">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
     </row>
@@ -3586,7 +4761,7 @@
         <v>1429000</v>
       </c>
       <c r="K52" s="79">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>142899999.995</v>
       </c>
       <c r="L52" s="87">
@@ -3621,7 +4796,7 @@
         <v>58474.68</v>
       </c>
       <c r="Y52" s="82">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
     </row>
@@ -3688,7 +4863,7 @@
         <v>1816739.1304347825</v>
       </c>
       <c r="K54" s="79">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>142899999.995</v>
       </c>
       <c r="L54" s="87">
@@ -3759,7 +4934,7 @@
         <v>2278369.5652173916</v>
       </c>
       <c r="K55" s="79">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>136999999.99500015</v>
       </c>
       <c r="L55" s="87">
@@ -3794,7 +4969,7 @@
         <v>56060.4</v>
       </c>
       <c r="Y55" s="82">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>-2414.2799999999988</v>
       </c>
       <c r="AF55" s="63"/>
@@ -3831,7 +5006,7 @@
         <v>2740000</v>
       </c>
       <c r="K56" s="79">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>136999999.99500015</v>
       </c>
       <c r="L56" s="87">
@@ -3866,7 +5041,7 @@
         <v>56060.4</v>
       </c>
       <c r="Y56" s="82">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="AF56" s="63"/>
@@ -3903,7 +5078,7 @@
         <v>436593.40659340657</v>
       </c>
       <c r="K57" s="79">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>136999999.99500015</v>
       </c>
       <c r="L57" s="87">
@@ -3938,7 +5113,7 @@
         <v>56060.4</v>
       </c>
       <c r="Y57" s="82">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="AF57" s="63"/>
@@ -3975,7 +5150,7 @@
         <v>903296.70329670329</v>
       </c>
       <c r="K58" s="79">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>136999999.99500015</v>
       </c>
       <c r="L58" s="87">
@@ -4011,7 +5186,7 @@
         <v>56060.4</v>
       </c>
       <c r="Y58" s="82">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="AF58" s="63"/>
@@ -4036,7 +5211,7 @@
       </c>
       <c r="J59" s="96"/>
       <c r="K59" s="96">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>5900000</v>
       </c>
       <c r="L59" s="98">
@@ -4085,7 +5260,7 @@
         <v>1413296.7032967033</v>
       </c>
       <c r="K60" s="79">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>142899999.99500018</v>
       </c>
       <c r="L60" s="87">
@@ -4143,7 +5318,7 @@
         <v>548</v>
       </c>
       <c r="E61" s="78">
-        <f t="shared" ref="E61:E66" si="22">+$F$20+F61</f>
+        <f t="shared" ref="E61:E64" si="22">+$F$20+F61</f>
         <v>-94949.538168822721</v>
       </c>
       <c r="F61" s="79">
@@ -4161,7 +5336,7 @@
         <v>1900098.9010989009</v>
       </c>
       <c r="K61" s="79">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>142899999.99500015</v>
       </c>
       <c r="L61" s="87">
@@ -4172,7 +5347,7 @@
         <v>-3874926.9253990222</v>
       </c>
       <c r="N61" s="50">
-        <f t="shared" si="10"/>
+        <f>M61-H61-F61</f>
         <v>-4002296.4073141743</v>
       </c>
       <c r="O61" s="50">
@@ -4200,7 +5375,7 @@
         <v>58474.69</v>
       </c>
       <c r="Y61" s="82">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>1.0000000002037268E-2</v>
       </c>
       <c r="AF61" s="63"/>
@@ -4236,7 +5411,7 @@
         <v>2371197.8021978023</v>
       </c>
       <c r="K62" s="79">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>142899999.99500015</v>
       </c>
       <c r="L62" s="87">
@@ -4275,7 +5450,7 @@
         <v>58474.7</v>
       </c>
       <c r="Y62" s="82">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>9.9999999947613105E-3</v>
       </c>
       <c r="AF62" s="63"/>
@@ -4311,7 +5486,7 @@
         <v>2858000</v>
       </c>
       <c r="K63" s="79">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>142899999.99500015</v>
       </c>
       <c r="L63" s="87">
@@ -4350,7 +5525,7 @@
         <v>58474.720000000001</v>
       </c>
       <c r="Y63" s="82">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>2.0000000004074536E-2</v>
       </c>
       <c r="AF63" s="63"/>
@@ -4386,7 +5561,7 @@
         <v>481510.86956521741</v>
       </c>
       <c r="K64" s="79">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>142899999.99500015</v>
       </c>
       <c r="L64" s="87">
@@ -4425,7 +5600,7 @@
         <v>58474.73</v>
       </c>
       <c r="Y64" s="82">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>1.0000000002037268E-2</v>
       </c>
       <c r="AF64" s="63"/>
@@ -4494,7 +5669,7 @@
         <v>907706.52173913037</v>
       </c>
       <c r="K66" s="79">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>142899999.99500018</v>
       </c>
       <c r="L66" s="87">
@@ -4569,7 +5744,7 @@
         <v>1369000</v>
       </c>
       <c r="K67" s="79">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>136899999.9950003</v>
       </c>
       <c r="L67" s="87">
@@ -4608,7 +5783,7 @@
         <v>56019.56</v>
       </c>
       <c r="Y67" s="82">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>-2455.1800000000003</v>
       </c>
       <c r="AF67" s="63"/>
@@ -4645,7 +5820,7 @@
         <v>1815413.0434782607</v>
       </c>
       <c r="K68" s="79">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>136899999.99500027</v>
       </c>
       <c r="L68" s="87">
@@ -4684,7 +5859,7 @@
         <v>56019.57</v>
       </c>
       <c r="Y68" s="82">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>1.0000000002037268E-2</v>
       </c>
       <c r="AF68" s="63"/>
@@ -4720,7 +5895,7 @@
         <v>2276706.5217391304</v>
       </c>
       <c r="K69" s="79">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>136899999.99500027</v>
       </c>
       <c r="L69" s="87">
@@ -4759,7 +5934,7 @@
         <v>56019.58</v>
       </c>
       <c r="Y69" s="82">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>1.0000000002037268E-2</v>
       </c>
       <c r="AF69" s="63"/>
@@ -4795,7 +5970,7 @@
         <v>2738000</v>
       </c>
       <c r="K70" s="79">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>136899999.99500027</v>
       </c>
       <c r="L70" s="87">
@@ -4834,7 +6009,7 @@
         <v>56019.59</v>
       </c>
       <c r="Y70" s="82">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>9.9999999947613105E-3</v>
       </c>
       <c r="AF70" s="63"/>
@@ -4870,7 +6045,7 @@
         <v>423558.01104972372</v>
       </c>
       <c r="K71" s="79">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>136899999.99500027</v>
       </c>
       <c r="L71" s="87">
@@ -4909,7 +6084,7 @@
         <v>56019.6</v>
       </c>
       <c r="Y71" s="82">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>1.0000000002037268E-2</v>
       </c>
       <c r="AF71" s="63"/>
@@ -4945,7 +6120,7 @@
         <v>892497.23756906076</v>
       </c>
       <c r="K72" s="79">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>136899999.99500027</v>
       </c>
       <c r="L72" s="87">
@@ -4984,7 +6159,7 @@
         <v>56019.62</v>
       </c>
       <c r="Y72" s="82">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>2.0000000004074536E-2</v>
       </c>
       <c r="AF72" s="63"/>
@@ -5020,7 +6195,7 @@
         <v>1346309.3922651934</v>
       </c>
       <c r="K73" s="79">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>136899999.99500027</v>
       </c>
       <c r="L73" s="87">
@@ -5059,7 +6234,7 @@
         <v>56019.63</v>
       </c>
       <c r="Y73" s="82">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>9.9999999947613105E-3</v>
       </c>
       <c r="AF73" s="63"/>
@@ -5095,7 +6270,7 @@
         <v>1815248.6187845303</v>
       </c>
       <c r="K74" s="79">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>136899999.99500027</v>
       </c>
       <c r="L74" s="87">
@@ -5134,7 +6309,7 @@
         <v>56019.64</v>
       </c>
       <c r="Y74" s="82">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>1.0000000002037268E-2</v>
       </c>
       <c r="AF74" s="63"/>
@@ -5170,14 +6345,14 @@
         <v>2269060.7734806631</v>
       </c>
       <c r="K75" s="79">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>136899999.99500027</v>
       </c>
       <c r="L75" s="87">
         <v>97.132788000000005</v>
       </c>
       <c r="M75" s="50">
-        <f t="shared" si="27"/>
+        <f>((($K$32*(L75-$L$32)/100)+($K$40*(L75-$L$40)/100))*$H$5/$H$4+($K$59*(L75-$L$59)/100))*$H$7/$H$6</f>
         <v>-3712228.8039686922</v>
       </c>
       <c r="N75" s="50">
@@ -5209,7 +6384,7 @@
         <v>56019.65</v>
       </c>
       <c r="Y75" s="82">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>1.0000000002037268E-2</v>
       </c>
       <c r="AF75" s="63"/>
@@ -5254,12 +6429,12 @@
         <v>100</v>
       </c>
       <c r="M76" s="50">
-        <f t="shared" si="27"/>
-        <v>212984.42389962959</v>
+        <f>O35</f>
+        <v>133071919.56</v>
       </c>
       <c r="N76" s="50">
-        <f t="shared" si="10"/>
-        <v>2.2796425328124315E-3</v>
+        <f>M76-H76-F76</f>
+        <v>132858935.13838002</v>
       </c>
       <c r="O76" s="50">
         <f t="shared" si="0"/>
@@ -5267,10 +6442,10 @@
       </c>
       <c r="P76" s="51">
         <f t="shared" si="28"/>
-        <v>-2.3126602172851563E-3</v>
+        <v>132858935.13378772</v>
       </c>
       <c r="Q76" s="88">
-        <f t="shared" si="24"/>
+        <f>A76-$A$60</f>
         <v>457</v>
       </c>
       <c r="R76" s="89"/>
@@ -5335,9 +6510,5801 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1"/>
+  <dimension ref="A1:V223"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData/>
+  <cols>
+    <col min="1" max="1" width="16.7109375" customWidth="1"/>
+    <col min="2" max="2" width="24.28515625" customWidth="1"/>
+    <col min="3" max="3" width="32.42578125" customWidth="1"/>
+    <col min="6" max="6" width="31.7109375" customWidth="1"/>
+    <col min="7" max="7" width="35" customWidth="1"/>
+    <col min="8" max="8" width="25.28515625" customWidth="1"/>
+    <col min="9" max="9" width="24.5703125" customWidth="1"/>
+    <col min="10" max="10" width="18.28515625" customWidth="1"/>
+    <col min="11" max="11" width="25.5703125" customWidth="1"/>
+    <col min="12" max="12" width="25" customWidth="1"/>
+    <col min="13" max="13" width="22.7109375" customWidth="1"/>
+    <col min="14" max="14" width="24.140625" customWidth="1"/>
+    <col min="15" max="15" width="14.85546875" customWidth="1"/>
+    <col min="16" max="16" width="17" customWidth="1"/>
+    <col min="19" max="19" width="13.140625" customWidth="1"/>
+    <col min="20" max="20" width="13.5703125" customWidth="1"/>
+    <col min="21" max="21" width="19.140625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:22" ht="23.25" x14ac:dyDescent="0.45">
+      <c r="A1" s="112" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="113" t="s">
+        <v>56</v>
+      </c>
+      <c r="F1" s="114" t="s">
+        <v>57</v>
+      </c>
+      <c r="J1" s="115" t="s">
+        <v>58</v>
+      </c>
+      <c r="K1" s="115"/>
+      <c r="L1" s="115"/>
+      <c r="M1" s="115"/>
+      <c r="N1" s="115"/>
+      <c r="O1" s="115"/>
+      <c r="P1" s="115"/>
+      <c r="Q1" s="115"/>
+      <c r="R1" s="115"/>
+      <c r="S1" s="115"/>
+      <c r="T1" s="115"/>
+      <c r="U1" s="115"/>
+      <c r="V1" s="115"/>
+    </row>
+    <row r="2" spans="1:22" ht="84" x14ac:dyDescent="0.35">
+      <c r="A2" s="112" t="s">
+        <v>2</v>
+      </c>
+      <c r="B2" s="116" t="s">
+        <v>59</v>
+      </c>
+      <c r="F2" s="14">
+        <v>46157</v>
+      </c>
+      <c r="J2" s="117" t="s">
+        <v>60</v>
+      </c>
+      <c r="K2" s="118" t="s">
+        <v>61</v>
+      </c>
+      <c r="L2" s="119" t="s">
+        <v>35</v>
+      </c>
+      <c r="M2" s="120" t="s">
+        <v>62</v>
+      </c>
+      <c r="N2" s="121" t="s">
+        <v>63</v>
+      </c>
+      <c r="O2" s="122" t="s">
+        <v>64</v>
+      </c>
+      <c r="P2" s="123" t="s">
+        <v>65</v>
+      </c>
+      <c r="Q2" s="124" t="s">
+        <v>66</v>
+      </c>
+      <c r="R2" s="124" t="s">
+        <v>67</v>
+      </c>
+      <c r="S2" s="125" t="s">
+        <v>68</v>
+      </c>
+      <c r="T2" s="126" t="s">
+        <v>69</v>
+      </c>
+      <c r="U2" s="127" t="s">
+        <v>70</v>
+      </c>
+      <c r="V2" s="128" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="3" spans="1:22" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A3" s="112" t="s">
+        <v>71</v>
+      </c>
+      <c r="B3" s="129">
+        <v>150000000</v>
+      </c>
+      <c r="C3" s="43"/>
+      <c r="F3" s="14">
+        <v>46341</v>
+      </c>
+      <c r="G3" s="14"/>
+      <c r="J3" s="130"/>
+      <c r="K3" s="131"/>
+      <c r="L3" s="132"/>
+      <c r="M3" s="133">
+        <f>IF(COUNTIF($J$3:$J$8,J3)=0,0,
+  _xlfn.LET(
+    _xlpm.t,J3,
+    _xlpm.nomRemaining,
+    MAX(0,
+      $B$3
+      + SUMIFS($K$3:$K$8,$J$3:$J$8,"&lt;="&amp;_xlpm.t)
+    ),
+    _xlpm.nomRemaining * ($B$5/100) / $B$8
+  )
+)</f>
+        <v>0</v>
+      </c>
+      <c r="N3" s="134"/>
+      <c r="O3" s="135">
+        <f>B13+SellTable1213614168132166915125[[#This Row],[Buy Discount ]]</f>
+        <v>0</v>
+      </c>
+      <c r="P3" s="136"/>
+      <c r="Q3" s="137">
+        <f t="shared" ref="Q3:Q4" si="0">IF(L3&gt;=100,((L3/100)-1)*K3,0)</f>
+        <v>0</v>
+      </c>
+      <c r="R3" s="138">
+        <f t="shared" ref="R3:R7" si="1">IF(OR(L3=0,L3&gt;=100,K3&lt;0),0,((L3/100)-1)*K3)</f>
+        <v>0</v>
+      </c>
+      <c r="S3" s="139">
+        <f>-SellTable1213614168132166915125[[#This Row],[Nominal Buy/Sell]]*SellTable1213614168132166915125[[#This Row],[Price]]/100</f>
+        <v>0</v>
+      </c>
+      <c r="T3" s="140" t="str">
+        <f t="shared" ref="T3:T7" si="2">IF($J3="","",
+  IF($K3&lt;=0,"",
+    _xlfn.LET(
+      _xlpm.t,       $J3,
+      _xlpm.nom,     $K3,
+      _xlpm.lastCpn, IFERROR(_xlfn.MAXIFS($F$2:$F$14,$F$2:$F$14,"&lt;="&amp;_xlpm.t),$B$10),
+      _xlpm.lastCpn2,IF(_xlpm.lastCpn=0,$B$10,_xlpm.lastCpn),
+      _xlpm.nextCpn, _xlfn.MINIFS($F$2:$F$14,$F$2:$F$14,"&gt;"&amp;_xlpm.t),
+      _xlpm.frac,    (_xlpm.t-_xlpm.lastCpn2)/(_xlpm.nextCpn-_xlpm.lastCpn2),
+      _xlpm.frac * (_xlpm.nom*$B$5/2/100)
+    )
+  )
+)</f>
+        <v/>
+      </c>
+      <c r="U3" s="141">
+        <f>$B$3+SUM($K$3:K3)</f>
+        <v>150000000</v>
+      </c>
+      <c r="V3" s="142" t="str" cm="1">
+        <f t="array" ref="V3">_xlfn.LET(
+  _xlpm.i,        ROW()-ROW($V$3)+1,
+  _xlpm.prev_wac, IF(_xlpm.i=1, $B$4, INDEX($V$3:$V$8, _xlpm.i-1)),
+  _xlpm.prev_nom, IF(_xlpm.i=1, $B$3, INDEX($U$3:$U$8, _xlpm.i-1)),
+  _xlpm.k,        INDEX($K$3:$K$8, _xlpm.i),
+  _xlpm.pr,       INDEX($L$3:$L$8, _xlpm.i),
+  _xlpm.d,        INDEX($J$3:$J$8, _xlpm.i),
+  IF(_xlpm.d="", "",
+    IF(_xlpm.k&gt;0, (_xlpm.prev_nom*_xlpm.prev_wac + _xlpm.k*_xlpm.pr)/(_xlpm.prev_nom+_xlpm.k), _xlpm.prev_wac))
+)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="4" spans="1:22" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A4" s="112" t="s">
+        <v>72</v>
+      </c>
+      <c r="B4" s="143">
+        <v>108.1015625</v>
+      </c>
+      <c r="F4" s="14">
+        <v>46522</v>
+      </c>
+      <c r="G4" s="14"/>
+      <c r="J4" s="130"/>
+      <c r="K4" s="131"/>
+      <c r="L4" s="144"/>
+      <c r="M4" s="133">
+        <f>IF(COUNTIF($J$3:$J$8,J4)=0,0,
+  _xlfn.LET(
+    _xlpm.t,J4,
+    _xlpm.nomRemaining,
+    MAX(0,
+      $B$3
+      + SUMIFS($K$3:$K$8,$J$3:$J$8,"&lt;="&amp;_xlpm.t)
+    ),
+    _xlpm.nomRemaining * ($B$5/100) / $B$8
+  )
+)</f>
+        <v>0</v>
+      </c>
+      <c r="N4" s="134"/>
+      <c r="O4" s="145">
+        <f>O3+SellTable1213614168132166915125[[#This Row],[Buy Discount ]]</f>
+        <v>0</v>
+      </c>
+      <c r="P4" s="136"/>
+      <c r="Q4" s="137">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="R4" s="138">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="S4" s="146">
+        <f>-SellTable1213614168132166915125[[#This Row],[Nominal Buy/Sell]]*SellTable1213614168132166915125[[#This Row],[Price]]/100</f>
+        <v>0</v>
+      </c>
+      <c r="T4" s="138" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="U4" s="137">
+        <f>$B$3+SUM($K$3:K4)</f>
+        <v>150000000</v>
+      </c>
+      <c r="V4" s="147" t="str" cm="1">
+        <f t="array" ref="V4">_xlfn.LET(
+  _xlpm.i,        ROW()-ROW($V$3)+1,
+  _xlpm.prev_wac, IF(_xlpm.i=1, $B$4, INDEX($V$3:$V$8, _xlpm.i-1)),
+  _xlpm.prev_nom, IF(_xlpm.i=1, $B$3, INDEX($U$3:$U$8, _xlpm.i-1)),
+  _xlpm.k,        INDEX($K$3:$K$8, _xlpm.i),
+  _xlpm.pr,       INDEX($L$3:$L$8, _xlpm.i),
+  _xlpm.d,        INDEX($J$3:$J$8, _xlpm.i),
+  IF(_xlpm.d="", "",
+    IF(_xlpm.k&gt;0, (_xlpm.prev_nom*_xlpm.prev_wac + _xlpm.k*_xlpm.pr)/(_xlpm.prev_nom+_xlpm.k), _xlpm.prev_wac))
+)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="5" spans="1:22" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A5" s="112" t="s">
+        <v>73</v>
+      </c>
+      <c r="B5" s="148">
+        <v>6.25</v>
+      </c>
+      <c r="D5" s="149"/>
+      <c r="F5" s="14">
+        <v>46706</v>
+      </c>
+      <c r="G5" s="14"/>
+      <c r="J5" s="130"/>
+      <c r="K5" s="131"/>
+      <c r="L5" s="144"/>
+      <c r="M5" s="133">
+        <f>IF(COUNTIF($J$3:$J$8,J5)=0,0,
+  _xlfn.LET(
+    _xlpm.t,J5,
+    _xlpm.nomRemaining,
+    MAX(0,
+      $B$3
+      + SUMIFS($K$3:$K$8,$J$3:$J$8,"&lt;="&amp;_xlpm.t)
+    ),
+    _xlpm.nomRemaining * ($B$5/100) / $B$8
+  )
+)</f>
+        <v>0</v>
+      </c>
+      <c r="N5" s="134"/>
+      <c r="O5" s="145">
+        <f>O4*SellTable1213614168132166915125[[#This Row],[Nominals]]/U4</f>
+        <v>0</v>
+      </c>
+      <c r="P5" s="136"/>
+      <c r="Q5" s="137">
+        <f>IF(L5&gt;=100,((L5/100)-1)*K5,0)</f>
+        <v>0</v>
+      </c>
+      <c r="R5" s="138">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="S5" s="146">
+        <f>-SellTable1213614168132166915125[[#This Row],[Nominal Buy/Sell]]*SellTable1213614168132166915125[[#This Row],[Price]]/100</f>
+        <v>0</v>
+      </c>
+      <c r="T5" s="138" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="U5" s="137">
+        <f>$B$3+SUM($K$3:K5)</f>
+        <v>150000000</v>
+      </c>
+      <c r="V5" s="147" t="str" cm="1">
+        <f t="array" ref="V5">_xlfn.LET(
+  _xlpm.i,        ROW()-ROW($V$3)+1,
+  _xlpm.prev_wac, IF(_xlpm.i=1, $B$4, INDEX($V$3:$V$8, _xlpm.i-1)),
+  _xlpm.prev_nom, IF(_xlpm.i=1, $B$3, INDEX($U$3:$U$8, _xlpm.i-1)),
+  _xlpm.k,        INDEX($K$3:$K$8, _xlpm.i),
+  _xlpm.pr,       INDEX($L$3:$L$8, _xlpm.i),
+  _xlpm.d,        INDEX($J$3:$J$8, _xlpm.i),
+  IF(_xlpm.d="", "",
+    IF(_xlpm.k&gt;0, (_xlpm.prev_nom*_xlpm.prev_wac + _xlpm.k*_xlpm.pr)/(_xlpm.prev_nom+_xlpm.k), _xlpm.prev_wac))
+)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="6" spans="1:22" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A6" s="112" t="s">
+        <v>11</v>
+      </c>
+      <c r="B6" s="150">
+        <f>B3*B5/2/100</f>
+        <v>4687500</v>
+      </c>
+      <c r="D6" s="151"/>
+      <c r="F6" s="14">
+        <v>46888</v>
+      </c>
+      <c r="G6" s="14"/>
+      <c r="J6" s="130"/>
+      <c r="K6" s="131"/>
+      <c r="L6" s="144"/>
+      <c r="M6" s="133">
+        <f>IF(COUNTIF($J$3:$J$8,J6)=0,0,
+  _xlfn.LET(
+    _xlpm.t,J6,
+    _xlpm.nomRemaining,
+    MAX(0,
+      $B$3
+      + SUMIFS($K$3:$K$8,$J$3:$J$8,"&lt;="&amp;_xlpm.t)
+    ),
+    _xlpm.nomRemaining * ($B$5/100) / $B$8
+  )
+)</f>
+        <v>0</v>
+      </c>
+      <c r="N6" s="134"/>
+      <c r="O6" s="145">
+        <f>O5*SellTable1213614168132166915125[[#This Row],[Nominals]]/U5</f>
+        <v>0</v>
+      </c>
+      <c r="P6" s="136"/>
+      <c r="Q6" s="137">
+        <f t="shared" ref="Q6:Q7" si="3">IF(L6&gt;=100,((L6/100)-1)*K6,0)</f>
+        <v>0</v>
+      </c>
+      <c r="R6" s="137">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="S6" s="146">
+        <f>-SellTable1213614168132166915125[[#This Row],[Nominal Buy/Sell]]*SellTable1213614168132166915125[[#This Row],[Price]]/100</f>
+        <v>0</v>
+      </c>
+      <c r="T6" s="138" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="U6" s="137">
+        <f>$B$3+SUM($K$3:K6)</f>
+        <v>150000000</v>
+      </c>
+      <c r="V6" s="147" t="str" cm="1">
+        <f t="array" ref="V6">_xlfn.LET(
+  _xlpm.i,        ROW()-ROW($V$3)+1,
+  _xlpm.prev_wac, IF(_xlpm.i=1, $B$4, INDEX($V$3:$V$8, _xlpm.i-1)),
+  _xlpm.prev_nom, IF(_xlpm.i=1, $B$3, INDEX($U$3:$U$8, _xlpm.i-1)),
+  _xlpm.k,        INDEX($K$3:$K$8, _xlpm.i),
+  _xlpm.pr,       INDEX($L$3:$L$8, _xlpm.i),
+  _xlpm.d,        INDEX($J$3:$J$8, _xlpm.i),
+  IF(_xlpm.d="", "",
+    IF(_xlpm.k&gt;0, (_xlpm.prev_nom*_xlpm.prev_wac + _xlpm.k*_xlpm.pr)/(_xlpm.prev_nom+_xlpm.k), _xlpm.prev_wac))
+)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7" spans="1:22" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A7" s="112" t="s">
+        <v>12</v>
+      </c>
+      <c r="B7" s="152">
+        <f>(B9-B10)/(B11-B10)*B6</f>
+        <v>4661602.2099447511</v>
+      </c>
+      <c r="D7" s="5"/>
+      <c r="F7" s="14">
+        <v>47072</v>
+      </c>
+      <c r="G7" s="14"/>
+      <c r="J7" s="153"/>
+      <c r="K7" s="154"/>
+      <c r="L7" s="155"/>
+      <c r="M7" s="156">
+        <f>IF(COUNTIF($J$3:$J$8,J7)=0,0,
+  _xlfn.LET(
+    _xlpm.t,J7,
+    _xlpm.nomRemaining,
+    MAX(0,
+      $B$3
+      + SUMIFS($K$3:$K$8,$J$3:$J$8,"&lt;="&amp;_xlpm.t)
+    ),
+    _xlpm.nomRemaining * ($B$5/100) / $B$8
+  )
+)</f>
+        <v>0</v>
+      </c>
+      <c r="N7" s="157"/>
+      <c r="O7" s="158">
+        <f>O6+SellTable1213614168132166915125[[#This Row],[Buy Discount ]]</f>
+        <v>0</v>
+      </c>
+      <c r="P7" s="159"/>
+      <c r="Q7" s="160">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="R7" s="160">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="S7" s="161">
+        <f>-SellTable1213614168132166915125[[#This Row],[Nominal Buy/Sell]]*SellTable1213614168132166915125[[#This Row],[Price]]/100</f>
+        <v>0</v>
+      </c>
+      <c r="T7" s="162" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="U7" s="160">
+        <f>$B$3+SUM($K$3:K7)</f>
+        <v>150000000</v>
+      </c>
+      <c r="V7" s="163" t="str" cm="1">
+        <f t="array" ref="V7">_xlfn.LET(
+  _xlpm.i,        ROW()-ROW($V$3)+1,
+  _xlpm.prev_wac, IF(_xlpm.i=1, $B$4, INDEX($V$3:$V$8, _xlpm.i-1)),
+  _xlpm.prev_nom, IF(_xlpm.i=1, $B$3, INDEX($U$3:$U$8, _xlpm.i-1)),
+  _xlpm.k,        INDEX($K$3:$K$8, _xlpm.i),
+  _xlpm.pr,       INDEX($L$3:$L$8, _xlpm.i),
+  _xlpm.d,        INDEX($J$3:$J$8, _xlpm.i),
+  IF(_xlpm.d="", "",
+    IF(_xlpm.k&gt;0, (_xlpm.prev_nom*_xlpm.prev_wac + _xlpm.k*_xlpm.pr)/(_xlpm.prev_nom+_xlpm.k), _xlpm.prev_wac))
+)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8" spans="1:22" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A8" s="112" t="s">
+        <v>74</v>
+      </c>
+      <c r="B8" s="116">
+        <v>2</v>
+      </c>
+      <c r="F8" s="14">
+        <v>47253</v>
+      </c>
+      <c r="G8" s="14"/>
+      <c r="J8" s="164"/>
+      <c r="K8" s="165"/>
+      <c r="L8" s="166"/>
+      <c r="M8" s="167"/>
+      <c r="N8" s="168"/>
+      <c r="O8" s="169"/>
+      <c r="P8" s="43"/>
+      <c r="Q8" s="43"/>
+      <c r="R8" s="43"/>
+      <c r="S8" s="43"/>
+      <c r="T8" s="43"/>
+      <c r="U8" s="43"/>
+    </row>
+    <row r="9" spans="1:22" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A9" s="112" t="s">
+        <v>14</v>
+      </c>
+      <c r="B9" s="170">
+        <v>46156</v>
+      </c>
+      <c r="F9" s="14">
+        <v>47437</v>
+      </c>
+      <c r="G9" s="14"/>
+      <c r="K9" s="171"/>
+      <c r="L9" s="172"/>
+      <c r="M9" s="173"/>
+      <c r="O9" s="65"/>
+    </row>
+    <row r="10" spans="1:22" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A10" s="112" t="s">
+        <v>15</v>
+      </c>
+      <c r="B10" s="174">
+        <f>IF(DAY(F2)=DAY(EOMONTH(F2,0)),
+EOMONTH(F2,-12/$B$8),
+EDATE(F2,-12/$B$8)
+)</f>
+        <v>45976</v>
+      </c>
+      <c r="C10" s="175"/>
+      <c r="D10" s="172"/>
+      <c r="F10" s="14">
+        <v>47618</v>
+      </c>
+      <c r="G10" s="14"/>
+      <c r="L10" s="176"/>
+      <c r="N10" s="176"/>
+      <c r="O10" s="169"/>
+      <c r="P10" s="171"/>
+      <c r="Q10" s="43"/>
+    </row>
+    <row r="11" spans="1:22" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A11" s="112" t="s">
+        <v>17</v>
+      </c>
+      <c r="B11" s="174">
+        <f>F2</f>
+        <v>46157</v>
+      </c>
+      <c r="F11" s="14"/>
+      <c r="G11" s="14"/>
+      <c r="J11" s="65"/>
+      <c r="K11" s="176"/>
+      <c r="L11" s="176"/>
+      <c r="N11" s="176"/>
+      <c r="P11" s="43"/>
+      <c r="Q11" s="43"/>
+      <c r="S11" s="177" t="s">
+        <v>75</v>
+      </c>
+      <c r="T11" s="178">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:22" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A12" s="112" t="s">
+        <v>76</v>
+      </c>
+      <c r="B12" s="170">
+        <f>F10</f>
+        <v>47618</v>
+      </c>
+      <c r="F12" s="14"/>
+      <c r="G12" s="14"/>
+      <c r="H12" s="59"/>
+      <c r="J12" s="65"/>
+      <c r="K12" s="176"/>
+      <c r="L12" s="176"/>
+      <c r="N12" s="176"/>
+      <c r="S12" s="177" t="s">
+        <v>77</v>
+      </c>
+      <c r="T12" s="178">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="13" spans="1:22" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A13" s="112" t="s">
+        <v>20</v>
+      </c>
+      <c r="B13" s="179">
+        <f>IF(B4&lt;100,(($B$4/100)-1)*$B$3,0)</f>
+        <v>0</v>
+      </c>
+      <c r="H13" s="65"/>
+      <c r="J13" s="180" t="s">
+        <v>78</v>
+      </c>
+      <c r="M13" s="65"/>
+      <c r="N13" s="65"/>
+      <c r="P13" s="181"/>
+      <c r="Q13" s="176"/>
+      <c r="S13" s="177" t="s">
+        <v>6</v>
+      </c>
+      <c r="T13" s="178">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="14" spans="1:22" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A14" s="112" t="s">
+        <v>79</v>
+      </c>
+      <c r="B14" s="182">
+        <f>IF(B4&gt;=100,(($B$4/100)-1)*$B$3,0)</f>
+        <v>12152343.750000006</v>
+      </c>
+      <c r="D14" s="183"/>
+      <c r="E14" s="176"/>
+      <c r="F14" s="184"/>
+      <c r="H14" s="65"/>
+      <c r="J14" s="185" t="s">
+        <v>80</v>
+      </c>
+      <c r="K14" s="176"/>
+      <c r="L14" s="186"/>
+      <c r="M14" s="65"/>
+      <c r="N14" s="65"/>
+      <c r="O14" s="43"/>
+    </row>
+    <row r="15" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A15" s="187"/>
+      <c r="F15" s="188"/>
+      <c r="J15" s="189" t="s">
+        <v>57</v>
+      </c>
+      <c r="L15" s="176"/>
+      <c r="M15" s="65"/>
+      <c r="N15" s="65"/>
+    </row>
+    <row r="16" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A16" s="187"/>
+      <c r="E16" s="190"/>
+      <c r="F16" s="184"/>
+    </row>
+    <row r="17" spans="1:22" ht="89.25" x14ac:dyDescent="0.25">
+      <c r="A17" s="191" t="s">
+        <v>26</v>
+      </c>
+      <c r="B17" s="192" t="s">
+        <v>27</v>
+      </c>
+      <c r="C17" s="192" t="s">
+        <v>28</v>
+      </c>
+      <c r="D17" s="191" t="s">
+        <v>29</v>
+      </c>
+      <c r="E17" s="191" t="s">
+        <v>30</v>
+      </c>
+      <c r="F17" s="193" t="s">
+        <v>31</v>
+      </c>
+      <c r="G17" s="191" t="s">
+        <v>32</v>
+      </c>
+      <c r="H17" s="193" t="s">
+        <v>33</v>
+      </c>
+      <c r="I17" s="193" t="s">
+        <v>81</v>
+      </c>
+      <c r="J17" s="193" t="s">
+        <v>34</v>
+      </c>
+      <c r="K17" s="193" t="s">
+        <v>12</v>
+      </c>
+      <c r="L17" s="193" t="s">
+        <v>28</v>
+      </c>
+      <c r="M17" s="193" t="s">
+        <v>35</v>
+      </c>
+      <c r="N17" s="193" t="s">
+        <v>36</v>
+      </c>
+      <c r="O17" s="193" t="s">
+        <v>37</v>
+      </c>
+      <c r="P17" s="193" t="s">
+        <v>38</v>
+      </c>
+      <c r="Q17" s="193" t="s">
+        <v>39</v>
+      </c>
+      <c r="R17" s="193" t="s">
+        <v>40</v>
+      </c>
+      <c r="S17" s="193" t="s">
+        <v>82</v>
+      </c>
+      <c r="T17" s="193" t="s">
+        <v>42</v>
+      </c>
+      <c r="U17" s="193" t="s">
+        <v>43</v>
+      </c>
+      <c r="V17" s="194" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="18" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A18" s="195"/>
+      <c r="B18" s="76">
+        <f>-B4*B3/100</f>
+        <v>-162152343.75</v>
+      </c>
+      <c r="C18" s="76">
+        <f>B3</f>
+        <v>150000000</v>
+      </c>
+      <c r="D18" s="196">
+        <f>A18-$A$18</f>
+        <v>0</v>
+      </c>
+      <c r="E18" s="197">
+        <f>+B13</f>
+        <v>0</v>
+      </c>
+      <c r="F18" s="79"/>
+      <c r="G18" s="78">
+        <f>+B14</f>
+        <v>12152343.750000006</v>
+      </c>
+      <c r="H18" s="79"/>
+      <c r="I18" s="79"/>
+      <c r="J18" s="198">
+        <f>+B3+G18+E18</f>
+        <v>162152343.75</v>
+      </c>
+      <c r="K18" s="79">
+        <f>B7</f>
+        <v>4661602.2099447511</v>
+      </c>
+      <c r="L18" s="79">
+        <f>J18-G18-E18</f>
+        <v>150000000</v>
+      </c>
+      <c r="M18" s="199">
+        <f>B4</f>
+        <v>108.1015625</v>
+      </c>
+      <c r="N18" s="78"/>
+      <c r="O18" s="78"/>
+      <c r="P18" s="200">
+        <f>ROUND(L18*M18/100,2)</f>
+        <v>162152343.75</v>
+      </c>
+      <c r="Q18" s="148"/>
+      <c r="R18" s="41"/>
+      <c r="S18" s="41"/>
+      <c r="T18" s="41"/>
+      <c r="U18" s="201"/>
+      <c r="V18" s="41"/>
+    </row>
+    <row r="19" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A19" s="195">
+        <f>B9</f>
+        <v>46156</v>
+      </c>
+      <c r="B19" s="76">
+        <f>+B18</f>
+        <v>-162152343.75</v>
+      </c>
+      <c r="C19" s="76">
+        <f>+C18</f>
+        <v>150000000</v>
+      </c>
+      <c r="D19" s="196">
+        <v>0</v>
+      </c>
+      <c r="E19" s="197">
+        <f>E18</f>
+        <v>0</v>
+      </c>
+      <c r="F19" s="79"/>
+      <c r="G19" s="78">
+        <f>G18</f>
+        <v>12152343.750000006</v>
+      </c>
+      <c r="H19" s="79">
+        <f>0</f>
+        <v>0</v>
+      </c>
+      <c r="I19" s="79"/>
+      <c r="J19" s="198">
+        <f>+$J$18+H19+F19</f>
+        <v>162152343.75</v>
+      </c>
+      <c r="K19" s="79">
+        <f>B7</f>
+        <v>4661602.2099447511</v>
+      </c>
+      <c r="L19" s="79">
+        <f>J19-G19-E19</f>
+        <v>150000000</v>
+      </c>
+      <c r="M19" s="199">
+        <f>M18</f>
+        <v>108.1015625</v>
+      </c>
+      <c r="N19" s="78"/>
+      <c r="O19" s="78"/>
+      <c r="P19" s="200">
+        <f>L19*M19/100</f>
+        <v>162152343.75</v>
+      </c>
+      <c r="Q19" s="78"/>
+      <c r="R19" s="41"/>
+      <c r="S19" s="41"/>
+      <c r="T19" s="41"/>
+      <c r="U19" s="201"/>
+      <c r="V19" s="41"/>
+    </row>
+    <row r="20" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A20" s="202" cm="1">
+        <f t="array" ref="A20:A76">_xlfn.LET(
+  _xlpm.settle,$A$19,
+  _xlpm.maturity,$B$12,
+  _xlpm.firstMonthEnd,EOMONTH(_xlpm.settle,0),
+  _xlpm.months,EDATE(_xlpm.firstMonthEnd,_xlfn.SEQUENCE(200,1,0,1)),
+  _xlpm.sellDates,$J$3:$J$8,
+  _xlpm.sellType,$N$3:$N$8,
+  _xlpm.fullSellDates,_xlfn._xlws.FILTER(_xlpm.sellDates,_xlpm.sellType=1),
+  _xlpm.all,_xlfn.VSTACK(_xlpm.months,$F$2:$F$12,$J$3:$J$8,_xlpm.maturity),
+  _xlpm.sorted,_xlfn._xlws.SORT(_xlfn.UNIQUE(_xlpm.all)),
+  _xlpm.fullSellDate,IFERROR(MIN(_xlpm.fullSellDates),""),
+  _xlpm.endDate,IF(_xlpm.fullSellDate="",_xlpm.maturity,_xlpm.fullSellDate),
+  _xlfn._xlws.FILTER(_xlpm.sorted,(_xlpm.sorted&gt;=_xlpm.settle)*(_xlpm.sorted&lt;=_xlpm.endDate))
+)</f>
+        <v>46157</v>
+      </c>
+      <c r="B20" s="183" cm="1">
+        <f t="array" ref="B20:B76">_xlfn.MAP(_xlfn.ANCHORARRAY(A20),_xlfn.LAMBDA(_xlpm.t,
+  _xlfn.LET(
+    _xlpm.txCF,       IFERROR(_xlfn.XLOOKUP(_xlpm.t,$J$3:$J$8,$S$3:$S$8),0),
+    _xlpm.isMaturity, _xlpm.t=$B$12,
+    _xlpm.last_tx,    IFERROR(_xlfn.MAXIFS($J$3:$J$8,$J$3:$J$8,"&lt;="&amp;_xlpm.t),0),
+    _xlpm.nom,        IF(_xlpm.last_tx=0,$B$3,_xlfn.XLOOKUP(_xlpm.last_tx,$J$3:$J$8,$U$3:$U$8)),
+    _xlpm.matCF,      IF(_xlpm.isMaturity,_xlpm.nom,0),
+    _xlpm.txCF + _xlpm.matCF
+  )
+))</f>
+        <v>0</v>
+      </c>
+      <c r="C20" s="203"/>
+      <c r="D20" s="196" cm="1">
+        <f t="array" ref="D20:D76">_xlfn.MAP(_xlfn.ANCHORARRAY(A20),_xlfn.LAMBDA(_xlpm.t,
+_xlpm.t-$A$19
+))</f>
+        <v>1</v>
+      </c>
+      <c r="E20" s="205" cm="1">
+        <f t="array" ref="E20:E76">_xlfn.MAP(_xlfn.ANCHORARRAY(A20),_xlfn.ANCHORARRAY(F20),_xlfn.LAMBDA(_xlpm.t,_xlpm.f,
+  _xlfn.LET(
+    _xlpm.isMonthEnd, _xlpm.t=EOMONTH(_xlpm.t,0),
+    _xlpm.isBuy,      (COUNTIF($J$3:$J$8,_xlpm.t)&gt;0)*(IFERROR(_xlfn.XLOOKUP(_xlpm.t,$J$3:$J$8,$K$3:$K$8,0),0)&gt;0),
+    _xlpm.last_tx,    IFERROR(_xlfn.MAXIFS($J$3:$J$8,$J$3:$J$8,"&lt;="&amp;_xlpm.t),0),
+    _xlpm.base_curr,  IF(_xlpm.last_tx=0,$B$13,_xlfn.XLOOKUP(_xlpm.last_tx,$J$3:$J$8,$O$3:$O$8)),
+    IF(AND(_xlpm.isBuy,NOT(_xlpm.isMonthEnd)),"",
+      _xlpm.base_curr + _xlpm.f
+    )
+  )
+))</f>
+        <v>0</v>
+      </c>
+      <c r="F20" s="79" cm="1">
+        <f t="array" ref="F20:F76">_xlfn.MAP(_xlfn.ANCHORARRAY(A20),_xlfn.LAMBDA(_xlpm.t,
+  _xlfn.LET(
+    _xlpm.buyMask,    ($J$3:$J$8&lt;&gt;"")*($K$3:$K$8&gt;0),
+    _xlpm.sellMask,   ($J$3:$J$8&lt;&gt;"")*($K$3:$K$8&lt;0),
+    _xlpm.bDates,     _xlfn.VSTACK($A$19, _xlfn._xlws.FILTER($J$3:$J$8, _xlpm.buyMask, $B$12+1)),
+    _xlpm.bDiscs,     _xlfn.VSTACK(ABS($B$13), _xlfn._xlws.FILTER(ABS($R$3:$R$8), _xlpm.buyMask, 0)),
+    _xlpm.sDates,     _xlfn._xlws.FILTER($J$3:$J$8, _xlpm.sellMask, 0),
+    _xlpm.sRatios,    _xlfn._xlws.FILTER(IFERROR($U$3:$U$8/_xlfn.VSTACK($B$3,$U$3:$U$7),1), _xlpm.sellMask, 1),
+    _xlpm.contributions, _xlfn.MAP(_xlpm.bDates, _xlpm.bDiscs, _xlfn.LAMBDA(_xlpm.bd,_xlpm.dsc,
+      IF((_xlpm.bd&gt;_xlpm.t)+(_xlpm.dsc=0), 0,
+        (_xlpm.dsc*(_xlpm.t-_xlpm.bd)/($B$12-_xlpm.bd))
+        * PRODUCT(IF((_xlpm.sDates&gt;_xlpm.bd)*(_xlpm.sDates&lt;_xlpm.t), _xlpm.sRatios, 1))
+      )
+    )),
+    SUM(_xlpm.contributions)
+  )
+))</f>
+        <v>0</v>
+      </c>
+      <c r="G20" s="78" cm="1">
+        <f t="array" ref="G20:G76">_xlfn.MAP(_xlfn.ANCHORARRAY(A20),_xlfn.ANCHORARRAY(H20),_xlfn.LAMBDA(_xlpm.t,_xlpm.h,
+  _xlfn.LET(
+    _xlpm.isMonthEnd, _xlpm.t=EOMONTH(_xlpm.t,0),
+    _xlpm.isBuy,      (COUNTIF($J$3:$J$8,_xlpm.t)&gt;0)*(IFERROR(_xlfn.XLOOKUP(_xlpm.t,$J$3:$J$8,$K$3:$K$8,0),0)&gt;0),
+    _xlpm.last_tx,    IFERROR(_xlfn.MAXIFS($J$3:$J$8,$J$3:$J$8,"&lt;="&amp;_xlpm.t),0),
+    _xlpm.base_curr,  IF(_xlpm.last_tx=0,$B$14,_xlfn.XLOOKUP(_xlpm.last_tx,$J$3:$J$8,$P$3:$P$8)),
+    IF(AND(_xlpm.isBuy,NOT(_xlpm.isMonthEnd)),"",
+      _xlpm.base_curr + _xlpm.h
+    )
+  )
+))</f>
+        <v>12144031.613372099</v>
+      </c>
+      <c r="H20" s="79" cm="1">
+        <f t="array" ref="H20:H76">-_xlfn.MAP(_xlfn.ANCHORARRAY(A20),_xlfn.LAMBDA(_xlpm.t,
+  _xlfn.LET(
+    _xlpm.buyMask,    ($J$3:$J$8&lt;&gt;"")*($K$3:$K$8&gt;0),
+    _xlpm.sellMask,   ($J$3:$J$8&lt;&gt;"")*($K$3:$K$8&lt;0),
+    _xlpm.bDates,     _xlfn.VSTACK($A$19, _xlfn._xlws.FILTER($J$3:$J$8, _xlpm.buyMask, $B$12+1)),
+    _xlpm.bPrems,     _xlfn.VSTACK(ABS($B$14), _xlfn._xlws.FILTER(ABS($Q$3:$Q$8), _xlpm.buyMask, 0)),
+    _xlpm.sDates,     _xlfn._xlws.FILTER($J$3:$J$8, _xlpm.sellMask, 0),
+    _xlpm.sRatios,    _xlfn._xlws.FILTER(IFERROR($U$3:$U$8/_xlfn.VSTACK($B$3,$U$3:$U$7),1), _xlpm.sellMask, 1),
+    _xlpm.contributions, _xlfn.MAP(_xlpm.bDates, _xlpm.bPrems, _xlfn.LAMBDA(_xlpm.bd,_xlpm.prm,
+      IF((_xlpm.bd&gt;_xlpm.t)+(_xlpm.prm=0), 0,
+        (_xlpm.prm*(_xlpm.t-_xlpm.bd)/($B$12-_xlpm.bd))
+        * PRODUCT(IF((_xlpm.sDates&gt;_xlpm.bd)*(_xlpm.sDates&lt;_xlpm.t), _xlpm.sRatios, 1))
+      )
+    )),
+    SUM(_xlpm.contributions)
+  )
+))</f>
+        <v>-8312.1366279069807</v>
+      </c>
+      <c r="I20" s="79" t="str" cm="1">
+        <f t="array" ref="I20:I76">_xlfn.MAP(_xlfn.ANCHORARRAY(A20),_xlfn.ANCHORARRAY(H20),_xlfn.ANCHORARRAY(F20),_xlfn.LAMBDA(_xlpm.t,_xlpm.h,_xlpm.f,
+  _xlfn.LET(
+    _xlpm.isTrans,  COUNTIF($J$3:$J$8,_xlpm.t)&gt;0,
+    _xlpm.jnum,     IF(ISNUMBER($J$3:$J$8),$J$3:$J$8,0),
+    _xlpm.knum,     IF(ISNUMBER($K$3:$K$8),$K$3:$K$8,0),
+    _xlpm.snum,     IF(ISNUMBER($S$3:$S$8),$S$3:$S$8,0),
+    _xlpm.vnum,     IF(ISNUMBER($V$3:$V$8),$V$3:$V$8,0),
+    _xlpm.buy_cf,   SUMPRODUCT((_xlpm.jnum&lt;_xlpm.t)*(_xlpm.jnum&lt;&gt;0)*(_xlpm.knum&gt;0)*_xlpm.snum),
+    _xlpm.sell_cv,  SUMPRODUCT((_xlpm.jnum&lt;_xlpm.t)*(_xlpm.jnum&lt;&gt;0)*(_xlpm.knum&lt;0)*ABS(_xlpm.knum)*_xlpm.vnum/100),
+    IF(_xlpm.isTrans, $J$18 + _xlpm.h + _xlpm.f - _xlpm.buy_cf - _xlpm.sell_cv, "")
+  )
+))</f>
+        <v/>
+      </c>
+      <c r="J20" s="198" cm="1">
+        <f t="array" ref="J20:J76">_xlfn.MAP(_xlfn.ANCHORARRAY(A20),_xlfn.ANCHORARRAY(H20),_xlfn.ANCHORARRAY(F20),_xlfn.LAMBDA(_xlpm.t,_xlpm.h,_xlpm.f,
+  _xlfn.LET(
+    _xlpm.isMonthEnd, _xlpm.t=EOMONTH(_xlpm.t,0),
+    _xlpm.isTrans,    COUNTIF($J$3:$J$8,_xlpm.t)&gt;0,
+    _xlpm.jnum,       IF(ISNUMBER($J$3:$J$8),$J$3:$J$8,0),
+    _xlpm.knum,       IF(ISNUMBER($K$3:$K$8),$K$3:$K$8,0),
+    _xlpm.snum,       IF(ISNUMBER($S$3:$S$8),$S$3:$S$8,0),
+    _xlpm.vnum,       IF(ISNUMBER($V$3:$V$8),$V$3:$V$8,0),
+    _xlpm.buy_cf,     SUMPRODUCT((_xlpm.jnum&lt;=_xlpm.t)*(_xlpm.jnum&lt;&gt;0)*(_xlpm.knum&gt;0)*_xlpm.snum),
+    _xlpm.sell_cv,    SUMPRODUCT((_xlpm.jnum&lt;=_xlpm.t)*(_xlpm.jnum&lt;&gt;0)*(_xlpm.knum&lt;0)*ABS(_xlpm.knum)*_xlpm.vnum/100),
+    IF(AND(_xlpm.isTrans,NOT(_xlpm.isMonthEnd)),0,
+      $J$18 + _xlpm.h + _xlpm.f - _xlpm.buy_cf - _xlpm.sell_cv
+    )
+  )
+))</f>
+        <v>162144031.61337209</v>
+      </c>
+      <c r="K20" s="79" cm="1">
+        <f t="array" ref="K20:K76">_xlfn.MAP(_xlfn.ANCHORARRAY(A20),_xlfn.LAMBDA(_xlpm.t,
+  IF(_xlpm.t&gt;$B$12,"",
+    _xlfn.LET(
+      _xlpm.isMonthEnd, _xlpm.t=EOMONTH(_xlpm.t,0),
+      _xlpm.isBuy,      (COUNTIF($J$3:$J$8,_xlpm.t)&gt;0)*(IFERROR(_xlfn.XLOOKUP(_xlpm.t,$J$3:$J$8,$K$3:$K$8,0),0)&gt;0),
+      _xlpm.last_buy,   IFERROR(_xlfn.MAXIFS($J$3:$J$8,$J$3:$J$8,"&lt;="&amp;_xlpm.t,$K$3:$K$8,"&gt;0"),0),
+      _xlpm.last_sell,  IFERROR(_xlfn.MAXIFS($J$3:$J$8,$J$3:$J$8,"&lt;"&amp;_xlpm.t,$K$3:$K$8,"&lt;0"),0),
+      _xlpm.last_tx,    MAX(_xlpm.last_buy,_xlpm.last_sell),
+      _xlpm.coupon,     IF(_xlpm.last_tx=0, $B$3*($B$5/100)/$B$8, _xlfn.XLOOKUP(_xlpm.last_tx,$J$3:$J$8,$M$3:$M$8)),
+      _xlpm.accrued,    IF(
+                    _xlpm.t&lt;MIN($F$2:$F$12),
+                    _xlpm.coupon*(_xlpm.t-$B$10)/(MIN($F$2:$F$12)-$B$10),
+                    IF(
+                      COUNTIF($F$2:$F$12,_xlpm.t)&gt;0,
+                      _xlpm.coupon,
+                      _xlfn.LET(
+                        _xlpm.prev, IFERROR(LOOKUP(_xlpm.t,$F$2:$F$12),$B$10),
+                        _xlpm.next, IFERROR(MIN(_xlfn._xlws.FILTER($F$2:$F$12,$F$2:$F$12&gt;_xlpm.t)),$B$12),
+                        _xlpm.coupon*(_xlpm.t-_xlpm.prev)/(_xlpm.next-_xlpm.prev)
+                      )
+                    )
+                  ),
+      IF(AND(_xlpm.isBuy,NOT(_xlpm.isMonthEnd)),"",_xlpm.accrued)
+    )
+  )
+))</f>
+        <v>4687500</v>
+      </c>
+      <c r="L20" s="79" cm="1">
+        <f t="array" ref="L20:L76">_xlfn.MAP(_xlfn.ANCHORARRAY(A20),_xlfn.LAMBDA(_xlpm.t,
+  _xlfn.LET(
+    _xlpm.isMonthEnd, _xlpm.t=EOMONTH(_xlpm.t,0),
+    _xlpm.isBuy,      (COUNTIF($J$3:$J$8,_xlpm.t)&gt;0)*(IFERROR(_xlfn.XLOOKUP(_xlpm.t,$J$3:$J$8,$K$3:$K$8,0),0)&gt;0),
+    _xlpm.val,        INDEX(_xlfn.ANCHORARRAY(J20),MATCH(_xlpm.t,_xlfn.ANCHORARRAY(A20),0))
+                - INDEX(_xlfn.ANCHORARRAY(G20),MATCH(_xlpm.t,_xlfn.ANCHORARRAY(A20),0))
+                - INDEX(_xlfn.ANCHORARRAY(E20),MATCH(_xlpm.t,_xlfn.ANCHORARRAY(A20),0)),
+    IF(AND(_xlpm.isBuy,NOT(_xlpm.isMonthEnd)),"",_xlpm.val)
+  )
+))</f>
+        <v>150000000</v>
+      </c>
+      <c r="M20" s="199">
+        <f>M19</f>
+        <v>108.1015625</v>
+      </c>
+      <c r="N20" s="78" cm="1">
+        <f t="array" ref="N20:N76">_xlfn.MAP(_xlfn.ANCHORARRAY(A20),_xlfn.LAMBDA(_xlpm.t,
+  _xlfn.LET(
+    _xlpm.p,        IFERROR(INDEX(M20:M100,MATCH(_xlpm.t,_xlfn.ANCHORARRAY(A20),0)),0),
+    _xlpm.buyMask,  ($J$3:$J$8&lt;&gt;"")*($K$3:$K$8&gt;0),
+    _xlpm.sellMask, ($J$3:$J$8&lt;&gt;"")*($K$3:$K$8&lt;0),
+    _xlpm.bDates,   _xlfn.VSTACK($A$19, _xlfn._xlws.FILTER($J$3:$J$8, _xlpm.buyMask, $B$12+1)),
+    _xlpm.bNoms,    _xlfn.VSTACK($B$3,  _xlfn._xlws.FILTER($K$3:$K$8, _xlpm.buyMask, 0)),
+    _xlpm.bPrices,  _xlfn.VSTACK($M$18, _xlfn._xlws.FILTER($L$3:$L$8, _xlpm.buyMask, 0)),
+    _xlpm.sDates,   _xlfn._xlws.FILTER($J$3:$J$8, _xlpm.sellMask, 0),
+    _xlpm.sRatios,  _xlfn._xlws.FILTER(IFERROR($U$3:$U$8/_xlfn.VSTACK($B$3,$U$3:$U$7),1), _xlpm.sellMask, 1),
+    _xlpm.contributions, _xlfn.MAP(_xlpm.bDates, _xlpm.bNoms, _xlpm.bPrices, _xlfn.LAMBDA(_xlpm.bd,_xlpm.nm,_xlpm.pr,
+      IF((_xlpm.bd&gt;_xlpm.t)+(_xlpm.nm=0), 0,
+        (_xlpm.nm*(_xlpm.p-_xlpm.pr)/100)
+        * PRODUCT(IF((_xlpm.sDates&gt;_xlpm.bd)*(_xlpm.sDates&lt;=_xlpm.t), _xlpm.sRatios, 1))
+      )
+    )),
+    SUM(_xlpm.contributions)
+  )
+))</f>
+        <v>0</v>
+      </c>
+      <c r="O20" s="78" cm="1">
+        <f t="array" ref="O20:O76">_xlfn.MAP(_xlfn.SEQUENCE(ROWS(_xlfn.ANCHORARRAY(A20))),_xlfn.LAMBDA(_xlpm.i,
+  _xlfn.LET(
+    _xlpm.t,          INDEX(_xlfn.ANCHORARRAY(A20),_xlpm.i),
+    _xlpm.isMonthEnd, _xlpm.t=EOMONTH(_xlpm.t,0),
+    _xlpm.isTrans,    COUNTIF($J$3:$J$8,_xlpm.t)&gt;0,
+    IF(AND(_xlpm.isTrans,NOT(_xlpm.isMonthEnd)),"",
+      INDEX(_xlfn.ANCHORARRAY(N20),_xlpm.i)-INDEX(_xlfn.ANCHORARRAY(H20),_xlpm.i)-INDEX(_xlfn.ANCHORARRAY(F20),_xlpm.i)
+    )
+  )
+))</f>
+        <v>8312.1366279069807</v>
+      </c>
+      <c r="P20" s="200" cm="1">
+        <f t="array" ref="P20:P76">_xlfn.MAP(_xlfn.ANCHORARRAY(A20),_xlfn.LAMBDA(_xlpm.t,
+  _xlfn.LET(
+    _xlpm.last_tx, IFERROR(_xlfn.MAXIFS($J$3:$J$8,$J$3:$J$8,"&lt;="&amp;_xlpm.t),0),
+    _xlpm.nom,     IF(_xlpm.last_tx=0, $B$3, _xlfn.XLOOKUP(_xlpm.last_tx,$J$3:$J$8,$U$3:$U$8)),
+    _xlpm.price,   IFERROR(INDEX(M20:M100,MATCH(_xlpm.t,_xlfn.ANCHORARRAY(A20),0)),0),
+    _xlpm.nom * _xlpm.price / 100
+  )
+))</f>
+        <v>162152343.75</v>
+      </c>
+      <c r="Q20" s="211" cm="1">
+        <f t="array" ref="Q20:Q76">_xlfn.MAP(_xlfn.ANCHORARRAY(A20),_xlfn.ANCHORARRAY(H20),_xlfn.ANCHORARRAY(F20),_xlfn.ANCHORARRAY(O20),_xlfn.ANCHORARRAY(P20),_xlfn.LAMBDA(_xlpm.t,_xlpm.h,_xlpm.f,_xlpm.n,_xlpm.o,
+  _xlfn.LET(
+    _xlpm.buyMask,    ($J$3:$J$8&lt;&gt;"")*($K$3:$K$8&gt;0),
+    _xlpm.sellMask,   ($J$3:$J$8&lt;&gt;"")*($K$3:$K$8&lt;0),
+    _xlpm.bDates,     _xlfn.VSTACK($A$19, _xlfn._xlws.FILTER($J$3:$J$8, _xlpm.buyMask, $B$12+1)),
+    _xlpm.bCFs,       _xlfn.VSTACK($B$18, _xlfn._xlws.FILTER($S$3:$S$8, _xlpm.buyMask, 0)),
+    _xlpm.sDates,     _xlfn._xlws.FILTER($J$3:$J$8, _xlpm.sellMask, 0),
+    _xlpm.sRatios,    _xlfn._xlws.FILTER(IFERROR($U$3:$U$8/_xlfn.VSTACK($B$3,$U$3:$U$7),1), _xlpm.sellMask, 1),
+    _xlpm.scaled_cf,  SUM(_xlfn.MAP(_xlpm.bDates, _xlpm.bCFs, _xlfn.LAMBDA(_xlpm.bd,_xlpm.cf,
+                  IF((_xlpm.bd&gt;_xlpm.t)+(_xlpm.cf=0), 0,
+                    _xlpm.cf * PRODUCT(IF((_xlpm.sDates&gt;_xlpm.bd)*(_xlpm.sDates&lt;=_xlpm.t), _xlpm.sRatios, 1))
+                  )
+                ))),
+    -_xlpm.scaled_cf + _xlpm.h + _xlpm.n - _xlpm.o + _xlpm.f
+  )
+))</f>
+        <v>0</v>
+      </c>
+      <c r="R20" s="213"/>
+      <c r="S20" s="214" cm="1">
+        <f t="array" ref="S20:S76">-_xlfn.MAP(_xlfn.ANCHORARRAY(A20),_xlfn.LAMBDA(_xlpm.t,
+  _xlfn.LET(
+    _xlpm.accr,       IFERROR(INDEX(_xlfn.ANCHORARRAY(K20),MATCH(_xlpm.t,_xlfn.ANCHORARRAY(A20),0)),0),
+    _xlpm.isCoupon,   COUNTIF($F$2:$F$12,_xlpm.t)&gt;0,
+    _xlpm.txNom,      IFERROR(_xlfn.XLOOKUP(_xlpm.t,$J$3:$J$8,$K$3:$K$8,0),0),
+    _xlpm.isSell,     _xlpm.txNom&lt;0,
+    _xlpm.prevCpn,    IFERROR(_xlfn.MAXIFS($F$2:$F$12,$F$2:$F$12,"&lt;"&amp;_xlpm.t),$B$10),
+    _xlpm.initAI,     IF(_xlpm.isCoupon*($A$19&gt;_xlpm.prevCpn)*($A$19&lt;=_xlpm.t), $B$7, 0),
+    _xlpm.buyAI,      IF(_xlpm.isCoupon,
+                  _xlpm.initAI + SUMPRODUCT(
+                    ($J$3:$J$8&lt;&gt;"")*($K$3:$K$8&gt;0)
+                    *($J$3:$J$8&gt;_xlpm.prevCpn)*($J$3:$J$8&lt;=_xlpm.t)
+                    *IF(ISNUMBER($T$3:$T$8),$T$3:$T$8,0)
+                  ),0),
+    _xlpm.couponPart, IF(_xlpm.isCoupon, _xlpm.accr - _xlpm.buyAI, 0),
+    _xlpm.sellPart,   IF(_xlpm.isSell,
+                  _xlfn.LET(
+                    _xlpm.sold,  ABS(_xlpm.txNom),
+                    _xlpm.prevN, _xlfn.XLOOKUP(_xlpm.t,$J$3:$J$8,_xlfn.VSTACK($B$3,$U$3:$U$7)),
+                    _xlpm.accr * _xlpm.sold / _xlpm.prevN
+                  ),0),
+    _xlpm.couponPart + _xlpm.sellPart
+  )
+))</f>
+        <v>-25897.790055248886</v>
+      </c>
+      <c r="T20" s="218" cm="1">
+        <f t="array" ref="T20:T76">_xlfn.MAP(_xlfn.ANCHORARRAY(A20),_xlfn.SEQUENCE(ROWS(_xlfn.ANCHORARRAY(A20))),_xlfn.LAMBDA(_xlpm.t,_xlpm.i,
+  IF(COUNTIF($F$2:$F$12,_xlpm.t)=0,0,
+    _xlfn.LET(
+      _xlpm.o, INDEX(_xlfn.ANCHORARRAY(O20),_xlpm.i), _xlpm.f, INDEX(_xlfn.ANCHORARRAY(F20),_xlpm.i), _xlpm.h, INDEX(_xlfn.ANCHORARRAY(H20),_xlpm.i),
+      _xlpm.s, INDEX($S$20:$S$220,_xlpm.i),
+      N(_xlpm.o)+N(_xlpm.f)+N(_xlpm.h)+N(_xlpm.s)
+    )
+  )
+))</f>
+        <v>-25897.790055248886</v>
+      </c>
+      <c r="U20" s="41"/>
+      <c r="V20" s="41"/>
+    </row>
+    <row r="21" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A21" s="202">
+        <v>46173</v>
+      </c>
+      <c r="B21" s="183">
+        <v>0</v>
+      </c>
+      <c r="C21" s="203"/>
+      <c r="D21" s="196">
+        <v>17</v>
+      </c>
+      <c r="E21" s="205">
+        <v>0</v>
+      </c>
+      <c r="F21" s="79">
+        <v>0</v>
+      </c>
+      <c r="G21" s="78">
+        <v>12011037.427325588</v>
+      </c>
+      <c r="H21" s="79">
+        <v>-141306.32267441865</v>
+      </c>
+      <c r="I21" s="79" t="str">
+        <v/>
+      </c>
+      <c r="J21" s="198">
+        <v>162011037.42732558</v>
+      </c>
+      <c r="K21" s="79">
+        <v>407608.69565217389</v>
+      </c>
+      <c r="L21" s="79">
+        <v>150000000</v>
+      </c>
+      <c r="M21" s="219">
+        <v>107.46875</v>
+      </c>
+      <c r="N21" s="78">
+        <v>-949218.75</v>
+      </c>
+      <c r="O21" s="50">
+        <v>-807912.42732558132</v>
+      </c>
+      <c r="P21" s="209">
+        <v>161203125</v>
+      </c>
+      <c r="Q21" s="211">
+        <v>0</v>
+      </c>
+      <c r="R21" s="213"/>
+      <c r="S21" s="215">
+        <v>0</v>
+      </c>
+      <c r="T21" s="218">
+        <v>0</v>
+      </c>
+      <c r="U21" s="41"/>
+      <c r="V21" s="41"/>
+    </row>
+    <row r="22" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A22" s="202">
+        <v>46203</v>
+      </c>
+      <c r="B22" s="183">
+        <v>0</v>
+      </c>
+      <c r="C22" s="203"/>
+      <c r="D22" s="196">
+        <v>47</v>
+      </c>
+      <c r="E22" s="205">
+        <v>0</v>
+      </c>
+      <c r="F22" s="79">
+        <v>0</v>
+      </c>
+      <c r="G22" s="78">
+        <v>11761673.328488378</v>
+      </c>
+      <c r="H22" s="79">
+        <v>-390670.42151162808</v>
+      </c>
+      <c r="I22" s="79" t="str">
+        <v/>
+      </c>
+      <c r="J22" s="198">
+        <v>161761673.32848838</v>
+      </c>
+      <c r="K22" s="79">
+        <v>1171875</v>
+      </c>
+      <c r="L22" s="79">
+        <v>150000000</v>
+      </c>
+      <c r="M22" s="220">
+        <v>97.132788000000005</v>
+      </c>
+      <c r="N22" s="78">
+        <v>-16453161.749999993</v>
+      </c>
+      <c r="O22" s="50">
+        <v>-16062491.328488365</v>
+      </c>
+      <c r="P22" s="209">
+        <v>145699182</v>
+      </c>
+      <c r="Q22" s="211">
+        <v>0</v>
+      </c>
+      <c r="R22" s="213"/>
+      <c r="S22" s="215">
+        <v>0</v>
+      </c>
+      <c r="T22" s="218">
+        <v>0</v>
+      </c>
+      <c r="U22" s="41"/>
+      <c r="V22" s="41" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="23" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A23" s="202">
+        <v>46234</v>
+      </c>
+      <c r="B23" s="183">
+        <v>0</v>
+      </c>
+      <c r="C23" s="203"/>
+      <c r="D23" s="196">
+        <v>78</v>
+      </c>
+      <c r="E23" s="205">
+        <v>0</v>
+      </c>
+      <c r="F23" s="79">
+        <v>0</v>
+      </c>
+      <c r="G23" s="78">
+        <v>11503997.093023261</v>
+      </c>
+      <c r="H23" s="79">
+        <v>-648346.65697674453</v>
+      </c>
+      <c r="I23" s="79" t="str">
+        <v/>
+      </c>
+      <c r="J23" s="198">
+        <v>161503997.09302324</v>
+      </c>
+      <c r="K23" s="79">
+        <v>1961616.8478260869</v>
+      </c>
+      <c r="L23" s="79">
+        <v>149999999.99999997</v>
+      </c>
+      <c r="M23" s="220">
+        <v>97.132788000000005</v>
+      </c>
+      <c r="N23" s="78">
+        <v>-16453161.749999993</v>
+      </c>
+      <c r="O23" s="50">
+        <v>-15804815.093023248</v>
+      </c>
+      <c r="P23" s="209">
+        <v>145699182</v>
+      </c>
+      <c r="Q23" s="211">
+        <v>0</v>
+      </c>
+      <c r="R23" s="213"/>
+      <c r="S23" s="215">
+        <v>0</v>
+      </c>
+      <c r="T23" s="218">
+        <v>0</v>
+      </c>
+      <c r="U23" s="41"/>
+      <c r="V23" s="41"/>
+    </row>
+    <row r="24" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A24" s="202">
+        <v>46265</v>
+      </c>
+      <c r="B24" s="183">
+        <v>0</v>
+      </c>
+      <c r="C24" s="203"/>
+      <c r="D24" s="196">
+        <v>109</v>
+      </c>
+      <c r="E24" s="205">
+        <v>0</v>
+      </c>
+      <c r="F24" s="79">
+        <v>0</v>
+      </c>
+      <c r="G24" s="78">
+        <v>11246320.857558144</v>
+      </c>
+      <c r="H24" s="79">
+        <v>-906022.89244186098</v>
+      </c>
+      <c r="I24" s="79" t="str">
+        <v/>
+      </c>
+      <c r="J24" s="198">
+        <v>161246320.85755813</v>
+      </c>
+      <c r="K24" s="79">
+        <v>2751358.6956521738</v>
+      </c>
+      <c r="L24" s="79">
+        <v>150000000</v>
+      </c>
+      <c r="M24" s="220">
+        <v>97.132788000000005</v>
+      </c>
+      <c r="N24" s="78">
+        <v>-16453161.749999993</v>
+      </c>
+      <c r="O24" s="50">
+        <v>-15547138.857558131</v>
+      </c>
+      <c r="P24" s="210">
+        <v>145699182</v>
+      </c>
+      <c r="Q24" s="211">
+        <v>0</v>
+      </c>
+      <c r="R24" s="213"/>
+      <c r="S24" s="215">
+        <v>0</v>
+      </c>
+      <c r="T24" s="218">
+        <v>0</v>
+      </c>
+      <c r="U24" s="41"/>
+      <c r="V24" s="41"/>
+    </row>
+    <row r="25" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A25" s="202">
+        <v>46295</v>
+      </c>
+      <c r="B25" s="183">
+        <v>0</v>
+      </c>
+      <c r="C25" s="203"/>
+      <c r="D25" s="196">
+        <v>139</v>
+      </c>
+      <c r="E25" s="205">
+        <v>0</v>
+      </c>
+      <c r="F25" s="79">
+        <v>0</v>
+      </c>
+      <c r="G25" s="78">
+        <v>10996956.758720934</v>
+      </c>
+      <c r="H25" s="79">
+        <v>-1155386.9912790703</v>
+      </c>
+      <c r="I25" s="79" t="str">
+        <v/>
+      </c>
+      <c r="J25" s="198">
+        <v>160996956.75872093</v>
+      </c>
+      <c r="K25" s="79">
+        <v>3515625</v>
+      </c>
+      <c r="L25" s="79">
+        <v>150000000</v>
+      </c>
+      <c r="M25" s="221">
+        <v>97.132788000000005</v>
+      </c>
+      <c r="N25" s="78">
+        <v>-16453161.749999993</v>
+      </c>
+      <c r="O25" s="50">
+        <v>-15297774.758720923</v>
+      </c>
+      <c r="P25" s="210">
+        <v>145699182</v>
+      </c>
+      <c r="Q25" s="211">
+        <v>0</v>
+      </c>
+      <c r="R25" s="213"/>
+      <c r="S25" s="216">
+        <v>0</v>
+      </c>
+      <c r="T25" s="218">
+        <v>0</v>
+      </c>
+      <c r="U25" s="35"/>
+      <c r="V25" s="35"/>
+    </row>
+    <row r="26" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A26" s="202">
+        <v>46326</v>
+      </c>
+      <c r="B26" s="183">
+        <v>0</v>
+      </c>
+      <c r="C26" s="203"/>
+      <c r="D26" s="196">
+        <v>170</v>
+      </c>
+      <c r="E26" s="205">
+        <v>0</v>
+      </c>
+      <c r="F26" s="79">
+        <v>0</v>
+      </c>
+      <c r="G26" s="78">
+        <v>10739280.523255819</v>
+      </c>
+      <c r="H26" s="79">
+        <v>-1413063.2267441866</v>
+      </c>
+      <c r="I26" s="79" t="str">
+        <v/>
+      </c>
+      <c r="J26" s="198">
+        <v>160739280.52325583</v>
+      </c>
+      <c r="K26" s="79">
+        <v>4305366.8478260869</v>
+      </c>
+      <c r="L26" s="79">
+        <v>150000000</v>
+      </c>
+      <c r="M26" s="221">
+        <v>99.640625</v>
+      </c>
+      <c r="N26" s="78">
+        <v>-12691406.25</v>
+      </c>
+      <c r="O26" s="50">
+        <v>-11278343.023255814</v>
+      </c>
+      <c r="P26" s="210">
+        <v>149460937.5</v>
+      </c>
+      <c r="Q26" s="211">
+        <v>0</v>
+      </c>
+      <c r="R26" s="213"/>
+      <c r="S26" s="216">
+        <v>0</v>
+      </c>
+      <c r="T26" s="218">
+        <v>0</v>
+      </c>
+      <c r="U26" s="35"/>
+      <c r="V26" s="35"/>
+    </row>
+    <row r="27" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A27" s="202">
+        <v>46341</v>
+      </c>
+      <c r="B27" s="183">
+        <v>0</v>
+      </c>
+      <c r="C27" s="203"/>
+      <c r="D27" s="196">
+        <v>185</v>
+      </c>
+      <c r="E27" s="205">
+        <v>0</v>
+      </c>
+      <c r="F27" s="79">
+        <v>0</v>
+      </c>
+      <c r="G27" s="78">
+        <v>10614598.473837214</v>
+      </c>
+      <c r="H27" s="79">
+        <v>-1537745.2761627913</v>
+      </c>
+      <c r="I27" s="79" t="str">
+        <v/>
+      </c>
+      <c r="J27" s="198">
+        <v>160614598.4738372</v>
+      </c>
+      <c r="K27" s="79">
+        <v>4687500</v>
+      </c>
+      <c r="L27" s="79">
+        <v>149999999.99999997</v>
+      </c>
+      <c r="M27" s="221">
+        <v>97.132788000000005</v>
+      </c>
+      <c r="N27" s="78">
+        <v>-16453161.749999993</v>
+      </c>
+      <c r="O27" s="50">
+        <v>-14915416.473837201</v>
+      </c>
+      <c r="P27" s="210">
+        <v>145699182</v>
+      </c>
+      <c r="Q27" s="211">
+        <v>0</v>
+      </c>
+      <c r="R27" s="213"/>
+      <c r="S27" s="216">
+        <v>-4687500</v>
+      </c>
+      <c r="T27" s="218">
+        <v>-21140661.749999993</v>
+      </c>
+      <c r="U27" s="35"/>
+      <c r="V27" s="35"/>
+    </row>
+    <row r="28" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A28" s="202">
+        <v>46356</v>
+      </c>
+      <c r="B28" s="183">
+        <v>0</v>
+      </c>
+      <c r="C28" s="203"/>
+      <c r="D28" s="196">
+        <v>200</v>
+      </c>
+      <c r="E28" s="205">
+        <v>0</v>
+      </c>
+      <c r="F28" s="79">
+        <v>0</v>
+      </c>
+      <c r="G28" s="78">
+        <v>10489916.42441861</v>
+      </c>
+      <c r="H28" s="79">
+        <v>-1662427.325581396</v>
+      </c>
+      <c r="I28" s="79" t="str">
+        <v/>
+      </c>
+      <c r="J28" s="198">
+        <v>160489916.4244186</v>
+      </c>
+      <c r="K28" s="79">
+        <v>388466.85082872928</v>
+      </c>
+      <c r="L28" s="79">
+        <v>150000000</v>
+      </c>
+      <c r="M28" s="221">
+        <v>97.132788000000005</v>
+      </c>
+      <c r="N28" s="78">
+        <v>-16453161.749999993</v>
+      </c>
+      <c r="O28" s="50">
+        <v>-14790734.424418597</v>
+      </c>
+      <c r="P28" s="210">
+        <v>145699182</v>
+      </c>
+      <c r="Q28" s="211">
+        <v>0</v>
+      </c>
+      <c r="R28" s="213"/>
+      <c r="S28" s="216">
+        <v>0</v>
+      </c>
+      <c r="T28" s="218">
+        <v>0</v>
+      </c>
+      <c r="U28" s="35"/>
+      <c r="V28" s="35"/>
+    </row>
+    <row r="29" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A29" s="202">
+        <v>46387</v>
+      </c>
+      <c r="B29" s="183">
+        <v>0</v>
+      </c>
+      <c r="C29" s="203"/>
+      <c r="D29" s="196">
+        <v>231</v>
+      </c>
+      <c r="E29" s="205">
+        <v>0</v>
+      </c>
+      <c r="F29" s="79">
+        <v>0</v>
+      </c>
+      <c r="G29" s="78">
+        <v>10232240.188953493</v>
+      </c>
+      <c r="H29" s="79">
+        <v>-1920103.5610465126</v>
+      </c>
+      <c r="I29" s="79" t="str">
+        <v/>
+      </c>
+      <c r="J29" s="198">
+        <v>160232240.18895349</v>
+      </c>
+      <c r="K29" s="79">
+        <v>1191298.3425414364</v>
+      </c>
+      <c r="L29" s="79">
+        <v>150000000</v>
+      </c>
+      <c r="M29" s="221">
+        <v>97.132788000000005</v>
+      </c>
+      <c r="N29" s="78">
+        <v>-16453161.749999993</v>
+      </c>
+      <c r="O29" s="50">
+        <v>-14533058.18895348</v>
+      </c>
+      <c r="P29" s="210">
+        <v>145699182</v>
+      </c>
+      <c r="Q29" s="211">
+        <v>0</v>
+      </c>
+      <c r="R29" s="213"/>
+      <c r="S29" s="216">
+        <v>0</v>
+      </c>
+      <c r="T29" s="218">
+        <v>0</v>
+      </c>
+      <c r="U29" s="35"/>
+      <c r="V29" s="35"/>
+    </row>
+    <row r="30" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A30" s="202">
+        <v>46418</v>
+      </c>
+      <c r="B30" s="183">
+        <v>0</v>
+      </c>
+      <c r="C30" s="203"/>
+      <c r="D30" s="196">
+        <v>262</v>
+      </c>
+      <c r="E30" s="205">
+        <v>0</v>
+      </c>
+      <c r="F30" s="79">
+        <v>0</v>
+      </c>
+      <c r="G30" s="78">
+        <v>9974563.953488376</v>
+      </c>
+      <c r="H30" s="79">
+        <v>-2177779.7965116287</v>
+      </c>
+      <c r="I30" s="79" t="str">
+        <v/>
+      </c>
+      <c r="J30" s="198">
+        <v>159974563.95348838</v>
+      </c>
+      <c r="K30" s="79">
+        <v>1994129.8342541438</v>
+      </c>
+      <c r="L30" s="79">
+        <v>150000000</v>
+      </c>
+      <c r="M30" s="221">
+        <v>97.132788000000005</v>
+      </c>
+      <c r="N30" s="78">
+        <v>-16453161.749999993</v>
+      </c>
+      <c r="O30" s="50">
+        <v>-14275381.953488365</v>
+      </c>
+      <c r="P30" s="210">
+        <v>145699182</v>
+      </c>
+      <c r="Q30" s="211">
+        <v>0</v>
+      </c>
+      <c r="R30" s="213"/>
+      <c r="S30" s="216">
+        <v>0</v>
+      </c>
+      <c r="T30" s="218">
+        <v>0</v>
+      </c>
+      <c r="U30" s="35"/>
+      <c r="V30" s="35"/>
+    </row>
+    <row r="31" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A31" s="202">
+        <v>46446</v>
+      </c>
+      <c r="B31" s="183">
+        <v>0</v>
+      </c>
+      <c r="C31" s="222"/>
+      <c r="D31" s="196">
+        <v>290</v>
+      </c>
+      <c r="E31" s="205">
+        <v>0</v>
+      </c>
+      <c r="F31" s="79">
+        <v>0</v>
+      </c>
+      <c r="G31" s="78">
+        <v>9741824.1279069819</v>
+      </c>
+      <c r="H31" s="79">
+        <v>-2410519.6220930242</v>
+      </c>
+      <c r="I31" s="79" t="str">
+        <v/>
+      </c>
+      <c r="J31" s="198">
+        <v>159741824.12790698</v>
+      </c>
+      <c r="K31" s="79">
+        <v>2719267.9558011051</v>
+      </c>
+      <c r="L31" s="79">
+        <v>150000000</v>
+      </c>
+      <c r="M31" s="221">
+        <v>97.132788000000005</v>
+      </c>
+      <c r="N31" s="78">
+        <v>-16453161.749999993</v>
+      </c>
+      <c r="O31" s="50">
+        <v>-14042642.127906969</v>
+      </c>
+      <c r="P31" s="210">
+        <v>145699182</v>
+      </c>
+      <c r="Q31" s="211">
+        <v>0</v>
+      </c>
+      <c r="R31" s="213"/>
+      <c r="S31" s="217">
+        <v>0</v>
+      </c>
+      <c r="T31" s="218">
+        <v>0</v>
+      </c>
+      <c r="U31" s="35"/>
+      <c r="V31" s="35"/>
+    </row>
+    <row r="32" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A32" s="202">
+        <v>46477</v>
+      </c>
+      <c r="B32" s="183">
+        <v>0</v>
+      </c>
+      <c r="C32" s="223"/>
+      <c r="D32" s="196">
+        <v>321</v>
+      </c>
+      <c r="E32" s="205">
+        <v>0</v>
+      </c>
+      <c r="F32" s="79">
+        <v>0</v>
+      </c>
+      <c r="G32" s="78">
+        <v>9484147.8924418651</v>
+      </c>
+      <c r="H32" s="79">
+        <v>-2668195.857558141</v>
+      </c>
+      <c r="I32" s="79" t="str">
+        <v/>
+      </c>
+      <c r="J32" s="198">
+        <v>159484147.89244187</v>
+      </c>
+      <c r="K32" s="79">
+        <v>3522099.4475138122</v>
+      </c>
+      <c r="L32" s="79">
+        <v>150000000</v>
+      </c>
+      <c r="M32" s="221">
+        <v>97.132788000000005</v>
+      </c>
+      <c r="N32" s="78">
+        <v>-16453161.749999993</v>
+      </c>
+      <c r="O32" s="50">
+        <v>-13784965.892441852</v>
+      </c>
+      <c r="P32" s="210">
+        <v>145699182</v>
+      </c>
+      <c r="Q32" s="211">
+        <v>2.9802322387695313E-8</v>
+      </c>
+      <c r="R32" s="213"/>
+      <c r="S32" s="216">
+        <v>0</v>
+      </c>
+      <c r="T32" s="218">
+        <v>0</v>
+      </c>
+      <c r="U32" s="35"/>
+      <c r="V32" s="35"/>
+    </row>
+    <row r="33" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A33" s="202">
+        <v>46507</v>
+      </c>
+      <c r="B33" s="183">
+        <v>0</v>
+      </c>
+      <c r="C33" s="223"/>
+      <c r="D33" s="196">
+        <v>351</v>
+      </c>
+      <c r="E33" s="205">
+        <v>0</v>
+      </c>
+      <c r="F33" s="79">
+        <v>0</v>
+      </c>
+      <c r="G33" s="78">
+        <v>9234783.7936046552</v>
+      </c>
+      <c r="H33" s="79">
+        <v>-2917559.9563953499</v>
+      </c>
+      <c r="I33" s="79" t="str">
+        <v/>
+      </c>
+      <c r="J33" s="198">
+        <v>159234783.79360464</v>
+      </c>
+      <c r="K33" s="79">
+        <v>4299033.1491712704</v>
+      </c>
+      <c r="L33" s="79">
+        <v>150000000</v>
+      </c>
+      <c r="M33" s="221">
+        <v>97.132788000000005</v>
+      </c>
+      <c r="N33" s="78">
+        <v>-16453161.749999993</v>
+      </c>
+      <c r="O33" s="50">
+        <v>-13535601.793604642</v>
+      </c>
+      <c r="P33" s="210">
+        <v>145699182</v>
+      </c>
+      <c r="Q33" s="211">
+        <v>0</v>
+      </c>
+      <c r="R33" s="213"/>
+      <c r="S33" s="216">
+        <v>0</v>
+      </c>
+      <c r="T33" s="218">
+        <v>0</v>
+      </c>
+      <c r="U33" s="35"/>
+      <c r="V33" s="35"/>
+    </row>
+    <row r="34" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A34" s="202">
+        <v>46522</v>
+      </c>
+      <c r="B34" s="183">
+        <v>0</v>
+      </c>
+      <c r="C34" s="223"/>
+      <c r="D34" s="196">
+        <v>366</v>
+      </c>
+      <c r="E34" s="205">
+        <v>0</v>
+      </c>
+      <c r="F34" s="79">
+        <v>0</v>
+      </c>
+      <c r="G34" s="78">
+        <v>9110101.7441860512</v>
+      </c>
+      <c r="H34" s="79">
+        <v>-3042242.0058139549</v>
+      </c>
+      <c r="I34" s="79" t="str">
+        <v/>
+      </c>
+      <c r="J34" s="198">
+        <v>159110101.74418604</v>
+      </c>
+      <c r="K34" s="79">
+        <v>4687500</v>
+      </c>
+      <c r="L34" s="79">
+        <v>150000000</v>
+      </c>
+      <c r="M34" s="221">
+        <v>97.132788000000005</v>
+      </c>
+      <c r="N34" s="78">
+        <v>-16453161.749999993</v>
+      </c>
+      <c r="O34" s="50">
+        <v>-13410919.744186038</v>
+      </c>
+      <c r="P34" s="210">
+        <v>145699182</v>
+      </c>
+      <c r="Q34" s="211">
+        <v>0</v>
+      </c>
+      <c r="R34" s="213"/>
+      <c r="S34" s="216">
+        <v>-4687500</v>
+      </c>
+      <c r="T34" s="218">
+        <v>-21140661.749999993</v>
+      </c>
+      <c r="U34" s="35"/>
+      <c r="V34" s="35"/>
+    </row>
+    <row r="35" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A35" s="202">
+        <v>46538</v>
+      </c>
+      <c r="B35" s="183">
+        <v>0</v>
+      </c>
+      <c r="C35" s="223"/>
+      <c r="D35" s="196">
+        <v>382</v>
+      </c>
+      <c r="E35" s="205">
+        <v>0</v>
+      </c>
+      <c r="F35" s="79">
+        <v>0</v>
+      </c>
+      <c r="G35" s="78">
+        <v>8977107.5581395403</v>
+      </c>
+      <c r="H35" s="79">
+        <v>-3175236.1918604663</v>
+      </c>
+      <c r="I35" s="79" t="str">
+        <v/>
+      </c>
+      <c r="J35" s="198">
+        <v>158977107.55813953</v>
+      </c>
+      <c r="K35" s="79">
+        <v>407608.69565217389</v>
+      </c>
+      <c r="L35" s="79">
+        <v>150000000</v>
+      </c>
+      <c r="M35" s="221">
+        <v>97.132788000000005</v>
+      </c>
+      <c r="N35" s="78">
+        <v>-16453161.749999993</v>
+      </c>
+      <c r="O35" s="50">
+        <v>-13277925.558139525</v>
+      </c>
+      <c r="P35" s="210">
+        <v>145699182</v>
+      </c>
+      <c r="Q35" s="211">
+        <v>0</v>
+      </c>
+      <c r="R35" s="213"/>
+      <c r="S35" s="216">
+        <v>0</v>
+      </c>
+      <c r="T35" s="218">
+        <v>0</v>
+      </c>
+      <c r="U35" s="35"/>
+      <c r="V35" s="35"/>
+    </row>
+    <row r="36" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A36" s="202">
+        <v>46568</v>
+      </c>
+      <c r="B36" s="183">
+        <v>0</v>
+      </c>
+      <c r="C36" s="223"/>
+      <c r="D36" s="196">
+        <v>412</v>
+      </c>
+      <c r="E36" s="205">
+        <v>0</v>
+      </c>
+      <c r="F36" s="79">
+        <v>0</v>
+      </c>
+      <c r="G36" s="78">
+        <v>8727743.4593023304</v>
+      </c>
+      <c r="H36" s="79">
+        <v>-3424600.2906976757</v>
+      </c>
+      <c r="I36" s="79" t="str">
+        <v/>
+      </c>
+      <c r="J36" s="198">
+        <v>158727743.45930234</v>
+      </c>
+      <c r="K36" s="79">
+        <v>1171875</v>
+      </c>
+      <c r="L36" s="79">
+        <v>150000000</v>
+      </c>
+      <c r="M36" s="221">
+        <v>97.132788000000005</v>
+      </c>
+      <c r="N36" s="78">
+        <v>-16453161.749999993</v>
+      </c>
+      <c r="O36" s="50">
+        <v>-13028561.459302317</v>
+      </c>
+      <c r="P36" s="210">
+        <v>145699182</v>
+      </c>
+      <c r="Q36" s="211">
+        <v>2.9802322387695313E-8</v>
+      </c>
+      <c r="R36" s="213"/>
+      <c r="S36" s="216">
+        <v>0</v>
+      </c>
+      <c r="T36" s="218">
+        <v>0</v>
+      </c>
+      <c r="U36" s="35"/>
+      <c r="V36" s="35"/>
+    </row>
+    <row r="37" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A37" s="202">
+        <v>46599</v>
+      </c>
+      <c r="B37" s="183">
+        <v>0</v>
+      </c>
+      <c r="C37" s="223"/>
+      <c r="D37" s="196">
+        <v>443</v>
+      </c>
+      <c r="E37" s="205">
+        <v>0</v>
+      </c>
+      <c r="F37" s="79">
+        <v>0</v>
+      </c>
+      <c r="G37" s="78">
+        <v>8470067.2238372136</v>
+      </c>
+      <c r="H37" s="79">
+        <v>-3682276.5261627925</v>
+      </c>
+      <c r="I37" s="79" t="str">
+        <v/>
+      </c>
+      <c r="J37" s="198">
+        <v>158470067.2238372</v>
+      </c>
+      <c r="K37" s="79">
+        <v>1961616.8478260869</v>
+      </c>
+      <c r="L37" s="79">
+        <v>149999999.99999997</v>
+      </c>
+      <c r="M37" s="221">
+        <v>97.132788000000005</v>
+      </c>
+      <c r="N37" s="78">
+        <v>-16453161.749999993</v>
+      </c>
+      <c r="O37" s="50">
+        <v>-12770885.223837201</v>
+      </c>
+      <c r="P37" s="210">
+        <v>145699182</v>
+      </c>
+      <c r="Q37" s="211">
+        <v>0</v>
+      </c>
+      <c r="R37" s="213"/>
+      <c r="S37" s="216">
+        <v>0</v>
+      </c>
+      <c r="T37" s="218">
+        <v>0</v>
+      </c>
+      <c r="U37" s="35"/>
+      <c r="V37" s="35"/>
+    </row>
+    <row r="38" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A38" s="202">
+        <v>46630</v>
+      </c>
+      <c r="B38" s="183">
+        <v>0</v>
+      </c>
+      <c r="C38" s="223"/>
+      <c r="D38" s="196">
+        <v>474</v>
+      </c>
+      <c r="E38" s="205">
+        <v>0</v>
+      </c>
+      <c r="F38" s="79">
+        <v>0</v>
+      </c>
+      <c r="G38" s="78">
+        <v>8212390.9883720968</v>
+      </c>
+      <c r="H38" s="79">
+        <v>-3939952.7616279088</v>
+      </c>
+      <c r="I38" s="79" t="str">
+        <v/>
+      </c>
+      <c r="J38" s="198">
+        <v>158212390.98837209</v>
+      </c>
+      <c r="K38" s="79">
+        <v>2751358.6956521738</v>
+      </c>
+      <c r="L38" s="79">
+        <v>150000000</v>
+      </c>
+      <c r="M38" s="221">
+        <v>97.132788000000005</v>
+      </c>
+      <c r="N38" s="78">
+        <v>-16453161.749999993</v>
+      </c>
+      <c r="O38" s="50">
+        <v>-12513208.988372084</v>
+      </c>
+      <c r="P38" s="210">
+        <v>145699182</v>
+      </c>
+      <c r="Q38" s="211">
+        <v>0</v>
+      </c>
+      <c r="R38" s="213"/>
+      <c r="S38" s="216">
+        <v>0</v>
+      </c>
+      <c r="T38" s="218">
+        <v>0</v>
+      </c>
+      <c r="U38" s="35"/>
+      <c r="V38" s="35"/>
+    </row>
+    <row r="39" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A39" s="202">
+        <v>46660</v>
+      </c>
+      <c r="B39" s="183">
+        <v>0</v>
+      </c>
+      <c r="C39" s="223"/>
+      <c r="D39" s="196">
+        <v>504</v>
+      </c>
+      <c r="E39" s="205">
+        <v>0</v>
+      </c>
+      <c r="F39" s="79">
+        <v>0</v>
+      </c>
+      <c r="G39" s="78">
+        <v>7963026.8895348869</v>
+      </c>
+      <c r="H39" s="79">
+        <v>-4189316.8604651182</v>
+      </c>
+      <c r="I39" s="79" t="str">
+        <v/>
+      </c>
+      <c r="J39" s="198">
+        <v>157963026.88953489</v>
+      </c>
+      <c r="K39" s="79">
+        <v>3515625</v>
+      </c>
+      <c r="L39" s="79">
+        <v>150000000</v>
+      </c>
+      <c r="M39" s="221">
+        <v>97.132788000000005</v>
+      </c>
+      <c r="N39" s="78">
+        <v>-16453161.749999993</v>
+      </c>
+      <c r="O39" s="50">
+        <v>-12263844.889534874</v>
+      </c>
+      <c r="P39" s="210">
+        <v>145699182</v>
+      </c>
+      <c r="Q39" s="211">
+        <v>2.9802322387695313E-8</v>
+      </c>
+      <c r="R39" s="213"/>
+      <c r="S39" s="216">
+        <v>0</v>
+      </c>
+      <c r="T39" s="218">
+        <v>0</v>
+      </c>
+      <c r="U39" s="35"/>
+      <c r="V39" s="35"/>
+    </row>
+    <row r="40" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A40" s="202">
+        <v>46691</v>
+      </c>
+      <c r="B40" s="183">
+        <v>0</v>
+      </c>
+      <c r="C40" s="203"/>
+      <c r="D40" s="196">
+        <v>535</v>
+      </c>
+      <c r="E40" s="205">
+        <v>0</v>
+      </c>
+      <c r="F40" s="79">
+        <v>0</v>
+      </c>
+      <c r="G40" s="78">
+        <v>7705350.6540697711</v>
+      </c>
+      <c r="H40" s="79">
+        <v>-4446993.0959302345</v>
+      </c>
+      <c r="I40" s="79" t="str">
+        <v/>
+      </c>
+      <c r="J40" s="198">
+        <v>157705350.65406975</v>
+      </c>
+      <c r="K40" s="79">
+        <v>4305366.8478260869</v>
+      </c>
+      <c r="L40" s="79">
+        <v>149999999.99999997</v>
+      </c>
+      <c r="M40" s="221">
+        <v>99</v>
+      </c>
+      <c r="N40" s="78">
+        <v>-13652343.75</v>
+      </c>
+      <c r="O40" s="50">
+        <v>-9205350.6540697664</v>
+      </c>
+      <c r="P40" s="210">
+        <v>148500000</v>
+      </c>
+      <c r="Q40" s="211">
+        <v>0</v>
+      </c>
+      <c r="R40" s="213"/>
+      <c r="S40" s="216">
+        <v>0</v>
+      </c>
+      <c r="T40" s="218">
+        <v>0</v>
+      </c>
+      <c r="U40" s="35"/>
+      <c r="V40" s="35"/>
+    </row>
+    <row r="41" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A41" s="202">
+        <v>46706</v>
+      </c>
+      <c r="B41" s="183">
+        <v>0</v>
+      </c>
+      <c r="C41" s="203"/>
+      <c r="D41" s="196">
+        <v>550</v>
+      </c>
+      <c r="E41" s="205">
+        <v>0</v>
+      </c>
+      <c r="F41" s="79">
+        <v>0</v>
+      </c>
+      <c r="G41" s="78">
+        <v>7580668.6046511661</v>
+      </c>
+      <c r="H41" s="79">
+        <v>-4571675.1453488395</v>
+      </c>
+      <c r="I41" s="79" t="str">
+        <v/>
+      </c>
+      <c r="J41" s="198">
+        <v>157580668.60465115</v>
+      </c>
+      <c r="K41" s="79">
+        <v>4687500</v>
+      </c>
+      <c r="L41" s="79">
+        <v>150000000</v>
+      </c>
+      <c r="M41" s="221">
+        <v>97.132788000000005</v>
+      </c>
+      <c r="N41" s="78">
+        <v>-16453161.749999993</v>
+      </c>
+      <c r="O41" s="50">
+        <v>-11881486.604651153</v>
+      </c>
+      <c r="P41" s="210">
+        <v>145699182</v>
+      </c>
+      <c r="Q41" s="211">
+        <v>0</v>
+      </c>
+      <c r="R41" s="213"/>
+      <c r="S41" s="216">
+        <v>-4687500</v>
+      </c>
+      <c r="T41" s="218">
+        <v>-21140661.749999993</v>
+      </c>
+      <c r="U41" s="35"/>
+      <c r="V41" s="35"/>
+    </row>
+    <row r="42" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A42" s="202">
+        <v>46721</v>
+      </c>
+      <c r="B42" s="183">
+        <v>0</v>
+      </c>
+      <c r="C42" s="203"/>
+      <c r="D42" s="196">
+        <v>565</v>
+      </c>
+      <c r="E42" s="205">
+        <v>0</v>
+      </c>
+      <c r="F42" s="79">
+        <v>0</v>
+      </c>
+      <c r="G42" s="78">
+        <v>7455986.5552325621</v>
+      </c>
+      <c r="H42" s="79">
+        <v>-4696357.1947674435</v>
+      </c>
+      <c r="I42" s="79" t="str">
+        <v/>
+      </c>
+      <c r="J42" s="198">
+        <v>157455986.55523255</v>
+      </c>
+      <c r="K42" s="79">
+        <v>386332.41758241761</v>
+      </c>
+      <c r="L42" s="79">
+        <v>150000000</v>
+      </c>
+      <c r="M42" s="221">
+        <v>97.132788000000005</v>
+      </c>
+      <c r="N42" s="78">
+        <v>-16453161.749999993</v>
+      </c>
+      <c r="O42" s="50">
+        <v>-11756804.555232549</v>
+      </c>
+      <c r="P42" s="210">
+        <v>145699182</v>
+      </c>
+      <c r="Q42" s="211">
+        <v>0</v>
+      </c>
+      <c r="R42" s="213"/>
+      <c r="S42" s="216">
+        <v>0</v>
+      </c>
+      <c r="T42" s="218">
+        <v>0</v>
+      </c>
+      <c r="U42" s="35"/>
+      <c r="V42" s="35"/>
+    </row>
+    <row r="43" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A43" s="202">
+        <v>46752</v>
+      </c>
+      <c r="B43" s="183">
+        <v>0</v>
+      </c>
+      <c r="C43" s="203"/>
+      <c r="D43" s="196">
+        <v>596</v>
+      </c>
+      <c r="E43" s="205">
+        <v>0</v>
+      </c>
+      <c r="F43" s="79">
+        <v>0</v>
+      </c>
+      <c r="G43" s="78">
+        <v>7198310.3197674453</v>
+      </c>
+      <c r="H43" s="79">
+        <v>-4954033.4302325603</v>
+      </c>
+      <c r="I43" s="79" t="str">
+        <v/>
+      </c>
+      <c r="J43" s="198">
+        <v>157198310.31976745</v>
+      </c>
+      <c r="K43" s="79">
+        <v>1184752.7472527472</v>
+      </c>
+      <c r="L43" s="79">
+        <v>150000000</v>
+      </c>
+      <c r="M43" s="221">
+        <v>97.132788000000005</v>
+      </c>
+      <c r="N43" s="78">
+        <v>-16453161.749999993</v>
+      </c>
+      <c r="O43" s="50">
+        <v>-11499128.319767432</v>
+      </c>
+      <c r="P43" s="210">
+        <v>145699182</v>
+      </c>
+      <c r="Q43" s="211">
+        <v>0</v>
+      </c>
+      <c r="R43" s="213"/>
+      <c r="S43" s="216">
+        <v>0</v>
+      </c>
+      <c r="T43" s="218">
+        <v>0</v>
+      </c>
+      <c r="U43" s="35"/>
+      <c r="V43" s="35"/>
+    </row>
+    <row r="44" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A44" s="202">
+        <v>46783</v>
+      </c>
+      <c r="B44" s="183">
+        <v>0</v>
+      </c>
+      <c r="C44" s="203"/>
+      <c r="D44" s="196">
+        <v>627</v>
+      </c>
+      <c r="E44" s="206">
+        <v>0</v>
+      </c>
+      <c r="F44" s="79">
+        <v>0</v>
+      </c>
+      <c r="G44" s="78">
+        <v>6940634.0843023285</v>
+      </c>
+      <c r="H44" s="79">
+        <v>-5211709.6656976771</v>
+      </c>
+      <c r="I44" s="79" t="str">
+        <v/>
+      </c>
+      <c r="J44" s="198">
+        <v>156940634.08430234</v>
+      </c>
+      <c r="K44" s="79">
+        <v>1983173.076923077</v>
+      </c>
+      <c r="L44" s="79">
+        <v>150000000</v>
+      </c>
+      <c r="M44" s="221">
+        <v>97.132788000000005</v>
+      </c>
+      <c r="N44" s="78">
+        <v>-16453161.749999993</v>
+      </c>
+      <c r="O44" s="50">
+        <v>-11241452.084302315</v>
+      </c>
+      <c r="P44" s="210">
+        <v>145699182</v>
+      </c>
+      <c r="Q44" s="211">
+        <v>2.9802322387695313E-8</v>
+      </c>
+      <c r="R44" s="213"/>
+      <c r="S44" s="216">
+        <v>0</v>
+      </c>
+      <c r="T44" s="218">
+        <v>0</v>
+      </c>
+      <c r="U44" s="35"/>
+      <c r="V44" s="35"/>
+    </row>
+    <row r="45" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A45" s="202">
+        <v>46812</v>
+      </c>
+      <c r="B45" s="183">
+        <v>0</v>
+      </c>
+      <c r="C45" s="203"/>
+      <c r="D45" s="196">
+        <v>656</v>
+      </c>
+      <c r="E45" s="205">
+        <v>0</v>
+      </c>
+      <c r="F45" s="79">
+        <v>0</v>
+      </c>
+      <c r="G45" s="78">
+        <v>6699582.1220930265</v>
+      </c>
+      <c r="H45" s="79">
+        <v>-5452761.6279069791</v>
+      </c>
+      <c r="I45" s="79" t="str">
+        <v/>
+      </c>
+      <c r="J45" s="198">
+        <v>156699582.12209302</v>
+      </c>
+      <c r="K45" s="79">
+        <v>2730082.4175824174</v>
+      </c>
+      <c r="L45" s="79">
+        <v>150000000</v>
+      </c>
+      <c r="M45" s="221">
+        <v>97.132788000000005</v>
+      </c>
+      <c r="N45" s="78">
+        <v>-16453161.749999993</v>
+      </c>
+      <c r="O45" s="50">
+        <v>-11000400.122093014</v>
+      </c>
+      <c r="P45" s="210">
+        <v>145699182</v>
+      </c>
+      <c r="Q45" s="211">
+        <v>0</v>
+      </c>
+      <c r="R45" s="213"/>
+      <c r="S45" s="216">
+        <v>0</v>
+      </c>
+      <c r="T45" s="218">
+        <v>0</v>
+      </c>
+      <c r="U45" s="35"/>
+      <c r="V45" s="35"/>
+    </row>
+    <row r="46" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A46" s="202">
+        <v>46843</v>
+      </c>
+      <c r="B46" s="183">
+        <v>0</v>
+      </c>
+      <c r="C46" s="203"/>
+      <c r="D46" s="196">
+        <v>687</v>
+      </c>
+      <c r="E46" s="205">
+        <v>0</v>
+      </c>
+      <c r="F46" s="79">
+        <v>0</v>
+      </c>
+      <c r="G46" s="78">
+        <v>6441905.8866279097</v>
+      </c>
+      <c r="H46" s="79">
+        <v>-5710437.8633720959</v>
+      </c>
+      <c r="I46" s="79" t="str">
+        <v/>
+      </c>
+      <c r="J46" s="198">
+        <v>156441905.88662791</v>
+      </c>
+      <c r="K46" s="79">
+        <v>3528502.7472527474</v>
+      </c>
+      <c r="L46" s="79">
+        <v>150000000</v>
+      </c>
+      <c r="M46" s="221">
+        <v>97.132788000000005</v>
+      </c>
+      <c r="N46" s="78">
+        <v>-16453161.749999993</v>
+      </c>
+      <c r="O46" s="50">
+        <v>-10742723.886627898</v>
+      </c>
+      <c r="P46" s="210">
+        <v>145699182</v>
+      </c>
+      <c r="Q46" s="211">
+        <v>0</v>
+      </c>
+      <c r="R46" s="213"/>
+      <c r="S46" s="216">
+        <v>0</v>
+      </c>
+      <c r="T46" s="218">
+        <v>0</v>
+      </c>
+      <c r="U46" s="35"/>
+      <c r="V46" s="35"/>
+    </row>
+    <row r="47" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A47" s="202">
+        <v>46873</v>
+      </c>
+      <c r="B47" s="183">
+        <v>0</v>
+      </c>
+      <c r="C47" s="203"/>
+      <c r="D47" s="196">
+        <v>717</v>
+      </c>
+      <c r="E47" s="205">
+        <v>0</v>
+      </c>
+      <c r="F47" s="79">
+        <v>0</v>
+      </c>
+      <c r="G47" s="78">
+        <v>6192541.7877907008</v>
+      </c>
+      <c r="H47" s="79">
+        <v>-5959801.9622093048</v>
+      </c>
+      <c r="I47" s="79" t="str">
+        <v/>
+      </c>
+      <c r="J47" s="198">
+        <v>156192541.78779069</v>
+      </c>
+      <c r="K47" s="79">
+        <v>4301167.5824175822</v>
+      </c>
+      <c r="L47" s="79">
+        <v>150000000</v>
+      </c>
+      <c r="M47" s="221">
+        <v>97.132788000000005</v>
+      </c>
+      <c r="N47" s="78">
+        <v>-16453161.749999993</v>
+      </c>
+      <c r="O47" s="50">
+        <v>-10493359.787790688</v>
+      </c>
+      <c r="P47" s="210">
+        <v>145699182</v>
+      </c>
+      <c r="Q47" s="211">
+        <v>0</v>
+      </c>
+      <c r="R47" s="213"/>
+      <c r="S47" s="216">
+        <v>0</v>
+      </c>
+      <c r="T47" s="218">
+        <v>0</v>
+      </c>
+      <c r="U47" s="35"/>
+      <c r="V47" s="35"/>
+    </row>
+    <row r="48" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A48" s="202">
+        <v>46888</v>
+      </c>
+      <c r="B48" s="183">
+        <v>0</v>
+      </c>
+      <c r="C48" s="224"/>
+      <c r="D48" s="196">
+        <v>732</v>
+      </c>
+      <c r="E48" s="205">
+        <v>0</v>
+      </c>
+      <c r="F48" s="79">
+        <v>0</v>
+      </c>
+      <c r="G48" s="78">
+        <v>6067859.7383720959</v>
+      </c>
+      <c r="H48" s="79">
+        <v>-6084484.0116279097</v>
+      </c>
+      <c r="I48" s="79" t="str">
+        <v/>
+      </c>
+      <c r="J48" s="198">
+        <v>156067859.73837209</v>
+      </c>
+      <c r="K48" s="79">
+        <v>4687500</v>
+      </c>
+      <c r="L48" s="79">
+        <v>150000000</v>
+      </c>
+      <c r="M48" s="221">
+        <v>97.132788000000005</v>
+      </c>
+      <c r="N48" s="78">
+        <v>-16453161.749999993</v>
+      </c>
+      <c r="O48" s="50">
+        <v>-10368677.738372084</v>
+      </c>
+      <c r="P48" s="210">
+        <v>145699182</v>
+      </c>
+      <c r="Q48" s="211">
+        <v>0</v>
+      </c>
+      <c r="R48" s="213"/>
+      <c r="S48" s="216">
+        <v>-4687500</v>
+      </c>
+      <c r="T48" s="218">
+        <v>-21140661.749999993</v>
+      </c>
+      <c r="U48" s="35"/>
+      <c r="V48" s="35"/>
+    </row>
+    <row r="49" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A49" s="202">
+        <v>46904</v>
+      </c>
+      <c r="B49" s="183">
+        <v>0</v>
+      </c>
+      <c r="C49" s="224"/>
+      <c r="D49" s="196">
+        <v>748</v>
+      </c>
+      <c r="E49" s="205">
+        <v>0</v>
+      </c>
+      <c r="F49" s="79">
+        <v>0</v>
+      </c>
+      <c r="G49" s="78">
+        <v>5934865.552325584</v>
+      </c>
+      <c r="H49" s="79">
+        <v>-6217478.1976744216</v>
+      </c>
+      <c r="I49" s="79" t="str">
+        <v/>
+      </c>
+      <c r="J49" s="198">
+        <v>155934865.55232558</v>
+      </c>
+      <c r="K49" s="79">
+        <v>407608.69565217389</v>
+      </c>
+      <c r="L49" s="79">
+        <v>150000000</v>
+      </c>
+      <c r="M49" s="221">
+        <v>97.132788000000005</v>
+      </c>
+      <c r="N49" s="78">
+        <v>-16453161.749999993</v>
+      </c>
+      <c r="O49" s="50">
+        <v>-10235683.552325571</v>
+      </c>
+      <c r="P49" s="210">
+        <v>145699182</v>
+      </c>
+      <c r="Q49" s="211">
+        <v>0</v>
+      </c>
+      <c r="R49" s="213"/>
+      <c r="S49" s="216">
+        <v>0</v>
+      </c>
+      <c r="T49" s="218">
+        <v>0</v>
+      </c>
+      <c r="U49" s="35"/>
+      <c r="V49" s="35"/>
+    </row>
+    <row r="50" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A50" s="202">
+        <v>46934</v>
+      </c>
+      <c r="B50" s="183">
+        <v>0</v>
+      </c>
+      <c r="C50" s="224"/>
+      <c r="D50" s="196">
+        <v>778</v>
+      </c>
+      <c r="E50" s="205">
+        <v>0</v>
+      </c>
+      <c r="F50" s="79">
+        <v>0</v>
+      </c>
+      <c r="G50" s="78">
+        <v>5685501.4534883751</v>
+      </c>
+      <c r="H50" s="79">
+        <v>-6466842.2965116305</v>
+      </c>
+      <c r="I50" s="79" t="str">
+        <v/>
+      </c>
+      <c r="J50" s="198">
+        <v>155685501.45348838</v>
+      </c>
+      <c r="K50" s="79">
+        <v>1171875</v>
+      </c>
+      <c r="L50" s="79">
+        <v>150000000</v>
+      </c>
+      <c r="M50" s="221">
+        <v>97.132788000000005</v>
+      </c>
+      <c r="N50" s="78">
+        <v>-16453161.749999993</v>
+      </c>
+      <c r="O50" s="50">
+        <v>-9986319.4534883611</v>
+      </c>
+      <c r="P50" s="210">
+        <v>145699182</v>
+      </c>
+      <c r="Q50" s="211">
+        <v>2.9802322387695313E-8</v>
+      </c>
+      <c r="R50" s="213"/>
+      <c r="S50" s="216">
+        <v>0</v>
+      </c>
+      <c r="T50" s="218">
+        <v>0</v>
+      </c>
+      <c r="U50" s="35"/>
+      <c r="V50" s="35"/>
+    </row>
+    <row r="51" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A51" s="202">
+        <v>46965</v>
+      </c>
+      <c r="B51" s="183">
+        <v>0</v>
+      </c>
+      <c r="C51" s="224"/>
+      <c r="D51" s="196">
+        <v>809</v>
+      </c>
+      <c r="E51" s="205">
+        <v>0</v>
+      </c>
+      <c r="F51" s="79">
+        <v>0</v>
+      </c>
+      <c r="G51" s="78">
+        <v>5427825.2180232592</v>
+      </c>
+      <c r="H51" s="79">
+        <v>-6724518.5319767464</v>
+      </c>
+      <c r="I51" s="79" t="str">
+        <v/>
+      </c>
+      <c r="J51" s="198">
+        <v>155427825.21802324</v>
+      </c>
+      <c r="K51" s="79">
+        <v>1961616.8478260869</v>
+      </c>
+      <c r="L51" s="79">
+        <v>149999999.99999997</v>
+      </c>
+      <c r="M51" s="221">
+        <v>97.132788000000005</v>
+      </c>
+      <c r="N51" s="78">
+        <v>-16453161.749999993</v>
+      </c>
+      <c r="O51" s="50">
+        <v>-9728643.2180232462</v>
+      </c>
+      <c r="P51" s="210">
+        <v>145699182</v>
+      </c>
+      <c r="Q51" s="211">
+        <v>0</v>
+      </c>
+      <c r="R51" s="213"/>
+      <c r="S51" s="216">
+        <v>0</v>
+      </c>
+      <c r="T51" s="218">
+        <v>0</v>
+      </c>
+      <c r="U51" s="35"/>
+      <c r="V51" s="35"/>
+    </row>
+    <row r="52" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A52" s="202">
+        <v>46996</v>
+      </c>
+      <c r="B52" s="183">
+        <v>0</v>
+      </c>
+      <c r="C52" s="224"/>
+      <c r="D52" s="196">
+        <v>840</v>
+      </c>
+      <c r="E52" s="205">
+        <v>0</v>
+      </c>
+      <c r="F52" s="79">
+        <v>0</v>
+      </c>
+      <c r="G52" s="78">
+        <v>5170148.9825581424</v>
+      </c>
+      <c r="H52" s="79">
+        <v>-6982194.7674418632</v>
+      </c>
+      <c r="I52" s="79" t="str">
+        <v/>
+      </c>
+      <c r="J52" s="198">
+        <v>155170148.98255813</v>
+      </c>
+      <c r="K52" s="79">
+        <v>2751358.6956521738</v>
+      </c>
+      <c r="L52" s="79">
+        <v>150000000</v>
+      </c>
+      <c r="M52" s="221">
+        <v>97.132788000000005</v>
+      </c>
+      <c r="N52" s="78">
+        <v>-16453161.749999993</v>
+      </c>
+      <c r="O52" s="50">
+        <v>-9470966.9825581294</v>
+      </c>
+      <c r="P52" s="210">
+        <v>145699182</v>
+      </c>
+      <c r="Q52" s="211">
+        <v>0</v>
+      </c>
+      <c r="R52" s="213"/>
+      <c r="S52" s="216">
+        <v>0</v>
+      </c>
+      <c r="T52" s="218">
+        <v>0</v>
+      </c>
+      <c r="U52" s="35"/>
+      <c r="V52" s="35"/>
+    </row>
+    <row r="53" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A53" s="202">
+        <v>47026</v>
+      </c>
+      <c r="B53" s="183">
+        <v>0</v>
+      </c>
+      <c r="C53" s="224"/>
+      <c r="D53" s="196">
+        <v>870</v>
+      </c>
+      <c r="E53" s="205">
+        <v>0</v>
+      </c>
+      <c r="F53" s="79">
+        <v>0</v>
+      </c>
+      <c r="G53" s="78">
+        <v>4920784.8837209316</v>
+      </c>
+      <c r="H53" s="79">
+        <v>-7231558.866279074</v>
+      </c>
+      <c r="I53" s="79" t="str">
+        <v/>
+      </c>
+      <c r="J53" s="198">
+        <v>154920784.88372093</v>
+      </c>
+      <c r="K53" s="79">
+        <v>3515625</v>
+      </c>
+      <c r="L53" s="79">
+        <v>150000000</v>
+      </c>
+      <c r="M53" s="221">
+        <v>97.132788000000005</v>
+      </c>
+      <c r="N53" s="78">
+        <v>-16453161.749999993</v>
+      </c>
+      <c r="O53" s="50">
+        <v>-9221602.8837209195</v>
+      </c>
+      <c r="P53" s="210">
+        <v>145699182</v>
+      </c>
+      <c r="Q53" s="211">
+        <v>0</v>
+      </c>
+      <c r="R53" s="213"/>
+      <c r="S53" s="216">
+        <v>0</v>
+      </c>
+      <c r="T53" s="218">
+        <v>0</v>
+      </c>
+      <c r="U53" s="35"/>
+      <c r="V53" s="35"/>
+    </row>
+    <row r="54" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A54" s="202">
+        <v>47057</v>
+      </c>
+      <c r="B54" s="183">
+        <v>0</v>
+      </c>
+      <c r="C54" s="224"/>
+      <c r="D54" s="196">
+        <v>901</v>
+      </c>
+      <c r="E54" s="205">
+        <v>0</v>
+      </c>
+      <c r="F54" s="79">
+        <v>0</v>
+      </c>
+      <c r="G54" s="78">
+        <v>4663108.6482558157</v>
+      </c>
+      <c r="H54" s="79">
+        <v>-7489235.1017441899</v>
+      </c>
+      <c r="I54" s="79" t="str">
+        <v/>
+      </c>
+      <c r="J54" s="198">
+        <v>154663108.64825583</v>
+      </c>
+      <c r="K54" s="79">
+        <v>4305366.8478260869</v>
+      </c>
+      <c r="L54" s="79">
+        <v>150000000</v>
+      </c>
+      <c r="M54" s="221">
+        <v>97.132788000000005</v>
+      </c>
+      <c r="N54" s="78">
+        <v>-16453161.749999993</v>
+      </c>
+      <c r="O54" s="50">
+        <v>-8963926.6482558027</v>
+      </c>
+      <c r="P54" s="210">
+        <v>145699182</v>
+      </c>
+      <c r="Q54" s="211">
+        <v>2.9802322387695313E-8</v>
+      </c>
+      <c r="R54" s="213"/>
+      <c r="S54" s="216">
+        <v>0</v>
+      </c>
+      <c r="T54" s="218">
+        <v>0</v>
+      </c>
+      <c r="U54" s="35"/>
+      <c r="V54" s="35"/>
+    </row>
+    <row r="55" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A55" s="202">
+        <v>47072</v>
+      </c>
+      <c r="B55" s="183">
+        <v>0</v>
+      </c>
+      <c r="C55" s="224"/>
+      <c r="D55" s="196">
+        <v>916</v>
+      </c>
+      <c r="E55" s="205">
+        <v>0</v>
+      </c>
+      <c r="F55" s="79">
+        <v>0</v>
+      </c>
+      <c r="G55" s="78">
+        <v>4538426.5988372108</v>
+      </c>
+      <c r="H55" s="79">
+        <v>-7613917.1511627948</v>
+      </c>
+      <c r="I55" s="79" t="str">
+        <v/>
+      </c>
+      <c r="J55" s="198">
+        <v>154538426.5988372</v>
+      </c>
+      <c r="K55" s="79">
+        <v>4687500</v>
+      </c>
+      <c r="L55" s="79">
+        <v>150000000</v>
+      </c>
+      <c r="M55" s="221">
+        <v>97.132788000000005</v>
+      </c>
+      <c r="N55" s="78">
+        <v>-16453161.749999993</v>
+      </c>
+      <c r="O55" s="50">
+        <v>-8839244.5988371968</v>
+      </c>
+      <c r="P55" s="210">
+        <v>145699182</v>
+      </c>
+      <c r="Q55" s="211">
+        <v>0</v>
+      </c>
+      <c r="R55" s="213"/>
+      <c r="S55" s="216">
+        <v>-4687500</v>
+      </c>
+      <c r="T55" s="218">
+        <v>-21140661.749999993</v>
+      </c>
+      <c r="U55" s="35"/>
+      <c r="V55" s="35"/>
+    </row>
+    <row r="56" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A56" s="202">
+        <v>47087</v>
+      </c>
+      <c r="B56" s="183">
+        <v>0</v>
+      </c>
+      <c r="C56" s="224"/>
+      <c r="D56" s="196">
+        <v>931</v>
+      </c>
+      <c r="E56" s="205">
+        <v>0</v>
+      </c>
+      <c r="F56" s="79">
+        <v>0</v>
+      </c>
+      <c r="G56" s="78">
+        <v>4413744.5494186059</v>
+      </c>
+      <c r="H56" s="79">
+        <v>-7738599.2005813997</v>
+      </c>
+      <c r="I56" s="79" t="str">
+        <v/>
+      </c>
+      <c r="J56" s="198">
+        <v>154413744.5494186</v>
+      </c>
+      <c r="K56" s="79">
+        <v>388466.85082872928</v>
+      </c>
+      <c r="L56" s="79">
+        <v>150000000</v>
+      </c>
+      <c r="M56" s="221">
+        <v>97.132788000000005</v>
+      </c>
+      <c r="N56" s="78">
+        <v>-16453161.749999993</v>
+      </c>
+      <c r="O56" s="50">
+        <v>-8714562.5494185928</v>
+      </c>
+      <c r="P56" s="210">
+        <v>145699182</v>
+      </c>
+      <c r="Q56" s="211">
+        <v>0</v>
+      </c>
+      <c r="R56" s="213"/>
+      <c r="S56" s="216">
+        <v>0</v>
+      </c>
+      <c r="T56" s="218">
+        <v>0</v>
+      </c>
+      <c r="U56" s="35"/>
+      <c r="V56" s="35"/>
+    </row>
+    <row r="57" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A57" s="202">
+        <v>47118</v>
+      </c>
+      <c r="B57" s="183">
+        <v>0</v>
+      </c>
+      <c r="C57" s="224"/>
+      <c r="D57" s="196">
+        <v>962</v>
+      </c>
+      <c r="E57" s="205">
+        <v>0</v>
+      </c>
+      <c r="F57" s="79">
+        <v>0</v>
+      </c>
+      <c r="G57" s="78">
+        <v>4156068.31395349</v>
+      </c>
+      <c r="H57" s="79">
+        <v>-7996275.4360465156</v>
+      </c>
+      <c r="I57" s="79" t="str">
+        <v/>
+      </c>
+      <c r="J57" s="198">
+        <v>154156068.31395349</v>
+      </c>
+      <c r="K57" s="79">
+        <v>1191298.3425414364</v>
+      </c>
+      <c r="L57" s="79">
+        <v>150000000</v>
+      </c>
+      <c r="M57" s="221">
+        <v>97.132788000000005</v>
+      </c>
+      <c r="N57" s="78">
+        <v>-16453161.749999993</v>
+      </c>
+      <c r="O57" s="50">
+        <v>-8456886.3139534779</v>
+      </c>
+      <c r="P57" s="210">
+        <v>145699182</v>
+      </c>
+      <c r="Q57" s="211">
+        <v>0</v>
+      </c>
+      <c r="R57" s="213"/>
+      <c r="S57" s="216">
+        <v>0</v>
+      </c>
+      <c r="T57" s="218">
+        <v>0</v>
+      </c>
+      <c r="U57" s="35"/>
+      <c r="V57" s="35"/>
+    </row>
+    <row r="58" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A58" s="202">
+        <v>47149</v>
+      </c>
+      <c r="B58" s="183">
+        <v>0</v>
+      </c>
+      <c r="C58" s="224"/>
+      <c r="D58" s="196">
+        <v>993</v>
+      </c>
+      <c r="E58" s="205">
+        <v>0</v>
+      </c>
+      <c r="F58" s="79">
+        <v>0</v>
+      </c>
+      <c r="G58" s="78">
+        <v>3898392.0784883741</v>
+      </c>
+      <c r="H58" s="79">
+        <v>-8253951.6715116315</v>
+      </c>
+      <c r="I58" s="79" t="str">
+        <v/>
+      </c>
+      <c r="J58" s="198">
+        <v>153898392.07848838</v>
+      </c>
+      <c r="K58" s="79">
+        <v>1994129.8342541438</v>
+      </c>
+      <c r="L58" s="79">
+        <v>150000000</v>
+      </c>
+      <c r="M58" s="221">
+        <v>97.132788000000005</v>
+      </c>
+      <c r="N58" s="78">
+        <v>-16453161.749999993</v>
+      </c>
+      <c r="O58" s="50">
+        <v>-8199210.0784883611</v>
+      </c>
+      <c r="P58" s="210">
+        <v>145699182</v>
+      </c>
+      <c r="Q58" s="211">
+        <v>2.9802322387695313E-8</v>
+      </c>
+      <c r="R58" s="213"/>
+      <c r="S58" s="216">
+        <v>0</v>
+      </c>
+      <c r="T58" s="218">
+        <v>0</v>
+      </c>
+      <c r="U58" s="35"/>
+      <c r="V58" s="35"/>
+    </row>
+    <row r="59" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A59" s="202">
+        <v>47177</v>
+      </c>
+      <c r="B59" s="183">
+        <v>0</v>
+      </c>
+      <c r="C59" s="203"/>
+      <c r="D59" s="196">
+        <v>1021</v>
+      </c>
+      <c r="E59" s="205">
+        <v>0</v>
+      </c>
+      <c r="F59" s="79">
+        <v>0</v>
+      </c>
+      <c r="G59" s="78">
+        <v>3665652.2529069781</v>
+      </c>
+      <c r="H59" s="79">
+        <v>-8486691.4970930275</v>
+      </c>
+      <c r="I59" s="79" t="str">
+        <v/>
+      </c>
+      <c r="J59" s="198">
+        <v>153665652.25290698</v>
+      </c>
+      <c r="K59" s="79">
+        <v>2719267.9558011051</v>
+      </c>
+      <c r="L59" s="79">
+        <v>150000000</v>
+      </c>
+      <c r="M59" s="221">
+        <v>97.132788000000005</v>
+      </c>
+      <c r="N59" s="78">
+        <v>-16453161.749999993</v>
+      </c>
+      <c r="O59" s="50">
+        <v>-7966470.2529069651</v>
+      </c>
+      <c r="P59" s="210">
+        <v>145699182</v>
+      </c>
+      <c r="Q59" s="211">
+        <v>0</v>
+      </c>
+      <c r="R59" s="213"/>
+      <c r="S59" s="216">
+        <v>0</v>
+      </c>
+      <c r="T59" s="218">
+        <v>0</v>
+      </c>
+      <c r="U59" s="35"/>
+      <c r="V59" s="35"/>
+    </row>
+    <row r="60" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A60" s="202">
+        <v>47208</v>
+      </c>
+      <c r="B60" s="183">
+        <v>0</v>
+      </c>
+      <c r="C60" s="203"/>
+      <c r="D60" s="196">
+        <v>1052</v>
+      </c>
+      <c r="E60" s="205">
+        <v>0</v>
+      </c>
+      <c r="F60" s="79">
+        <v>0</v>
+      </c>
+      <c r="G60" s="78">
+        <v>3407976.0174418613</v>
+      </c>
+      <c r="H60" s="79">
+        <v>-8744367.7325581443</v>
+      </c>
+      <c r="I60" s="79" t="str">
+        <v/>
+      </c>
+      <c r="J60" s="198">
+        <v>153407976.01744187</v>
+      </c>
+      <c r="K60" s="79">
+        <v>3522099.4475138122</v>
+      </c>
+      <c r="L60" s="79">
+        <v>150000000</v>
+      </c>
+      <c r="M60" s="221">
+        <v>100</v>
+      </c>
+      <c r="N60" s="78">
+        <v>-12152343.75</v>
+      </c>
+      <c r="O60" s="50">
+        <v>-3407976.0174418557</v>
+      </c>
+      <c r="P60" s="210">
+        <v>150000000</v>
+      </c>
+      <c r="Q60" s="211">
+        <v>0</v>
+      </c>
+      <c r="R60" s="213"/>
+      <c r="S60" s="216">
+        <v>0</v>
+      </c>
+      <c r="T60" s="218">
+        <v>0</v>
+      </c>
+      <c r="U60" s="35"/>
+      <c r="V60" s="35"/>
+    </row>
+    <row r="61" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A61" s="202">
+        <v>47238</v>
+      </c>
+      <c r="B61" s="183">
+        <v>0</v>
+      </c>
+      <c r="C61" s="203"/>
+      <c r="D61" s="196">
+        <v>1082</v>
+      </c>
+      <c r="E61" s="205">
+        <v>0</v>
+      </c>
+      <c r="F61" s="79">
+        <v>0</v>
+      </c>
+      <c r="G61" s="78">
+        <v>3158611.9186046533</v>
+      </c>
+      <c r="H61" s="79">
+        <v>-8993731.8313953523</v>
+      </c>
+      <c r="I61" s="79" t="str">
+        <v/>
+      </c>
+      <c r="J61" s="198">
+        <v>153158611.91860464</v>
+      </c>
+      <c r="K61" s="79">
+        <v>4299033.1491712704</v>
+      </c>
+      <c r="L61" s="79">
+        <v>150000000</v>
+      </c>
+      <c r="M61" s="221">
+        <v>97.132788000000005</v>
+      </c>
+      <c r="N61" s="78">
+        <v>-16453161.749999993</v>
+      </c>
+      <c r="O61" s="50">
+        <v>-7459429.9186046403</v>
+      </c>
+      <c r="P61" s="210">
+        <v>145699182</v>
+      </c>
+      <c r="Q61" s="211">
+        <v>0</v>
+      </c>
+      <c r="R61" s="213"/>
+      <c r="S61" s="216">
+        <v>0</v>
+      </c>
+      <c r="T61" s="218">
+        <v>0</v>
+      </c>
+      <c r="U61" s="35"/>
+      <c r="V61" s="35"/>
+    </row>
+    <row r="62" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A62" s="202">
+        <v>47253</v>
+      </c>
+      <c r="B62" s="183">
+        <v>0</v>
+      </c>
+      <c r="C62" s="203"/>
+      <c r="D62" s="196">
+        <v>1097</v>
+      </c>
+      <c r="E62" s="205">
+        <v>0</v>
+      </c>
+      <c r="F62" s="79">
+        <v>0</v>
+      </c>
+      <c r="G62" s="78">
+        <v>3033929.8691860475</v>
+      </c>
+      <c r="H62" s="79">
+        <v>-9118413.8808139581</v>
+      </c>
+      <c r="I62" s="79" t="str">
+        <v/>
+      </c>
+      <c r="J62" s="198">
+        <v>153033929.86918604</v>
+      </c>
+      <c r="K62" s="79">
+        <v>4687500</v>
+      </c>
+      <c r="L62" s="79">
+        <v>150000000</v>
+      </c>
+      <c r="M62" s="221">
+        <v>97.132788000000005</v>
+      </c>
+      <c r="N62" s="78">
+        <v>-16453161.749999993</v>
+      </c>
+      <c r="O62" s="50">
+        <v>-7334747.8691860344</v>
+      </c>
+      <c r="P62" s="210">
+        <v>145699182</v>
+      </c>
+      <c r="Q62" s="211">
+        <v>0</v>
+      </c>
+      <c r="R62" s="213"/>
+      <c r="S62" s="216">
+        <v>-4687500</v>
+      </c>
+      <c r="T62" s="218">
+        <v>-21140661.749999993</v>
+      </c>
+      <c r="U62" s="35"/>
+      <c r="V62" s="35"/>
+    </row>
+    <row r="63" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A63" s="202">
+        <v>47269</v>
+      </c>
+      <c r="B63" s="183">
+        <v>0</v>
+      </c>
+      <c r="C63" s="203"/>
+      <c r="D63" s="196">
+        <v>1113</v>
+      </c>
+      <c r="E63" s="205">
+        <v>0</v>
+      </c>
+      <c r="F63" s="79">
+        <v>0</v>
+      </c>
+      <c r="G63" s="78">
+        <v>2900935.6831395365</v>
+      </c>
+      <c r="H63" s="79">
+        <v>-9251408.0668604691</v>
+      </c>
+      <c r="I63" s="79" t="str">
+        <v/>
+      </c>
+      <c r="J63" s="198">
+        <v>152900935.68313953</v>
+      </c>
+      <c r="K63" s="79">
+        <v>407608.69565217389</v>
+      </c>
+      <c r="L63" s="79">
+        <v>150000000</v>
+      </c>
+      <c r="M63" s="221">
+        <v>97.132788000000005</v>
+      </c>
+      <c r="N63" s="78">
+        <v>-16453161.749999993</v>
+      </c>
+      <c r="O63" s="50">
+        <v>-7201753.6831395235</v>
+      </c>
+      <c r="P63" s="210">
+        <v>145699182</v>
+      </c>
+      <c r="Q63" s="211">
+        <v>0</v>
+      </c>
+      <c r="R63" s="213"/>
+      <c r="S63" s="216">
+        <v>0</v>
+      </c>
+      <c r="T63" s="218">
+        <v>0</v>
+      </c>
+      <c r="U63" s="35"/>
+      <c r="V63" s="35"/>
+    </row>
+    <row r="64" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A64" s="202">
+        <v>47299</v>
+      </c>
+      <c r="B64" s="183">
+        <v>0</v>
+      </c>
+      <c r="C64" s="203"/>
+      <c r="D64" s="196">
+        <v>1143</v>
+      </c>
+      <c r="E64" s="205">
+        <v>0</v>
+      </c>
+      <c r="F64" s="79">
+        <v>0</v>
+      </c>
+      <c r="G64" s="78">
+        <v>2651571.5843023267</v>
+      </c>
+      <c r="H64" s="79">
+        <v>-9500772.1656976789</v>
+      </c>
+      <c r="I64" s="79" t="str">
+        <v/>
+      </c>
+      <c r="J64" s="198">
+        <v>152651571.58430231</v>
+      </c>
+      <c r="K64" s="79">
+        <v>1171875</v>
+      </c>
+      <c r="L64" s="79">
+        <v>149999999.99999997</v>
+      </c>
+      <c r="M64" s="221">
+        <v>97.132788000000005</v>
+      </c>
+      <c r="N64" s="78">
+        <v>-16453161.749999993</v>
+      </c>
+      <c r="O64" s="50">
+        <v>-6952389.5843023136</v>
+      </c>
+      <c r="P64" s="210">
+        <v>145699182</v>
+      </c>
+      <c r="Q64" s="211">
+        <v>0</v>
+      </c>
+      <c r="R64" s="213"/>
+      <c r="S64" s="216">
+        <v>0</v>
+      </c>
+      <c r="T64" s="218">
+        <v>0</v>
+      </c>
+      <c r="U64" s="35"/>
+      <c r="V64" s="35"/>
+    </row>
+    <row r="65" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A65" s="202">
+        <v>47330</v>
+      </c>
+      <c r="B65" s="183">
+        <v>0</v>
+      </c>
+      <c r="C65" s="203"/>
+      <c r="D65" s="196">
+        <v>1174</v>
+      </c>
+      <c r="E65" s="205">
+        <v>0</v>
+      </c>
+      <c r="F65" s="79">
+        <v>0</v>
+      </c>
+      <c r="G65" s="78">
+        <v>2393895.3488372117</v>
+      </c>
+      <c r="H65" s="79">
+        <v>-9758448.4011627939</v>
+      </c>
+      <c r="I65" s="79" t="str">
+        <v/>
+      </c>
+      <c r="J65" s="198">
+        <v>152393895.3488372</v>
+      </c>
+      <c r="K65" s="79">
+        <v>1961616.8478260869</v>
+      </c>
+      <c r="L65" s="79">
+        <v>150000000</v>
+      </c>
+      <c r="M65" s="221">
+        <v>97.132788000000005</v>
+      </c>
+      <c r="N65" s="78">
+        <v>-16453161.749999993</v>
+      </c>
+      <c r="O65" s="50">
+        <v>-6694713.3488371987</v>
+      </c>
+      <c r="P65" s="210">
+        <v>145699182</v>
+      </c>
+      <c r="Q65" s="211">
+        <v>0</v>
+      </c>
+      <c r="R65" s="213"/>
+      <c r="S65" s="216">
+        <v>0</v>
+      </c>
+      <c r="T65" s="218">
+        <v>0</v>
+      </c>
+      <c r="U65" s="35"/>
+      <c r="V65" s="35"/>
+    </row>
+    <row r="66" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A66" s="202">
+        <v>47361</v>
+      </c>
+      <c r="B66" s="183">
+        <v>0</v>
+      </c>
+      <c r="C66" s="203"/>
+      <c r="D66" s="196">
+        <v>1205</v>
+      </c>
+      <c r="E66" s="205">
+        <v>0</v>
+      </c>
+      <c r="F66" s="79">
+        <v>0</v>
+      </c>
+      <c r="G66" s="78">
+        <v>2136219.1133720931</v>
+      </c>
+      <c r="H66" s="79">
+        <v>-10016124.636627913</v>
+      </c>
+      <c r="I66" s="79" t="str">
+        <v/>
+      </c>
+      <c r="J66" s="198">
+        <v>152136219.11337209</v>
+      </c>
+      <c r="K66" s="79">
+        <v>2751358.6956521738</v>
+      </c>
+      <c r="L66" s="79">
+        <v>150000000</v>
+      </c>
+      <c r="M66" s="221">
+        <v>97.132788000000005</v>
+      </c>
+      <c r="N66" s="78">
+        <v>-16453161.749999993</v>
+      </c>
+      <c r="O66" s="50">
+        <v>-6437037.11337208</v>
+      </c>
+      <c r="P66" s="210">
+        <v>145699182</v>
+      </c>
+      <c r="Q66" s="211">
+        <v>0</v>
+      </c>
+      <c r="R66" s="213"/>
+      <c r="S66" s="216">
+        <v>0</v>
+      </c>
+      <c r="T66" s="218">
+        <v>0</v>
+      </c>
+      <c r="U66" s="35"/>
+      <c r="V66" s="35"/>
+    </row>
+    <row r="67" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A67" s="202">
+        <v>47391</v>
+      </c>
+      <c r="B67" s="183">
+        <v>0</v>
+      </c>
+      <c r="C67" s="203"/>
+      <c r="D67" s="196">
+        <v>1235</v>
+      </c>
+      <c r="E67" s="205">
+        <v>0</v>
+      </c>
+      <c r="F67" s="79">
+        <v>0</v>
+      </c>
+      <c r="G67" s="78">
+        <v>1886855.0145348832</v>
+      </c>
+      <c r="H67" s="79">
+        <v>-10265488.735465122</v>
+      </c>
+      <c r="I67" s="79" t="str">
+        <v/>
+      </c>
+      <c r="J67" s="198">
+        <v>151886855.01453489</v>
+      </c>
+      <c r="K67" s="79">
+        <v>3515625</v>
+      </c>
+      <c r="L67" s="79">
+        <v>150000000</v>
+      </c>
+      <c r="M67" s="221">
+        <v>97.132788000000005</v>
+      </c>
+      <c r="N67" s="78">
+        <v>-16453161.749999993</v>
+      </c>
+      <c r="O67" s="50">
+        <v>-6187673.0145348702</v>
+      </c>
+      <c r="P67" s="210">
+        <v>145699182</v>
+      </c>
+      <c r="Q67" s="211">
+        <v>2.9802322387695313E-8</v>
+      </c>
+      <c r="R67" s="213"/>
+      <c r="S67" s="216">
+        <v>0</v>
+      </c>
+      <c r="T67" s="218">
+        <v>0</v>
+      </c>
+      <c r="U67" s="35"/>
+      <c r="V67" s="35"/>
+    </row>
+    <row r="68" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A68" s="202">
+        <v>47422</v>
+      </c>
+      <c r="B68" s="183">
+        <v>0</v>
+      </c>
+      <c r="C68" s="203"/>
+      <c r="D68" s="196">
+        <v>1266</v>
+      </c>
+      <c r="E68" s="205">
+        <v>0</v>
+      </c>
+      <c r="F68" s="79">
+        <v>0</v>
+      </c>
+      <c r="G68" s="78">
+        <v>1629178.7790697683</v>
+      </c>
+      <c r="H68" s="79">
+        <v>-10523164.970930237</v>
+      </c>
+      <c r="I68" s="79" t="str">
+        <v/>
+      </c>
+      <c r="J68" s="198">
+        <v>151629178.77906975</v>
+      </c>
+      <c r="K68" s="79">
+        <v>4305366.8478260869</v>
+      </c>
+      <c r="L68" s="79">
+        <v>149999999.99999997</v>
+      </c>
+      <c r="M68" s="221">
+        <v>97.132788000000005</v>
+      </c>
+      <c r="N68" s="78">
+        <v>-16453161.749999993</v>
+      </c>
+      <c r="O68" s="50">
+        <v>-5929996.7790697552</v>
+      </c>
+      <c r="P68" s="210">
+        <v>145699182</v>
+      </c>
+      <c r="Q68" s="211">
+        <v>0</v>
+      </c>
+      <c r="R68" s="213"/>
+      <c r="S68" s="216">
+        <v>0</v>
+      </c>
+      <c r="T68" s="218">
+        <v>0</v>
+      </c>
+      <c r="U68" s="35"/>
+      <c r="V68" s="35"/>
+    </row>
+    <row r="69" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A69" s="202">
+        <v>47437</v>
+      </c>
+      <c r="B69" s="183">
+        <v>0</v>
+      </c>
+      <c r="C69" s="203"/>
+      <c r="D69" s="196">
+        <v>1281</v>
+      </c>
+      <c r="E69" s="205">
+        <v>0</v>
+      </c>
+      <c r="F69" s="79">
+        <v>0</v>
+      </c>
+      <c r="G69" s="78">
+        <v>1504496.7296511624</v>
+      </c>
+      <c r="H69" s="79">
+        <v>-10647847.020348843</v>
+      </c>
+      <c r="I69" s="79" t="str">
+        <v/>
+      </c>
+      <c r="J69" s="198">
+        <v>151504496.72965115</v>
+      </c>
+      <c r="K69" s="79">
+        <v>4687500</v>
+      </c>
+      <c r="L69" s="79">
+        <v>150000000</v>
+      </c>
+      <c r="M69" s="221">
+        <v>97.132788000000005</v>
+      </c>
+      <c r="N69" s="78">
+        <v>-16453161.749999993</v>
+      </c>
+      <c r="O69" s="50">
+        <v>-5805314.7296511494</v>
+      </c>
+      <c r="P69" s="210">
+        <v>145699182</v>
+      </c>
+      <c r="Q69" s="211">
+        <v>0</v>
+      </c>
+      <c r="R69" s="213"/>
+      <c r="S69" s="216">
+        <v>-4687500</v>
+      </c>
+      <c r="T69" s="218">
+        <v>-21140661.749999993</v>
+      </c>
+      <c r="U69" s="35"/>
+      <c r="V69" s="35"/>
+    </row>
+    <row r="70" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A70" s="202">
+        <v>47452</v>
+      </c>
+      <c r="B70" s="183">
+        <v>0</v>
+      </c>
+      <c r="C70" s="203"/>
+      <c r="D70" s="196">
+        <v>1296</v>
+      </c>
+      <c r="E70" s="205">
+        <v>0</v>
+      </c>
+      <c r="F70" s="79">
+        <v>0</v>
+      </c>
+      <c r="G70" s="78">
+        <v>1379814.6802325584</v>
+      </c>
+      <c r="H70" s="79">
+        <v>-10772529.069767447</v>
+      </c>
+      <c r="I70" s="79" t="str">
+        <v/>
+      </c>
+      <c r="J70" s="198">
+        <v>151379814.68023255</v>
+      </c>
+      <c r="K70" s="79">
+        <v>388466.85082872928</v>
+      </c>
+      <c r="L70" s="79">
+        <v>150000000</v>
+      </c>
+      <c r="M70" s="221">
+        <v>97.132788000000005</v>
+      </c>
+      <c r="N70" s="78">
+        <v>-16453161.749999993</v>
+      </c>
+      <c r="O70" s="50">
+        <v>-5680632.6802325454</v>
+      </c>
+      <c r="P70" s="210">
+        <v>145699182</v>
+      </c>
+      <c r="Q70" s="211">
+        <v>0</v>
+      </c>
+      <c r="R70" s="213"/>
+      <c r="S70" s="216">
+        <v>0</v>
+      </c>
+      <c r="T70" s="218">
+        <v>0</v>
+      </c>
+      <c r="U70" s="35"/>
+      <c r="V70" s="35"/>
+    </row>
+    <row r="71" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A71" s="202">
+        <v>47483</v>
+      </c>
+      <c r="B71" s="183">
+        <v>0</v>
+      </c>
+      <c r="C71" s="203"/>
+      <c r="D71" s="196">
+        <v>1327</v>
+      </c>
+      <c r="E71" s="205">
+        <v>0</v>
+      </c>
+      <c r="F71" s="79">
+        <v>0</v>
+      </c>
+      <c r="G71" s="78">
+        <v>1122138.4447674416</v>
+      </c>
+      <c r="H71" s="79">
+        <v>-11030205.305232564</v>
+      </c>
+      <c r="I71" s="79" t="str">
+        <v/>
+      </c>
+      <c r="J71" s="198">
+        <v>151122138.44476745</v>
+      </c>
+      <c r="K71" s="79">
+        <v>1191298.3425414364</v>
+      </c>
+      <c r="L71" s="79">
+        <v>150000000</v>
+      </c>
+      <c r="M71" s="221">
+        <v>97.132788000000005</v>
+      </c>
+      <c r="N71" s="78">
+        <v>-16453161.749999993</v>
+      </c>
+      <c r="O71" s="50">
+        <v>-5422956.4447674286</v>
+      </c>
+      <c r="P71" s="210">
+        <v>145699182</v>
+      </c>
+      <c r="Q71" s="211">
+        <v>2.9802322387695313E-8</v>
+      </c>
+      <c r="R71" s="213"/>
+      <c r="S71" s="216">
+        <v>0</v>
+      </c>
+      <c r="T71" s="218">
+        <v>0</v>
+      </c>
+      <c r="U71" s="35"/>
+      <c r="V71" s="35"/>
+    </row>
+    <row r="72" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A72" s="202">
+        <v>47514</v>
+      </c>
+      <c r="B72" s="183">
+        <v>0</v>
+      </c>
+      <c r="C72" s="203"/>
+      <c r="D72" s="204">
+        <v>1358</v>
+      </c>
+      <c r="E72" s="207">
+        <v>0</v>
+      </c>
+      <c r="F72" s="103">
+        <v>0</v>
+      </c>
+      <c r="G72" s="50">
+        <v>864462.20930232666</v>
+      </c>
+      <c r="H72" s="103">
+        <v>-11287881.540697679</v>
+      </c>
+      <c r="I72" s="103" t="str">
+        <v/>
+      </c>
+      <c r="J72" s="208">
+        <v>150864462.20930231</v>
+      </c>
+      <c r="K72" s="103">
+        <v>1994129.8342541438</v>
+      </c>
+      <c r="L72" s="103">
+        <v>149999999.99999997</v>
+      </c>
+      <c r="M72" s="221">
+        <v>97.132788000000005</v>
+      </c>
+      <c r="N72" s="50">
+        <v>-16453161.749999993</v>
+      </c>
+      <c r="O72" s="50">
+        <v>-5165280.2093023136</v>
+      </c>
+      <c r="P72" s="210">
+        <v>145699182</v>
+      </c>
+      <c r="Q72" s="212">
+        <v>0</v>
+      </c>
+      <c r="R72" s="213"/>
+      <c r="S72" s="216">
+        <v>0</v>
+      </c>
+      <c r="T72" s="218">
+        <v>0</v>
+      </c>
+      <c r="U72" s="35"/>
+      <c r="V72" s="35"/>
+    </row>
+    <row r="73" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A73" s="202">
+        <v>47542</v>
+      </c>
+      <c r="B73" s="183">
+        <v>0</v>
+      </c>
+      <c r="C73" s="203"/>
+      <c r="D73" s="204">
+        <v>1386</v>
+      </c>
+      <c r="E73" s="207">
+        <v>0</v>
+      </c>
+      <c r="F73" s="103">
+        <v>0</v>
+      </c>
+      <c r="G73" s="50">
+        <v>631722.38372093067</v>
+      </c>
+      <c r="H73" s="103">
+        <v>-11520621.366279075</v>
+      </c>
+      <c r="I73" s="103" t="str">
+        <v/>
+      </c>
+      <c r="J73" s="208">
+        <v>150631722.38372093</v>
+      </c>
+      <c r="K73" s="103">
+        <v>2719267.9558011051</v>
+      </c>
+      <c r="L73" s="103">
+        <v>150000000</v>
+      </c>
+      <c r="M73" s="221">
+        <v>97.132788000000005</v>
+      </c>
+      <c r="N73" s="50">
+        <v>-16453161.749999993</v>
+      </c>
+      <c r="O73" s="50">
+        <v>-4932540.3837209176</v>
+      </c>
+      <c r="P73" s="210">
+        <v>145699182</v>
+      </c>
+      <c r="Q73" s="212">
+        <v>2.9802322387695313E-8</v>
+      </c>
+      <c r="R73" s="213"/>
+      <c r="S73" s="216">
+        <v>0</v>
+      </c>
+      <c r="T73" s="218">
+        <v>0</v>
+      </c>
+      <c r="U73" s="35"/>
+      <c r="V73" s="35"/>
+    </row>
+    <row r="74" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A74" s="202">
+        <v>47573</v>
+      </c>
+      <c r="B74" s="183">
+        <v>0</v>
+      </c>
+      <c r="C74" s="203"/>
+      <c r="D74" s="204">
+        <v>1417</v>
+      </c>
+      <c r="E74" s="207">
+        <v>0</v>
+      </c>
+      <c r="F74" s="103">
+        <v>0</v>
+      </c>
+      <c r="G74" s="50">
+        <v>374046.14825581387</v>
+      </c>
+      <c r="H74" s="103">
+        <v>-11778297.601744192</v>
+      </c>
+      <c r="I74" s="103" t="str">
+        <v/>
+      </c>
+      <c r="J74" s="208">
+        <v>150374046.1482558</v>
+      </c>
+      <c r="K74" s="103">
+        <v>3522099.4475138122</v>
+      </c>
+      <c r="L74" s="103">
+        <v>149999999.99999997</v>
+      </c>
+      <c r="M74" s="221">
+        <v>97.132788000000005</v>
+      </c>
+      <c r="N74" s="50">
+        <v>-16453161.749999993</v>
+      </c>
+      <c r="O74" s="50">
+        <v>-4674864.1482558008</v>
+      </c>
+      <c r="P74" s="210">
+        <v>145699182</v>
+      </c>
+      <c r="Q74" s="212">
+        <v>0</v>
+      </c>
+      <c r="R74" s="213"/>
+      <c r="S74" s="216">
+        <v>0</v>
+      </c>
+      <c r="T74" s="218">
+        <v>0</v>
+      </c>
+      <c r="U74" s="35"/>
+      <c r="V74" s="35"/>
+    </row>
+    <row r="75" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A75" s="202">
+        <v>47603</v>
+      </c>
+      <c r="B75" s="183">
+        <v>0</v>
+      </c>
+      <c r="C75" s="203"/>
+      <c r="D75" s="204">
+        <v>1447</v>
+      </c>
+      <c r="E75" s="207">
+        <v>0</v>
+      </c>
+      <c r="F75" s="103">
+        <v>0</v>
+      </c>
+      <c r="G75" s="50">
+        <v>124682.04941860586</v>
+      </c>
+      <c r="H75" s="103">
+        <v>-12027661.7005814</v>
+      </c>
+      <c r="I75" s="103" t="str">
+        <v/>
+      </c>
+      <c r="J75" s="208">
+        <v>150124682.0494186</v>
+      </c>
+      <c r="K75" s="103">
+        <v>4299033.1491712704</v>
+      </c>
+      <c r="L75" s="103">
+        <v>150000000</v>
+      </c>
+      <c r="M75" s="221">
+        <v>97.132788000000005</v>
+      </c>
+      <c r="N75" s="50">
+        <v>-16453161.749999993</v>
+      </c>
+      <c r="O75" s="50">
+        <v>-4425500.0494185928</v>
+      </c>
+      <c r="P75" s="210">
+        <v>145699182</v>
+      </c>
+      <c r="Q75" s="212">
+        <v>0</v>
+      </c>
+      <c r="R75" s="213"/>
+      <c r="S75" s="216">
+        <v>0</v>
+      </c>
+      <c r="T75" s="218">
+        <v>0</v>
+      </c>
+      <c r="U75" s="35"/>
+      <c r="V75" s="35"/>
+    </row>
+    <row r="76" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A76" s="202">
+        <v>47618</v>
+      </c>
+      <c r="B76" s="183">
+        <v>150000000</v>
+      </c>
+      <c r="C76" s="203"/>
+      <c r="D76" s="204">
+        <v>1462</v>
+      </c>
+      <c r="E76" s="207">
+        <v>0</v>
+      </c>
+      <c r="F76" s="103">
+        <v>0</v>
+      </c>
+      <c r="G76" s="50">
+        <v>0</v>
+      </c>
+      <c r="H76" s="103">
+        <v>-12152343.750000006</v>
+      </c>
+      <c r="I76" s="103" t="str">
+        <v/>
+      </c>
+      <c r="J76" s="208">
+        <v>150000000</v>
+      </c>
+      <c r="K76" s="103">
+        <v>4687500</v>
+      </c>
+      <c r="L76" s="103">
+        <v>150000000</v>
+      </c>
+      <c r="M76" s="221">
+        <v>97.132788000000005</v>
+      </c>
+      <c r="N76" s="50">
+        <v>-16453161.749999993</v>
+      </c>
+      <c r="O76" s="50">
+        <v>-4300817.999999987</v>
+      </c>
+      <c r="P76" s="210">
+        <v>145699182</v>
+      </c>
+      <c r="Q76" s="212">
+        <v>0</v>
+      </c>
+      <c r="R76" s="213"/>
+      <c r="S76" s="216">
+        <v>-4687500</v>
+      </c>
+      <c r="T76" s="218">
+        <v>-21140661.749999993</v>
+      </c>
+      <c r="U76" s="35"/>
+      <c r="V76" s="35"/>
+    </row>
+    <row r="77" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A77" s="202"/>
+      <c r="B77" s="183"/>
+      <c r="C77" s="203"/>
+      <c r="D77" s="204"/>
+      <c r="E77" s="207"/>
+      <c r="F77" s="103"/>
+      <c r="G77" s="50"/>
+      <c r="H77" s="103"/>
+      <c r="I77" s="103"/>
+      <c r="J77" s="208"/>
+      <c r="K77" s="103"/>
+      <c r="L77" s="103"/>
+      <c r="M77" s="221">
+        <v>97.132788000000005</v>
+      </c>
+      <c r="N77" s="50"/>
+      <c r="O77" s="50"/>
+      <c r="P77" s="210"/>
+      <c r="Q77" s="212"/>
+      <c r="R77" s="213"/>
+      <c r="S77" s="35"/>
+      <c r="T77" s="218"/>
+      <c r="U77" s="35"/>
+      <c r="V77" s="35"/>
+    </row>
+    <row r="78" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A78" s="202"/>
+      <c r="B78" s="183"/>
+      <c r="C78" s="203"/>
+      <c r="D78" s="204"/>
+      <c r="E78" s="207"/>
+      <c r="F78" s="103"/>
+      <c r="G78" s="50"/>
+      <c r="H78" s="103"/>
+      <c r="I78" s="103"/>
+      <c r="J78" s="208"/>
+      <c r="K78" s="103"/>
+      <c r="L78" s="103"/>
+      <c r="M78" s="221">
+        <v>97.132788000000005</v>
+      </c>
+      <c r="N78" s="50"/>
+      <c r="O78" s="50"/>
+      <c r="P78" s="210"/>
+      <c r="Q78" s="212"/>
+      <c r="R78" s="213"/>
+      <c r="S78" s="35"/>
+      <c r="T78" s="218"/>
+      <c r="U78" s="35"/>
+      <c r="V78" s="35"/>
+    </row>
+    <row r="79" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A79" s="202"/>
+      <c r="B79" s="183"/>
+      <c r="C79" s="203"/>
+      <c r="D79" s="204"/>
+      <c r="E79" s="207"/>
+      <c r="F79" s="103"/>
+      <c r="G79" s="50"/>
+      <c r="H79" s="208"/>
+      <c r="I79" s="103"/>
+      <c r="J79" s="208"/>
+      <c r="K79" s="103"/>
+      <c r="L79" s="103"/>
+      <c r="M79" s="221">
+        <v>100</v>
+      </c>
+      <c r="N79" s="50"/>
+      <c r="O79" s="50"/>
+      <c r="P79" s="210"/>
+      <c r="Q79" s="212"/>
+      <c r="R79" s="213"/>
+      <c r="S79" s="35"/>
+      <c r="T79" s="218"/>
+      <c r="U79" s="35"/>
+      <c r="V79" s="35"/>
+    </row>
+    <row r="80" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A80" s="202"/>
+      <c r="B80" s="183"/>
+      <c r="C80" s="203"/>
+      <c r="D80" s="204"/>
+      <c r="E80" s="207"/>
+      <c r="F80" s="103"/>
+      <c r="G80" s="50"/>
+      <c r="H80" s="103"/>
+      <c r="I80" s="103"/>
+      <c r="J80" s="208"/>
+      <c r="K80" s="103"/>
+      <c r="L80" s="103"/>
+      <c r="M80" s="221"/>
+      <c r="N80" s="50"/>
+      <c r="O80" s="50"/>
+      <c r="P80" s="210"/>
+      <c r="Q80" s="212"/>
+      <c r="R80" s="213"/>
+      <c r="S80" s="35"/>
+      <c r="T80" s="218"/>
+      <c r="U80" s="35"/>
+      <c r="V80" s="35"/>
+    </row>
+    <row r="81" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A81" s="202"/>
+      <c r="B81" s="183"/>
+      <c r="D81" s="204"/>
+      <c r="E81" s="207"/>
+      <c r="F81" s="103"/>
+      <c r="G81" s="50"/>
+      <c r="H81" s="103"/>
+      <c r="I81" s="103"/>
+      <c r="J81" s="208"/>
+      <c r="K81" s="103"/>
+      <c r="L81" s="103"/>
+      <c r="M81" s="221"/>
+      <c r="N81" s="35"/>
+      <c r="O81" s="35"/>
+      <c r="P81" s="210"/>
+      <c r="Q81" s="225"/>
+      <c r="R81" s="35"/>
+      <c r="S81" s="35"/>
+      <c r="T81" s="218"/>
+      <c r="U81" s="35"/>
+      <c r="V81" s="35"/>
+    </row>
+    <row r="82" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A82" s="202"/>
+      <c r="D82" s="204"/>
+      <c r="E82" s="207"/>
+      <c r="F82" s="103"/>
+      <c r="G82" s="50"/>
+      <c r="H82" s="103"/>
+      <c r="I82" s="103"/>
+      <c r="J82" s="208"/>
+      <c r="K82" s="103"/>
+      <c r="L82" s="103"/>
+      <c r="M82" s="226"/>
+      <c r="N82" s="35"/>
+      <c r="O82" s="35"/>
+      <c r="P82" s="210"/>
+      <c r="Q82" s="225"/>
+      <c r="R82" s="35"/>
+      <c r="S82" s="35"/>
+      <c r="T82" s="218"/>
+      <c r="U82" s="35"/>
+      <c r="V82" s="35"/>
+    </row>
+    <row r="83" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A83" s="202"/>
+      <c r="D83" s="204"/>
+      <c r="E83" s="207"/>
+      <c r="F83" s="103"/>
+      <c r="G83" s="50"/>
+      <c r="H83" s="103"/>
+      <c r="I83" s="103"/>
+      <c r="J83" s="208"/>
+      <c r="K83" s="103"/>
+      <c r="L83" s="103"/>
+      <c r="M83" s="226"/>
+      <c r="N83" s="35"/>
+      <c r="O83" s="35"/>
+      <c r="P83" s="210"/>
+      <c r="Q83" s="227"/>
+      <c r="R83" s="35"/>
+      <c r="S83" s="35"/>
+      <c r="T83" s="218"/>
+      <c r="U83" s="35"/>
+      <c r="V83" s="35"/>
+    </row>
+    <row r="84" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A84" s="202"/>
+      <c r="D84" s="204"/>
+      <c r="E84" s="207"/>
+      <c r="F84" s="103"/>
+      <c r="G84" s="50"/>
+      <c r="H84" s="103"/>
+      <c r="I84" s="103"/>
+      <c r="J84" s="208"/>
+      <c r="K84" s="103"/>
+      <c r="L84" s="103"/>
+      <c r="M84" s="226"/>
+      <c r="N84" s="35"/>
+      <c r="O84" s="35"/>
+      <c r="P84" s="210"/>
+      <c r="Q84" s="227"/>
+      <c r="R84" s="35"/>
+      <c r="S84" s="35"/>
+      <c r="T84" s="218"/>
+      <c r="U84" s="35"/>
+      <c r="V84" s="35"/>
+    </row>
+    <row r="85" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A85" s="202"/>
+      <c r="D85" s="204"/>
+      <c r="E85" s="207"/>
+      <c r="F85" s="103"/>
+      <c r="G85" s="50"/>
+      <c r="H85" s="103"/>
+      <c r="I85" s="103"/>
+      <c r="J85" s="208"/>
+      <c r="K85" s="103"/>
+      <c r="L85" s="103"/>
+      <c r="M85" s="226"/>
+      <c r="N85" s="35"/>
+      <c r="O85" s="35"/>
+      <c r="P85" s="210"/>
+      <c r="Q85" s="227"/>
+      <c r="R85" s="35"/>
+      <c r="S85" s="35"/>
+      <c r="T85" s="35"/>
+      <c r="U85" s="35"/>
+      <c r="V85" s="35"/>
+    </row>
+    <row r="86" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A86" s="202"/>
+      <c r="D86" s="204"/>
+      <c r="E86" s="207"/>
+      <c r="F86" s="103"/>
+      <c r="G86" s="50"/>
+      <c r="H86" s="103"/>
+      <c r="I86" s="103"/>
+      <c r="J86" s="208"/>
+      <c r="K86" s="103"/>
+      <c r="L86" s="103"/>
+      <c r="M86" s="226"/>
+      <c r="N86" s="35"/>
+      <c r="O86" s="35"/>
+      <c r="P86" s="210"/>
+      <c r="Q86" s="227"/>
+      <c r="R86" s="35"/>
+      <c r="S86" s="35"/>
+      <c r="T86" s="35"/>
+      <c r="U86" s="35"/>
+      <c r="V86" s="35"/>
+    </row>
+    <row r="87" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A87" s="202"/>
+      <c r="D87" s="204"/>
+      <c r="E87" s="207"/>
+      <c r="F87" s="103"/>
+      <c r="G87" s="50"/>
+      <c r="H87" s="103"/>
+      <c r="I87" s="103"/>
+      <c r="J87" s="208"/>
+      <c r="K87" s="103"/>
+      <c r="L87" s="103"/>
+      <c r="M87" s="226"/>
+      <c r="N87" s="35"/>
+      <c r="O87" s="35"/>
+      <c r="P87" s="210"/>
+      <c r="Q87" s="227"/>
+      <c r="R87" s="35"/>
+      <c r="S87" s="35"/>
+      <c r="T87" s="35"/>
+      <c r="U87" s="35"/>
+      <c r="V87" s="35"/>
+    </row>
+    <row r="88" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A88" s="202"/>
+      <c r="D88" s="204"/>
+      <c r="E88" s="207"/>
+      <c r="F88" s="103"/>
+      <c r="G88" s="50"/>
+      <c r="H88" s="103"/>
+      <c r="I88" s="103"/>
+      <c r="J88" s="208"/>
+      <c r="K88" s="103"/>
+      <c r="L88" s="103"/>
+      <c r="M88" s="226"/>
+      <c r="N88" s="35"/>
+      <c r="O88" s="35"/>
+      <c r="P88" s="210"/>
+      <c r="Q88" s="227"/>
+      <c r="R88" s="35"/>
+      <c r="S88" s="35"/>
+      <c r="T88" s="35"/>
+      <c r="U88" s="35"/>
+      <c r="V88" s="35"/>
+    </row>
+    <row r="89" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A89" s="202"/>
+      <c r="D89" s="204"/>
+      <c r="E89" s="207"/>
+      <c r="F89" s="103"/>
+      <c r="G89" s="50"/>
+      <c r="H89" s="103"/>
+      <c r="I89" s="103"/>
+      <c r="J89" s="208"/>
+      <c r="K89" s="103"/>
+      <c r="L89" s="103"/>
+      <c r="M89" s="226"/>
+      <c r="N89" s="35"/>
+      <c r="O89" s="35"/>
+      <c r="P89" s="210"/>
+      <c r="Q89" s="227"/>
+      <c r="R89" s="35"/>
+      <c r="S89" s="35"/>
+      <c r="T89" s="35"/>
+      <c r="U89" s="35"/>
+      <c r="V89" s="35"/>
+    </row>
+    <row r="90" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A90" s="228"/>
+      <c r="D90" s="204"/>
+      <c r="E90" s="207"/>
+      <c r="F90" s="103"/>
+      <c r="G90" s="50"/>
+      <c r="H90" s="103"/>
+      <c r="I90" s="103"/>
+      <c r="J90" s="208"/>
+      <c r="K90" s="103"/>
+      <c r="L90" s="103"/>
+      <c r="M90" s="226"/>
+      <c r="N90" s="35"/>
+      <c r="O90" s="35"/>
+      <c r="P90" s="210"/>
+      <c r="Q90" s="227"/>
+      <c r="R90" s="35"/>
+      <c r="S90" s="35"/>
+      <c r="T90" s="35"/>
+      <c r="U90" s="35"/>
+      <c r="V90" s="35"/>
+    </row>
+    <row r="91" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A91" s="228"/>
+      <c r="D91" s="35"/>
+      <c r="E91" s="207"/>
+      <c r="F91" s="103"/>
+      <c r="G91" s="50"/>
+      <c r="H91" s="103"/>
+      <c r="I91" s="103"/>
+      <c r="J91" s="208"/>
+      <c r="K91" s="103"/>
+      <c r="L91" s="103"/>
+      <c r="M91" s="35"/>
+      <c r="N91" s="35"/>
+      <c r="O91" s="35"/>
+      <c r="P91" s="210"/>
+      <c r="Q91" s="35"/>
+      <c r="R91" s="35"/>
+      <c r="S91" s="35"/>
+      <c r="T91" s="35"/>
+      <c r="U91" s="35"/>
+      <c r="V91" s="35"/>
+    </row>
+    <row r="92" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A92" s="229"/>
+      <c r="F92" s="230"/>
+    </row>
+    <row r="93" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A93" s="229"/>
+    </row>
+    <row r="94" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A94" s="5"/>
+      <c r="B94" s="5"/>
+      <c r="C94" s="5"/>
+    </row>
+    <row r="95" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A95" s="5"/>
+      <c r="B95" s="5"/>
+      <c r="C95" s="5"/>
+    </row>
+    <row r="96" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A96" s="5"/>
+      <c r="B96" s="5"/>
+      <c r="C96" s="5"/>
+    </row>
+    <row r="97" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A97" s="5"/>
+      <c r="B97" s="5"/>
+      <c r="C97" s="5"/>
+    </row>
+    <row r="98" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A98" s="5"/>
+      <c r="B98" s="5"/>
+      <c r="C98" s="5"/>
+    </row>
+    <row r="99" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A99" s="231"/>
+      <c r="B99" s="5"/>
+      <c r="C99" s="5"/>
+    </row>
+    <row r="100" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A100" s="232"/>
+      <c r="B100" s="233"/>
+    </row>
+    <row r="101" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A101" s="237"/>
+      <c r="B101" s="238"/>
+      <c r="C101" s="239"/>
+      <c r="D101" s="235"/>
+      <c r="E101" s="236"/>
+      <c r="F101" s="5"/>
+      <c r="G101" s="5"/>
+      <c r="H101" s="5"/>
+      <c r="I101" s="5"/>
+      <c r="J101" s="5"/>
+      <c r="K101" s="5"/>
+    </row>
+    <row r="102" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A102" s="240"/>
+      <c r="B102" s="240"/>
+      <c r="C102" s="240"/>
+      <c r="D102" s="236"/>
+      <c r="E102" s="236"/>
+      <c r="F102" s="5"/>
+      <c r="G102" s="5"/>
+      <c r="H102" s="5"/>
+      <c r="I102" s="5"/>
+      <c r="J102" s="5"/>
+      <c r="K102" s="5"/>
+    </row>
+    <row r="103" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A103" s="237"/>
+      <c r="B103" s="238"/>
+      <c r="C103" s="234"/>
+      <c r="D103" s="235"/>
+      <c r="E103" s="236"/>
+      <c r="F103" s="5"/>
+      <c r="G103" s="5"/>
+      <c r="H103" s="5"/>
+      <c r="I103" s="5"/>
+      <c r="J103" s="5"/>
+      <c r="K103" s="5"/>
+    </row>
+    <row r="104" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A104" s="237"/>
+      <c r="B104" s="238"/>
+      <c r="C104" s="239"/>
+      <c r="D104" s="235"/>
+      <c r="E104" s="236"/>
+      <c r="F104" s="5"/>
+      <c r="G104" s="5"/>
+      <c r="H104" s="5"/>
+      <c r="I104" s="5"/>
+      <c r="J104" s="5"/>
+      <c r="K104" s="5"/>
+    </row>
+    <row r="105" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A105" s="240"/>
+      <c r="B105" s="240"/>
+      <c r="C105" s="240"/>
+      <c r="D105" s="236"/>
+      <c r="E105" s="236"/>
+      <c r="F105" s="5"/>
+      <c r="G105" s="5"/>
+      <c r="H105" s="5"/>
+      <c r="I105" s="5"/>
+      <c r="J105" s="5"/>
+      <c r="K105" s="5"/>
+    </row>
+    <row r="106" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A106" s="237"/>
+      <c r="B106" s="238"/>
+      <c r="C106" s="234"/>
+      <c r="D106" s="235"/>
+      <c r="E106" s="236"/>
+      <c r="F106" s="5"/>
+      <c r="G106" s="5"/>
+      <c r="H106" s="5"/>
+      <c r="I106" s="5"/>
+      <c r="J106" s="5"/>
+      <c r="K106" s="5"/>
+    </row>
+    <row r="107" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A107" s="237"/>
+      <c r="B107" s="238"/>
+      <c r="C107" s="239"/>
+      <c r="D107" s="235"/>
+      <c r="E107" s="236"/>
+      <c r="F107" s="5"/>
+      <c r="G107" s="5"/>
+      <c r="H107" s="5"/>
+      <c r="I107" s="5"/>
+      <c r="J107" s="5"/>
+      <c r="K107" s="5"/>
+    </row>
+    <row r="108" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A108" s="240"/>
+      <c r="B108" s="241"/>
+      <c r="C108" s="240"/>
+      <c r="D108" s="236"/>
+      <c r="E108" s="236"/>
+      <c r="F108" s="5"/>
+      <c r="G108" s="5"/>
+      <c r="H108" s="5"/>
+      <c r="I108" s="5"/>
+      <c r="J108" s="5"/>
+      <c r="K108" s="5"/>
+    </row>
+    <row r="109" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A109" s="237"/>
+      <c r="B109" s="238"/>
+      <c r="C109" s="234"/>
+      <c r="D109" s="235"/>
+      <c r="E109" s="236"/>
+      <c r="F109" s="5"/>
+      <c r="G109" s="5"/>
+      <c r="H109" s="5"/>
+      <c r="I109" s="5"/>
+      <c r="J109" s="5"/>
+      <c r="K109" s="5"/>
+    </row>
+    <row r="110" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A110" s="242"/>
+      <c r="B110" s="243"/>
+      <c r="C110" s="244"/>
+      <c r="D110" s="235"/>
+      <c r="E110" s="236"/>
+      <c r="F110" s="5"/>
+      <c r="G110" s="5"/>
+      <c r="H110" s="5"/>
+      <c r="I110" s="5"/>
+      <c r="J110" s="5"/>
+      <c r="K110" s="5"/>
+    </row>
+    <row r="111" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A111" s="237"/>
+      <c r="B111" s="238"/>
+      <c r="C111" s="239"/>
+      <c r="D111" s="235"/>
+      <c r="E111" s="236"/>
+      <c r="F111" s="5"/>
+      <c r="G111" s="5"/>
+      <c r="H111" s="5"/>
+      <c r="I111" s="5"/>
+      <c r="J111" s="5"/>
+      <c r="K111" s="5"/>
+    </row>
+    <row r="112" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A112" s="240"/>
+      <c r="B112" s="241"/>
+      <c r="C112" s="240"/>
+      <c r="D112" s="236"/>
+      <c r="E112" s="236"/>
+      <c r="F112" s="5"/>
+      <c r="G112" s="5"/>
+      <c r="H112" s="5"/>
+      <c r="I112" s="5"/>
+      <c r="J112" s="5"/>
+      <c r="K112" s="5"/>
+    </row>
+    <row r="113" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A113" s="237"/>
+      <c r="B113" s="238"/>
+      <c r="C113" s="234"/>
+      <c r="D113" s="235"/>
+      <c r="E113" s="236"/>
+      <c r="F113" s="5"/>
+      <c r="G113" s="5"/>
+      <c r="H113" s="5"/>
+      <c r="I113" s="5"/>
+      <c r="J113" s="5"/>
+      <c r="K113" s="5"/>
+    </row>
+    <row r="114" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A114" s="242"/>
+      <c r="B114" s="243"/>
+      <c r="C114" s="244"/>
+      <c r="D114" s="235"/>
+      <c r="E114" s="236"/>
+      <c r="F114" s="5"/>
+      <c r="G114" s="5"/>
+      <c r="H114" s="5"/>
+      <c r="I114" s="5"/>
+      <c r="J114" s="5"/>
+      <c r="K114" s="5"/>
+    </row>
+    <row r="115" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A115" s="237"/>
+      <c r="B115" s="238"/>
+      <c r="C115" s="239"/>
+      <c r="D115" s="235"/>
+      <c r="E115" s="236"/>
+      <c r="F115" s="5"/>
+      <c r="G115" s="5"/>
+      <c r="H115" s="5"/>
+      <c r="I115" s="5"/>
+      <c r="J115" s="5"/>
+      <c r="K115" s="5"/>
+    </row>
+    <row r="116" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A116" s="5"/>
+      <c r="B116" s="5"/>
+      <c r="C116" s="5"/>
+      <c r="D116" s="5"/>
+      <c r="E116" s="5"/>
+      <c r="F116" s="5"/>
+      <c r="G116" s="5"/>
+      <c r="H116" s="5"/>
+      <c r="I116" s="5"/>
+      <c r="J116" s="5"/>
+      <c r="K116" s="5"/>
+    </row>
+    <row r="117" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A117" s="5"/>
+      <c r="B117" s="5"/>
+      <c r="C117" s="5"/>
+      <c r="D117" s="5"/>
+      <c r="E117" s="5"/>
+      <c r="F117" s="5"/>
+      <c r="G117" s="5"/>
+      <c r="H117" s="5"/>
+      <c r="I117" s="5"/>
+      <c r="J117" s="5"/>
+      <c r="K117" s="5"/>
+    </row>
+    <row r="118" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A118" s="232"/>
+      <c r="B118" s="233"/>
+      <c r="C118" s="234"/>
+      <c r="D118" s="235"/>
+      <c r="E118" s="236"/>
+      <c r="F118" s="5"/>
+      <c r="G118" s="5"/>
+      <c r="H118" s="5"/>
+      <c r="I118" s="5"/>
+      <c r="J118" s="5"/>
+      <c r="K118" s="5"/>
+    </row>
+    <row r="119" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A119" s="237"/>
+      <c r="B119" s="238"/>
+      <c r="C119" s="239"/>
+      <c r="D119" s="235"/>
+      <c r="E119" s="236"/>
+      <c r="F119" s="5"/>
+      <c r="G119" s="5"/>
+      <c r="H119" s="5"/>
+      <c r="I119" s="5"/>
+      <c r="J119" s="5"/>
+      <c r="K119" s="5"/>
+    </row>
+    <row r="120" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A120" s="240"/>
+      <c r="B120" s="240"/>
+      <c r="C120" s="240"/>
+      <c r="D120" s="236"/>
+      <c r="E120" s="236"/>
+      <c r="F120" s="5"/>
+      <c r="G120" s="5"/>
+      <c r="H120" s="5"/>
+      <c r="I120" s="5"/>
+      <c r="J120" s="5"/>
+      <c r="K120" s="5"/>
+    </row>
+    <row r="121" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A121" s="237"/>
+      <c r="B121" s="238"/>
+      <c r="C121" s="234"/>
+      <c r="D121" s="235"/>
+      <c r="E121" s="236"/>
+      <c r="F121" s="5"/>
+      <c r="G121" s="5"/>
+      <c r="H121" s="5"/>
+      <c r="I121" s="5"/>
+      <c r="J121" s="5"/>
+      <c r="K121" s="5"/>
+    </row>
+    <row r="122" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A122" s="237"/>
+      <c r="B122" s="238"/>
+      <c r="C122" s="239"/>
+      <c r="D122" s="235"/>
+      <c r="E122" s="236"/>
+      <c r="F122" s="5"/>
+      <c r="G122" s="5"/>
+      <c r="H122" s="5"/>
+      <c r="I122" s="5"/>
+      <c r="J122" s="5"/>
+      <c r="K122" s="5"/>
+    </row>
+    <row r="123" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A123" s="240"/>
+      <c r="B123" s="240"/>
+      <c r="C123" s="240"/>
+      <c r="D123" s="236"/>
+      <c r="E123" s="236"/>
+      <c r="F123" s="5"/>
+      <c r="G123" s="5"/>
+      <c r="H123" s="5"/>
+      <c r="I123" s="5"/>
+      <c r="J123" s="5"/>
+      <c r="K123" s="5"/>
+    </row>
+    <row r="124" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A124" s="237"/>
+      <c r="B124" s="238"/>
+      <c r="C124" s="234"/>
+      <c r="D124" s="235"/>
+      <c r="E124" s="236"/>
+      <c r="F124" s="5"/>
+      <c r="G124" s="5"/>
+      <c r="H124" s="5"/>
+      <c r="I124" s="5"/>
+      <c r="J124" s="5"/>
+      <c r="K124" s="5"/>
+    </row>
+    <row r="125" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A125" s="237"/>
+      <c r="B125" s="238"/>
+      <c r="C125" s="239"/>
+      <c r="D125" s="235"/>
+      <c r="E125" s="236"/>
+      <c r="F125" s="5"/>
+      <c r="G125" s="5"/>
+      <c r="H125" s="5"/>
+      <c r="I125" s="5"/>
+      <c r="J125" s="5"/>
+      <c r="K125" s="5"/>
+    </row>
+    <row r="126" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A126" s="240"/>
+      <c r="B126" s="240"/>
+      <c r="C126" s="240"/>
+      <c r="D126" s="236"/>
+      <c r="E126" s="236"/>
+      <c r="F126" s="5"/>
+      <c r="G126" s="5"/>
+      <c r="H126" s="5"/>
+      <c r="I126" s="5"/>
+      <c r="J126" s="5"/>
+      <c r="K126" s="5"/>
+    </row>
+    <row r="127" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A127" s="237"/>
+      <c r="B127" s="238"/>
+      <c r="C127" s="234"/>
+      <c r="D127" s="235"/>
+      <c r="E127" s="236"/>
+      <c r="F127" s="5"/>
+      <c r="G127" s="5"/>
+      <c r="H127" s="5"/>
+      <c r="I127" s="5"/>
+      <c r="J127" s="5"/>
+      <c r="K127" s="5"/>
+    </row>
+    <row r="128" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A128" s="237"/>
+      <c r="B128" s="238"/>
+      <c r="C128" s="239"/>
+      <c r="D128" s="235"/>
+      <c r="E128" s="236"/>
+      <c r="F128" s="5"/>
+      <c r="G128" s="5"/>
+      <c r="H128" s="5"/>
+      <c r="I128" s="5"/>
+      <c r="J128" s="5"/>
+      <c r="K128" s="5"/>
+    </row>
+    <row r="129" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A129" s="5"/>
+      <c r="B129" s="5"/>
+      <c r="C129" s="5"/>
+      <c r="D129" s="5"/>
+      <c r="E129" s="5"/>
+      <c r="F129" s="5"/>
+      <c r="G129" s="5"/>
+      <c r="H129" s="5"/>
+      <c r="I129" s="5"/>
+      <c r="J129" s="5"/>
+      <c r="K129" s="5"/>
+    </row>
+    <row r="130" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A130" s="5"/>
+      <c r="B130" s="5"/>
+      <c r="C130" s="5"/>
+      <c r="D130" s="5"/>
+      <c r="E130" s="5"/>
+      <c r="F130" s="5"/>
+      <c r="G130" s="5"/>
+      <c r="H130" s="5"/>
+      <c r="I130" s="5"/>
+      <c r="J130" s="5"/>
+      <c r="K130" s="5"/>
+    </row>
+    <row r="131" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A131" s="232"/>
+      <c r="B131" s="233"/>
+      <c r="C131" s="234"/>
+      <c r="D131" s="235"/>
+      <c r="E131" s="236"/>
+      <c r="F131" s="5"/>
+      <c r="G131" s="5"/>
+      <c r="H131" s="5"/>
+      <c r="I131" s="5"/>
+      <c r="J131" s="5"/>
+      <c r="K131" s="5"/>
+    </row>
+    <row r="132" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A132" s="237"/>
+      <c r="B132" s="238"/>
+      <c r="C132" s="239"/>
+      <c r="D132" s="235"/>
+      <c r="E132" s="236"/>
+      <c r="F132" s="5"/>
+      <c r="G132" s="5"/>
+      <c r="H132" s="5"/>
+      <c r="I132" s="5"/>
+      <c r="J132" s="5"/>
+      <c r="K132" s="5"/>
+    </row>
+    <row r="133" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A133" s="5"/>
+      <c r="B133" s="5"/>
+      <c r="C133" s="5"/>
+      <c r="D133" s="5"/>
+      <c r="E133" s="5"/>
+      <c r="F133" s="5"/>
+      <c r="G133" s="5"/>
+      <c r="H133" s="5"/>
+      <c r="I133" s="5"/>
+      <c r="J133" s="5"/>
+      <c r="K133" s="5"/>
+    </row>
+    <row r="134" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A134" s="5"/>
+      <c r="B134" s="5"/>
+      <c r="C134" s="5"/>
+      <c r="D134" s="5"/>
+      <c r="E134" s="5"/>
+      <c r="F134" s="5"/>
+      <c r="G134" s="5"/>
+      <c r="H134" s="5"/>
+      <c r="I134" s="5"/>
+      <c r="J134" s="5"/>
+      <c r="K134" s="5"/>
+    </row>
+    <row r="135" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A135" s="232"/>
+      <c r="B135" s="233"/>
+      <c r="C135" s="234"/>
+      <c r="D135" s="235"/>
+      <c r="E135" s="236"/>
+      <c r="F135" s="5"/>
+      <c r="G135" s="5"/>
+      <c r="H135" s="5"/>
+      <c r="I135" s="5"/>
+      <c r="J135" s="5"/>
+      <c r="K135" s="5"/>
+    </row>
+    <row r="136" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A136" s="237"/>
+      <c r="B136" s="238"/>
+      <c r="C136" s="239"/>
+      <c r="D136" s="235"/>
+      <c r="E136" s="236"/>
+      <c r="F136" s="5"/>
+      <c r="G136" s="5"/>
+      <c r="H136" s="5"/>
+      <c r="I136" s="5"/>
+      <c r="J136" s="5"/>
+      <c r="K136" s="5"/>
+    </row>
+    <row r="137" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A137" s="5"/>
+      <c r="B137" s="5"/>
+      <c r="C137" s="5"/>
+      <c r="D137" s="5"/>
+      <c r="E137" s="5"/>
+      <c r="F137" s="5"/>
+      <c r="G137" s="5"/>
+      <c r="H137" s="5"/>
+      <c r="I137" s="5"/>
+      <c r="J137" s="5"/>
+      <c r="K137" s="5"/>
+    </row>
+    <row r="138" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A138" s="5"/>
+      <c r="B138" s="5"/>
+      <c r="C138" s="5"/>
+      <c r="D138" s="5"/>
+      <c r="E138" s="5"/>
+      <c r="F138" s="5"/>
+      <c r="G138" s="5"/>
+      <c r="H138" s="5"/>
+      <c r="I138" s="5"/>
+      <c r="J138" s="5"/>
+      <c r="K138" s="5"/>
+    </row>
+    <row r="139" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A139" s="5"/>
+      <c r="B139" s="5"/>
+      <c r="C139" s="5"/>
+      <c r="D139" s="5"/>
+      <c r="E139" s="5"/>
+      <c r="F139" s="5"/>
+      <c r="G139" s="5"/>
+      <c r="H139" s="5"/>
+      <c r="I139" s="5"/>
+      <c r="J139" s="5"/>
+      <c r="K139" s="5"/>
+    </row>
+    <row r="140" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A140" s="5"/>
+      <c r="B140" s="5"/>
+      <c r="C140" s="5"/>
+      <c r="D140" s="5"/>
+      <c r="E140" s="5"/>
+      <c r="F140" s="5"/>
+      <c r="G140" s="5"/>
+      <c r="H140" s="5"/>
+      <c r="I140" s="5"/>
+      <c r="J140" s="5"/>
+      <c r="K140" s="5"/>
+    </row>
+    <row r="141" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A141" s="5"/>
+      <c r="B141" s="5"/>
+      <c r="C141" s="5"/>
+      <c r="D141" s="5"/>
+      <c r="E141" s="5"/>
+      <c r="F141" s="5"/>
+      <c r="G141" s="5"/>
+      <c r="H141" s="5"/>
+      <c r="I141" s="5"/>
+      <c r="J141" s="5"/>
+      <c r="K141" s="5"/>
+    </row>
+    <row r="142" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A142" s="5"/>
+      <c r="B142" s="5"/>
+      <c r="C142" s="5"/>
+      <c r="D142" s="5"/>
+      <c r="E142" s="5"/>
+      <c r="F142" s="5"/>
+      <c r="G142" s="5"/>
+      <c r="H142" s="5"/>
+      <c r="I142" s="5"/>
+      <c r="J142" s="5"/>
+      <c r="K142" s="5"/>
+    </row>
+    <row r="143" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A143" s="5"/>
+      <c r="B143" s="5"/>
+      <c r="C143" s="245"/>
+      <c r="D143" s="246"/>
+      <c r="E143" s="236"/>
+      <c r="F143" s="236"/>
+      <c r="G143" s="236"/>
+      <c r="H143" s="5"/>
+      <c r="I143" s="5"/>
+      <c r="J143" s="5"/>
+      <c r="K143" s="5"/>
+    </row>
+    <row r="144" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A144" s="5"/>
+      <c r="B144" s="5"/>
+      <c r="C144" s="245"/>
+      <c r="D144" s="246"/>
+      <c r="E144" s="236"/>
+      <c r="F144" s="236"/>
+      <c r="G144" s="236"/>
+      <c r="H144" s="5"/>
+      <c r="I144" s="5"/>
+      <c r="J144" s="5"/>
+      <c r="K144" s="5"/>
+    </row>
+    <row r="145" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A145" s="5"/>
+      <c r="B145" s="5"/>
+      <c r="C145" s="5"/>
+      <c r="D145" s="5"/>
+      <c r="E145" s="5"/>
+      <c r="F145" s="5"/>
+      <c r="G145" s="5"/>
+      <c r="H145" s="5"/>
+      <c r="I145" s="5"/>
+      <c r="J145" s="5"/>
+      <c r="K145" s="5"/>
+    </row>
+    <row r="146" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A146" s="5"/>
+      <c r="B146" s="5"/>
+      <c r="C146" s="5"/>
+      <c r="D146" s="5"/>
+      <c r="E146" s="5"/>
+      <c r="F146" s="5"/>
+      <c r="G146" s="5"/>
+      <c r="H146" s="5"/>
+      <c r="I146" s="5"/>
+      <c r="J146" s="5"/>
+      <c r="K146" s="5"/>
+    </row>
+    <row r="147" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A147" s="5"/>
+      <c r="B147" s="5"/>
+      <c r="C147" s="5"/>
+      <c r="D147" s="5"/>
+      <c r="E147" s="5"/>
+      <c r="F147" s="5"/>
+      <c r="G147" s="5"/>
+      <c r="H147" s="5"/>
+      <c r="I147" s="5"/>
+      <c r="J147" s="5"/>
+      <c r="K147" s="5"/>
+    </row>
+    <row r="148" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A148" s="5"/>
+      <c r="B148" s="5"/>
+      <c r="C148" s="5"/>
+      <c r="D148" s="5"/>
+      <c r="E148" s="5"/>
+      <c r="F148" s="5"/>
+      <c r="G148" s="5"/>
+      <c r="H148" s="5"/>
+      <c r="I148" s="5"/>
+      <c r="J148" s="5"/>
+      <c r="K148" s="5"/>
+    </row>
+    <row r="149" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A149" s="5"/>
+      <c r="B149" s="5"/>
+      <c r="C149" s="5"/>
+      <c r="D149" s="5"/>
+      <c r="E149" s="5"/>
+      <c r="F149" s="5"/>
+      <c r="G149" s="5"/>
+      <c r="H149" s="5"/>
+      <c r="I149" s="5"/>
+      <c r="J149" s="5"/>
+      <c r="K149" s="5"/>
+    </row>
+    <row r="150" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A150" s="5"/>
+      <c r="B150" s="5"/>
+      <c r="C150" s="5"/>
+      <c r="D150" s="5"/>
+      <c r="E150" s="5"/>
+      <c r="F150" s="5"/>
+      <c r="G150" s="5"/>
+      <c r="H150" s="5"/>
+      <c r="I150" s="5"/>
+      <c r="J150" s="5"/>
+      <c r="K150" s="5"/>
+    </row>
+    <row r="151" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A151" s="5"/>
+      <c r="B151" s="5"/>
+      <c r="C151" s="245"/>
+      <c r="D151" s="246"/>
+      <c r="E151" s="236"/>
+      <c r="F151" s="236"/>
+      <c r="G151" s="236"/>
+      <c r="H151" s="5"/>
+      <c r="I151" s="5"/>
+      <c r="J151" s="5"/>
+      <c r="K151" s="5"/>
+    </row>
+    <row r="152" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A152" s="5"/>
+      <c r="B152" s="5"/>
+      <c r="C152" s="245"/>
+      <c r="D152" s="246"/>
+      <c r="E152" s="236"/>
+      <c r="F152" s="236"/>
+      <c r="G152" s="236"/>
+      <c r="H152" s="5"/>
+      <c r="I152" s="5"/>
+      <c r="J152" s="5"/>
+      <c r="K152" s="5"/>
+    </row>
+    <row r="153" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A153" s="5"/>
+      <c r="B153" s="5"/>
+      <c r="C153" s="5"/>
+      <c r="D153" s="5"/>
+      <c r="E153" s="5"/>
+      <c r="F153" s="5"/>
+      <c r="G153" s="5"/>
+      <c r="H153" s="5"/>
+      <c r="I153" s="5"/>
+      <c r="J153" s="5"/>
+      <c r="K153" s="5"/>
+    </row>
+    <row r="154" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A154" s="5"/>
+      <c r="B154" s="5"/>
+      <c r="C154" s="5"/>
+      <c r="D154" s="5"/>
+      <c r="E154" s="5"/>
+      <c r="F154" s="5"/>
+      <c r="G154" s="5"/>
+      <c r="H154" s="5"/>
+      <c r="I154" s="5"/>
+      <c r="J154" s="5"/>
+      <c r="K154" s="5"/>
+    </row>
+    <row r="155" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A155" s="5"/>
+      <c r="B155" s="5"/>
+      <c r="C155" s="5"/>
+      <c r="D155" s="5"/>
+      <c r="E155" s="5"/>
+      <c r="F155" s="5"/>
+      <c r="G155" s="5"/>
+      <c r="H155" s="5"/>
+      <c r="I155" s="5"/>
+      <c r="J155" s="5"/>
+      <c r="K155" s="5"/>
+    </row>
+    <row r="156" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A156" s="5"/>
+      <c r="B156" s="5"/>
+      <c r="C156" s="5"/>
+      <c r="D156" s="5"/>
+      <c r="E156" s="5"/>
+      <c r="F156" s="5"/>
+      <c r="G156" s="5"/>
+      <c r="H156" s="5"/>
+      <c r="I156" s="5"/>
+      <c r="J156" s="5"/>
+      <c r="K156" s="5"/>
+    </row>
+    <row r="157" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A157" s="5"/>
+      <c r="B157" s="5"/>
+      <c r="C157" s="5"/>
+      <c r="D157" s="5"/>
+      <c r="E157" s="5"/>
+      <c r="F157" s="5"/>
+      <c r="G157" s="5"/>
+      <c r="H157" s="5"/>
+      <c r="I157" s="5"/>
+      <c r="J157" s="5"/>
+      <c r="K157" s="5"/>
+    </row>
+    <row r="162" spans="6:6" x14ac:dyDescent="0.25">
+      <c r="F162" s="230"/>
+    </row>
+    <row r="163" spans="6:6" x14ac:dyDescent="0.25">
+      <c r="F163" s="230"/>
+    </row>
+    <row r="164" spans="6:6" x14ac:dyDescent="0.25">
+      <c r="F164" s="230"/>
+    </row>
+    <row r="165" spans="6:6" x14ac:dyDescent="0.25">
+      <c r="F165" s="230"/>
+    </row>
+    <row r="166" spans="6:6" x14ac:dyDescent="0.25">
+      <c r="F166" s="230"/>
+    </row>
+    <row r="167" spans="6:6" x14ac:dyDescent="0.25">
+      <c r="F167" s="230"/>
+    </row>
+    <row r="168" spans="6:6" x14ac:dyDescent="0.25">
+      <c r="F168" s="230"/>
+    </row>
+    <row r="169" spans="6:6" x14ac:dyDescent="0.25">
+      <c r="F169" s="230"/>
+    </row>
+    <row r="170" spans="6:6" x14ac:dyDescent="0.25">
+      <c r="F170" s="230"/>
+    </row>
+    <row r="171" spans="6:6" x14ac:dyDescent="0.25">
+      <c r="F171" s="230"/>
+    </row>
+    <row r="172" spans="6:6" x14ac:dyDescent="0.25">
+      <c r="F172" s="230"/>
+    </row>
+    <row r="173" spans="6:6" x14ac:dyDescent="0.25">
+      <c r="F173" s="230"/>
+    </row>
+    <row r="174" spans="6:6" x14ac:dyDescent="0.25">
+      <c r="F174" s="230"/>
+    </row>
+    <row r="175" spans="6:6" x14ac:dyDescent="0.25">
+      <c r="F175" s="230"/>
+    </row>
+    <row r="176" spans="6:6" x14ac:dyDescent="0.25">
+      <c r="F176" s="230"/>
+    </row>
+    <row r="177" spans="6:6" x14ac:dyDescent="0.25">
+      <c r="F177" s="230"/>
+    </row>
+    <row r="178" spans="6:6" x14ac:dyDescent="0.25">
+      <c r="F178" s="230"/>
+    </row>
+    <row r="179" spans="6:6" x14ac:dyDescent="0.25">
+      <c r="F179" s="230"/>
+    </row>
+    <row r="180" spans="6:6" x14ac:dyDescent="0.25">
+      <c r="F180" s="230"/>
+    </row>
+    <row r="181" spans="6:6" x14ac:dyDescent="0.25">
+      <c r="F181" s="230"/>
+    </row>
+    <row r="182" spans="6:6" x14ac:dyDescent="0.25">
+      <c r="F182" s="230"/>
+    </row>
+    <row r="183" spans="6:6" x14ac:dyDescent="0.25">
+      <c r="F183" s="230"/>
+    </row>
+    <row r="184" spans="6:6" x14ac:dyDescent="0.25">
+      <c r="F184" s="230"/>
+    </row>
+    <row r="185" spans="6:6" x14ac:dyDescent="0.25">
+      <c r="F185" s="230"/>
+    </row>
+    <row r="186" spans="6:6" x14ac:dyDescent="0.25">
+      <c r="F186" s="230"/>
+    </row>
+    <row r="187" spans="6:6" x14ac:dyDescent="0.25">
+      <c r="F187" s="230"/>
+    </row>
+    <row r="188" spans="6:6" x14ac:dyDescent="0.25">
+      <c r="F188" s="230"/>
+    </row>
+    <row r="189" spans="6:6" x14ac:dyDescent="0.25">
+      <c r="F189" s="230"/>
+    </row>
+    <row r="190" spans="6:6" x14ac:dyDescent="0.25">
+      <c r="F190" s="230"/>
+    </row>
+    <row r="191" spans="6:6" x14ac:dyDescent="0.25">
+      <c r="F191" s="230"/>
+    </row>
+    <row r="192" spans="6:6" x14ac:dyDescent="0.25">
+      <c r="F192" s="230"/>
+    </row>
+    <row r="193" spans="6:6" x14ac:dyDescent="0.25">
+      <c r="F193" s="230"/>
+    </row>
+    <row r="194" spans="6:6" x14ac:dyDescent="0.25">
+      <c r="F194" s="230"/>
+    </row>
+    <row r="195" spans="6:6" x14ac:dyDescent="0.25">
+      <c r="F195" s="230"/>
+    </row>
+    <row r="196" spans="6:6" x14ac:dyDescent="0.25">
+      <c r="F196" s="230"/>
+    </row>
+    <row r="197" spans="6:6" x14ac:dyDescent="0.25">
+      <c r="F197" s="230"/>
+    </row>
+    <row r="198" spans="6:6" x14ac:dyDescent="0.25">
+      <c r="F198" s="230"/>
+    </row>
+    <row r="199" spans="6:6" x14ac:dyDescent="0.25">
+      <c r="F199" s="230"/>
+    </row>
+    <row r="200" spans="6:6" x14ac:dyDescent="0.25">
+      <c r="F200" s="230"/>
+    </row>
+    <row r="201" spans="6:6" x14ac:dyDescent="0.25">
+      <c r="F201" s="230"/>
+    </row>
+    <row r="202" spans="6:6" x14ac:dyDescent="0.25">
+      <c r="F202" s="230"/>
+    </row>
+    <row r="203" spans="6:6" x14ac:dyDescent="0.25">
+      <c r="F203" s="230"/>
+    </row>
+    <row r="204" spans="6:6" x14ac:dyDescent="0.25">
+      <c r="F204" s="230"/>
+    </row>
+    <row r="205" spans="6:6" x14ac:dyDescent="0.25">
+      <c r="F205" s="230"/>
+    </row>
+    <row r="206" spans="6:6" x14ac:dyDescent="0.25">
+      <c r="F206" s="230"/>
+    </row>
+    <row r="207" spans="6:6" x14ac:dyDescent="0.25">
+      <c r="F207" s="230"/>
+    </row>
+    <row r="208" spans="6:6" x14ac:dyDescent="0.25">
+      <c r="F208" s="230"/>
+    </row>
+    <row r="209" spans="6:6" x14ac:dyDescent="0.25">
+      <c r="F209" s="230"/>
+    </row>
+    <row r="210" spans="6:6" x14ac:dyDescent="0.25">
+      <c r="F210" s="230"/>
+    </row>
+    <row r="211" spans="6:6" x14ac:dyDescent="0.25">
+      <c r="F211" s="230"/>
+    </row>
+    <row r="212" spans="6:6" x14ac:dyDescent="0.25">
+      <c r="F212" s="230"/>
+    </row>
+    <row r="213" spans="6:6" x14ac:dyDescent="0.25">
+      <c r="F213" s="230"/>
+    </row>
+    <row r="214" spans="6:6" x14ac:dyDescent="0.25">
+      <c r="F214" s="230"/>
+    </row>
+    <row r="215" spans="6:6" x14ac:dyDescent="0.25">
+      <c r="F215" s="230"/>
+    </row>
+    <row r="216" spans="6:6" x14ac:dyDescent="0.25">
+      <c r="F216" s="230"/>
+    </row>
+    <row r="217" spans="6:6" x14ac:dyDescent="0.25">
+      <c r="F217" s="230"/>
+    </row>
+    <row r="218" spans="6:6" x14ac:dyDescent="0.25">
+      <c r="F218" s="230"/>
+    </row>
+    <row r="219" spans="6:6" x14ac:dyDescent="0.25">
+      <c r="F219" s="230"/>
+    </row>
+    <row r="220" spans="6:6" x14ac:dyDescent="0.25">
+      <c r="F220" s="230"/>
+    </row>
+    <row r="221" spans="6:6" x14ac:dyDescent="0.25">
+      <c r="F221" s="230"/>
+    </row>
+    <row r="222" spans="6:6" x14ac:dyDescent="0.25">
+      <c r="F222" s="230"/>
+    </row>
+    <row r="223" spans="6:6" x14ac:dyDescent="0.25">
+      <c r="F223" s="230"/>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="J1:V1"/>
+  </mergeCells>
+  <conditionalFormatting sqref="A20:A67">
+    <cfRule type="expression" dxfId="2" priority="2">
+      <formula>COUNTIF($J$3:$J$8,A20)&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A20:A91">
+    <cfRule type="expression" dxfId="1" priority="1">
+      <formula>SUMIFS($K$3:$K$8,$J$3:$J$8,A20)&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A20:A98">
+    <cfRule type="expression" dxfId="0" priority="3">
+      <formula>ISNUMBER(MATCH(A20,$F$2:$F$13,0))</formula>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <tableParts count="2">
+    <tablePart r:id="rId1"/>
+    <tablePart r:id="rId2"/>
+  </tableParts>
 </worksheet>
 </file>